--- a/data/Variables Finales/vencimientos_2y_nuevo.xlsx
+++ b/data/Variables Finales/vencimientos_2y_nuevo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Por Tipo y Moneda" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por Tipo y Moneda" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -726,19 +726,19 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
+          <t>03/2015</t>
+        </is>
+      </c>
+      <c r="AE6" s="2" t="inlineStr">
+        <is>
           <t>06/2015</t>
         </is>
       </c>
-      <c r="AE6" s="2" t="inlineStr">
+      <c r="AF6" s="2" t="inlineStr">
         <is>
           <t>09/2015</t>
         </is>
       </c>
-      <c r="AF6" s="2" t="inlineStr">
-        <is>
-          <t>03/2015</t>
-        </is>
-      </c>
       <c r="AG6" s="2" t="inlineStr">
         <is>
           <t>12/2015</t>
@@ -746,19 +746,19 @@
       </c>
       <c r="AH6" s="2" t="inlineStr">
         <is>
+          <t>03/2016</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
           <t>06/2016</t>
         </is>
       </c>
-      <c r="AI6" s="2" t="inlineStr">
+      <c r="AJ6" s="2" t="inlineStr">
         <is>
           <t>09/2016</t>
         </is>
       </c>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>03/2016</t>
-        </is>
-      </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
           <t>12/2016</t>
@@ -766,19 +766,19 @@
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
+          <t>03/2017</t>
+        </is>
+      </c>
+      <c r="AM6" s="2" t="inlineStr">
+        <is>
           <t>06/2017</t>
         </is>
       </c>
-      <c r="AM6" s="2" t="inlineStr">
+      <c r="AN6" s="2" t="inlineStr">
         <is>
           <t>09/2017</t>
         </is>
       </c>
-      <c r="AN6" s="2" t="inlineStr">
-        <is>
-          <t>03/2017</t>
-        </is>
-      </c>
       <c r="AO6" s="2" t="inlineStr">
         <is>
           <t>12/2017</t>
@@ -786,19 +786,19 @@
       </c>
       <c r="AP6" s="2" t="inlineStr">
         <is>
+          <t>03/2018</t>
+        </is>
+      </c>
+      <c r="AQ6" s="2" t="inlineStr">
+        <is>
           <t>06/2018</t>
         </is>
       </c>
-      <c r="AQ6" s="2" t="inlineStr">
+      <c r="AR6" s="2" t="inlineStr">
         <is>
           <t>09/2018</t>
         </is>
       </c>
-      <c r="AR6" s="2" t="inlineStr">
-        <is>
-          <t>03/2018</t>
-        </is>
-      </c>
       <c r="AS6" s="2" t="inlineStr">
         <is>
           <t>12/2018</t>
@@ -806,19 +806,19 @@
       </c>
       <c r="AT6" s="2" t="inlineStr">
         <is>
+          <t>03/2019</t>
+        </is>
+      </c>
+      <c r="AU6" s="2" t="inlineStr">
+        <is>
           <t>06/2019</t>
         </is>
       </c>
-      <c r="AU6" s="2" t="inlineStr">
+      <c r="AV6" s="2" t="inlineStr">
         <is>
           <t>09/2019</t>
         </is>
       </c>
-      <c r="AV6" s="2" t="inlineStr">
-        <is>
-          <t>03/2019</t>
-        </is>
-      </c>
       <c r="AW6" s="2" t="inlineStr">
         <is>
           <t>12/2019</t>
@@ -826,19 +826,19 @@
       </c>
       <c r="AX6" s="2" t="inlineStr">
         <is>
+          <t>03/2020</t>
+        </is>
+      </c>
+      <c r="AY6" s="2" t="inlineStr">
+        <is>
           <t>06/2020</t>
         </is>
       </c>
-      <c r="AY6" s="2" t="inlineStr">
+      <c r="AZ6" s="2" t="inlineStr">
         <is>
           <t>09/2020</t>
         </is>
       </c>
-      <c r="AZ6" s="2" t="inlineStr">
-        <is>
-          <t>03/2020</t>
-        </is>
-      </c>
       <c r="BA6" s="2" t="inlineStr">
         <is>
           <t>12/2020</t>
@@ -846,19 +846,19 @@
       </c>
       <c r="BB6" s="2" t="inlineStr">
         <is>
+          <t>03/2021</t>
+        </is>
+      </c>
+      <c r="BC6" s="2" t="inlineStr">
+        <is>
           <t>06/2021</t>
         </is>
       </c>
-      <c r="BC6" s="2" t="inlineStr">
+      <c r="BD6" s="2" t="inlineStr">
         <is>
           <t>09/2021</t>
         </is>
       </c>
-      <c r="BD6" s="2" t="inlineStr">
-        <is>
-          <t>03/2021</t>
-        </is>
-      </c>
       <c r="BE6" s="2" t="inlineStr">
         <is>
           <t>12/2021</t>
@@ -881,19 +881,19 @@
       </c>
       <c r="BI6" s="2" t="inlineStr">
         <is>
+          <t>03/2023</t>
+        </is>
+      </c>
+      <c r="BJ6" s="2" t="inlineStr">
+        <is>
           <t>06/2023</t>
         </is>
       </c>
-      <c r="BJ6" s="2" t="inlineStr">
+      <c r="BK6" s="2" t="inlineStr">
         <is>
           <t>09/2023</t>
         </is>
       </c>
-      <c r="BK6" s="2" t="inlineStr">
-        <is>
-          <t>03/2023</t>
-        </is>
-      </c>
       <c r="BL6" s="2" t="inlineStr">
         <is>
           <t>12/2023</t>
@@ -901,19 +901,19 @@
       </c>
       <c r="BM6" s="2" t="inlineStr">
         <is>
+          <t>03/2024</t>
+        </is>
+      </c>
+      <c r="BN6" s="2" t="inlineStr">
+        <is>
           <t>06/2024</t>
         </is>
       </c>
-      <c r="BN6" s="2" t="inlineStr">
+      <c r="BO6" s="2" t="inlineStr">
         <is>
           <t>09/2024</t>
         </is>
       </c>
-      <c r="BO6" s="2" t="inlineStr">
-        <is>
-          <t>03/2024</t>
-        </is>
-      </c>
       <c r="BP6" s="2" t="inlineStr">
         <is>
           <t>12/2024</t>
@@ -921,17 +921,17 @@
       </c>
       <c r="BQ6" s="2" t="inlineStr">
         <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="BR6" s="2" t="inlineStr">
+        <is>
           <t>06/2025</t>
         </is>
       </c>
-      <c r="BR6" s="2" t="inlineStr">
+      <c r="BS6" s="2" t="inlineStr">
         <is>
           <t>09/2025</t>
-        </is>
-      </c>
-      <c r="BS6" s="2" t="inlineStr">
-        <is>
-          <t>03/2025</t>
         </is>
       </c>
       <c r="BT6" s="2" t="inlineStr">
@@ -1031,85 +1031,85 @@
         <v>87398.026</v>
       </c>
       <c r="AD7" s="4" t="n">
+        <v>88628.315</v>
+      </c>
+      <c r="AE7" s="4" t="n">
         <v>101544.673</v>
       </c>
-      <c r="AE7" s="4" t="n">
+      <c r="AF7" s="4" t="n">
         <v>105853.556</v>
-      </c>
-      <c r="AF7" s="4" t="n">
-        <v>88628.315</v>
       </c>
       <c r="AG7" s="4" t="n">
         <v>88031.443</v>
       </c>
       <c r="AH7" s="4" t="n">
+        <v>82898.344</v>
+      </c>
+      <c r="AI7" s="4" t="n">
         <v>89085.586</v>
       </c>
-      <c r="AI7" s="4" t="n">
+      <c r="AJ7" s="4" t="n">
         <v>89668.997</v>
-      </c>
-      <c r="AJ7" s="4" t="n">
-        <v>82898.344</v>
       </c>
       <c r="AK7" s="4" t="n">
         <v>108373.846</v>
       </c>
       <c r="AL7" s="4" t="n">
+        <v>114923.759</v>
+      </c>
+      <c r="AM7" s="4" t="n">
         <v>120964.344</v>
       </c>
-      <c r="AM7" s="4" t="n">
+      <c r="AN7" s="4" t="n">
         <v>121528.779</v>
-      </c>
-      <c r="AN7" s="4" t="n">
-        <v>114923.759</v>
       </c>
       <c r="AO7" s="4" t="n">
         <v>129453.821</v>
       </c>
       <c r="AP7" s="4" t="n">
+        <v>133492.536</v>
+      </c>
+      <c r="AQ7" s="4" t="n">
         <v>127729.768</v>
       </c>
-      <c r="AQ7" s="4" t="n">
+      <c r="AR7" s="4" t="n">
         <v>114397.896</v>
-      </c>
-      <c r="AR7" s="4" t="n">
-        <v>133492.536</v>
       </c>
       <c r="AS7" s="4" t="n">
         <v>128760.041</v>
       </c>
       <c r="AT7" s="4" t="n">
+        <v>131470.208</v>
+      </c>
+      <c r="AU7" s="4" t="n">
         <v>135870.769</v>
       </c>
-      <c r="AU7" s="4" t="n">
+      <c r="AV7" s="4" t="n">
         <v>114099.147</v>
-      </c>
-      <c r="AV7" s="4" t="n">
-        <v>131470.208</v>
       </c>
       <c r="AW7" s="4" t="n">
         <v>123970.792</v>
       </c>
       <c r="AX7" s="4" t="n">
+        <v>126488.075</v>
+      </c>
+      <c r="AY7" s="4" t="n">
         <v>137325.236</v>
       </c>
-      <c r="AY7" s="4" t="n">
+      <c r="AZ7" s="4" t="n">
         <v>107614.027</v>
-      </c>
-      <c r="AZ7" s="4" t="n">
-        <v>126488.075</v>
       </c>
       <c r="BA7" s="4" t="n">
         <v>115106.815</v>
       </c>
       <c r="BB7" s="4" t="n">
+        <v>121915.052</v>
+      </c>
+      <c r="BC7" s="4" t="n">
         <v>131144.842</v>
       </c>
-      <c r="BC7" s="4" t="n">
+      <c r="BD7" s="4" t="n">
         <v>136697.946</v>
-      </c>
-      <c r="BD7" s="4" t="n">
-        <v>121915.052</v>
       </c>
       <c r="BE7" s="4" t="n">
         <v>154646.713</v>
@@ -1124,37 +1124,37 @@
         <v>178574.111</v>
       </c>
       <c r="BI7" s="4" t="n">
+        <v>172472.135</v>
+      </c>
+      <c r="BJ7" s="4" t="n">
         <v>191527.107</v>
       </c>
-      <c r="BJ7" s="4" t="n">
+      <c r="BK7" s="4" t="n">
         <v>189523.345</v>
-      </c>
-      <c r="BK7" s="4" t="n">
-        <v>172472.135</v>
       </c>
       <c r="BL7" s="4" t="n">
         <v>158705.147</v>
       </c>
       <c r="BM7" s="4" t="n">
+        <v>132086.675</v>
+      </c>
+      <c r="BN7" s="4" t="n">
         <v>166100.777</v>
       </c>
-      <c r="BN7" s="4" t="n">
+      <c r="BO7" s="4" t="n">
         <v>171012.644</v>
-      </c>
-      <c r="BO7" s="4" t="n">
-        <v>132086.675</v>
       </c>
       <c r="BP7" s="4" t="n">
         <v>200016.714</v>
       </c>
       <c r="BQ7" s="4" t="n">
+        <v>207726.473</v>
+      </c>
+      <c r="BR7" s="4" t="n">
         <v>195326.897</v>
       </c>
-      <c r="BR7" s="4" t="n">
+      <c r="BS7" s="4" t="n">
         <v>194068.53</v>
-      </c>
-      <c r="BS7" s="4" t="n">
-        <v>207726.473</v>
       </c>
       <c r="BT7" s="4" t="n">
         <v>208734.929</v>
@@ -1251,85 +1251,85 @@
         <v>52971.079</v>
       </c>
       <c r="AD8" s="6" t="n">
+        <v>54796.867</v>
+      </c>
+      <c r="AE8" s="6" t="n">
         <v>55126.662</v>
       </c>
-      <c r="AE8" s="6" t="n">
+      <c r="AF8" s="6" t="n">
         <v>59885.452</v>
-      </c>
-      <c r="AF8" s="6" t="n">
-        <v>54796.867</v>
       </c>
       <c r="AG8" s="6" t="n">
         <v>52883.728</v>
       </c>
       <c r="AH8" s="6" t="n">
+        <v>47270.387</v>
+      </c>
+      <c r="AI8" s="6" t="n">
         <v>46968.4</v>
       </c>
-      <c r="AI8" s="6" t="n">
+      <c r="AJ8" s="6" t="n">
         <v>45683.591</v>
-      </c>
-      <c r="AJ8" s="6" t="n">
-        <v>47270.387</v>
       </c>
       <c r="AK8" s="6" t="n">
         <v>58884.274</v>
       </c>
       <c r="AL8" s="6" t="n">
+        <v>61997.368</v>
+      </c>
+      <c r="AM8" s="6" t="n">
         <v>65996.963</v>
       </c>
-      <c r="AM8" s="6" t="n">
+      <c r="AN8" s="6" t="n">
         <v>63921.602</v>
-      </c>
-      <c r="AN8" s="6" t="n">
-        <v>61997.368</v>
       </c>
       <c r="AO8" s="6" t="n">
         <v>71457.027</v>
       </c>
       <c r="AP8" s="6" t="n">
+        <v>64415.551</v>
+      </c>
+      <c r="AQ8" s="6" t="n">
         <v>56046.765</v>
       </c>
-      <c r="AQ8" s="6" t="n">
+      <c r="AR8" s="6" t="n">
         <v>42721.357</v>
-      </c>
-      <c r="AR8" s="6" t="n">
-        <v>64415.551</v>
       </c>
       <c r="AS8" s="6" t="n">
         <v>59061.274</v>
       </c>
       <c r="AT8" s="6" t="n">
+        <v>50102.253</v>
+      </c>
+      <c r="AU8" s="6" t="n">
         <v>54819.466</v>
       </c>
-      <c r="AU8" s="6" t="n">
+      <c r="AV8" s="6" t="n">
         <v>45876.212</v>
-      </c>
-      <c r="AV8" s="6" t="n">
-        <v>50102.253</v>
       </c>
       <c r="AW8" s="6" t="n">
         <v>55836.958</v>
       </c>
       <c r="AX8" s="6" t="n">
+        <v>54335.487</v>
+      </c>
+      <c r="AY8" s="6" t="n">
         <v>54088.301</v>
       </c>
-      <c r="AY8" s="6" t="n">
+      <c r="AZ8" s="6" t="n">
         <v>57634.527</v>
-      </c>
-      <c r="AZ8" s="6" t="n">
-        <v>54335.487</v>
       </c>
       <c r="BA8" s="6" t="n">
         <v>55617.591</v>
       </c>
       <c r="BB8" s="6" t="n">
+        <v>59428.426</v>
+      </c>
+      <c r="BC8" s="6" t="n">
         <v>62762.044</v>
       </c>
-      <c r="BC8" s="6" t="n">
+      <c r="BD8" s="6" t="n">
         <v>63300.884</v>
-      </c>
-      <c r="BD8" s="6" t="n">
-        <v>59428.426</v>
       </c>
       <c r="BE8" s="6" t="n">
         <v>79682.626</v>
@@ -1344,37 +1344,37 @@
         <v>87497.90399999999</v>
       </c>
       <c r="BI8" s="6" t="n">
+        <v>78098.594</v>
+      </c>
+      <c r="BJ8" s="6" t="n">
         <v>84448.107</v>
       </c>
-      <c r="BJ8" s="6" t="n">
+      <c r="BK8" s="6" t="n">
         <v>79148.70299999999</v>
-      </c>
-      <c r="BK8" s="6" t="n">
-        <v>78098.594</v>
       </c>
       <c r="BL8" s="6" t="n">
         <v>49400.567</v>
       </c>
       <c r="BM8" s="6" t="n">
+        <v>59891.183</v>
+      </c>
+      <c r="BN8" s="6" t="n">
         <v>98298.209</v>
       </c>
-      <c r="BN8" s="6" t="n">
+      <c r="BO8" s="6" t="n">
         <v>110576.221</v>
-      </c>
-      <c r="BO8" s="6" t="n">
-        <v>59891.183</v>
       </c>
       <c r="BP8" s="6" t="n">
         <v>140546.692</v>
       </c>
       <c r="BQ8" s="6" t="n">
+        <v>155953.202</v>
+      </c>
+      <c r="BR8" s="6" t="n">
         <v>154768.75</v>
       </c>
-      <c r="BR8" s="6" t="n">
+      <c r="BS8" s="6" t="n">
         <v>145317.961</v>
-      </c>
-      <c r="BS8" s="6" t="n">
-        <v>155953.202</v>
       </c>
       <c r="BT8" s="6" t="n">
         <v>155230.857</v>
@@ -1471,85 +1471,85 @@
         <v>34426.947</v>
       </c>
       <c r="AD9" s="8" t="n">
+        <v>33831.449</v>
+      </c>
+      <c r="AE9" s="8" t="n">
         <v>46418.011</v>
       </c>
-      <c r="AE9" s="8" t="n">
+      <c r="AF9" s="8" t="n">
         <v>45968.105</v>
-      </c>
-      <c r="AF9" s="8" t="n">
-        <v>33831.449</v>
       </c>
       <c r="AG9" s="8" t="n">
         <v>35147.715</v>
       </c>
       <c r="AH9" s="8" t="n">
+        <v>35627.957</v>
+      </c>
+      <c r="AI9" s="8" t="n">
         <v>42117.186</v>
       </c>
-      <c r="AI9" s="8" t="n">
+      <c r="AJ9" s="8" t="n">
         <v>43985.406</v>
-      </c>
-      <c r="AJ9" s="8" t="n">
-        <v>35627.957</v>
       </c>
       <c r="AK9" s="8" t="n">
         <v>49489.572</v>
       </c>
       <c r="AL9" s="8" t="n">
+        <v>52926.39</v>
+      </c>
+      <c r="AM9" s="8" t="n">
         <v>54967.381</v>
       </c>
-      <c r="AM9" s="8" t="n">
+      <c r="AN9" s="8" t="n">
         <v>57607.177</v>
-      </c>
-      <c r="AN9" s="8" t="n">
-        <v>52926.39</v>
       </c>
       <c r="AO9" s="8" t="n">
         <v>57996.794</v>
       </c>
       <c r="AP9" s="8" t="n">
+        <v>69076.986</v>
+      </c>
+      <c r="AQ9" s="8" t="n">
         <v>71683.00199999999</v>
       </c>
-      <c r="AQ9" s="8" t="n">
+      <c r="AR9" s="8" t="n">
         <v>71676.539</v>
-      </c>
-      <c r="AR9" s="8" t="n">
-        <v>69076.986</v>
       </c>
       <c r="AS9" s="8" t="n">
         <v>69698.76700000001</v>
       </c>
       <c r="AT9" s="8" t="n">
+        <v>81367.955</v>
+      </c>
+      <c r="AU9" s="8" t="n">
         <v>81051.303</v>
       </c>
-      <c r="AU9" s="8" t="n">
+      <c r="AV9" s="8" t="n">
         <v>68222.935</v>
-      </c>
-      <c r="AV9" s="8" t="n">
-        <v>81367.955</v>
       </c>
       <c r="AW9" s="8" t="n">
         <v>68133.83500000001</v>
       </c>
       <c r="AX9" s="8" t="n">
+        <v>72152.588</v>
+      </c>
+      <c r="AY9" s="8" t="n">
         <v>83236.935</v>
       </c>
-      <c r="AY9" s="8" t="n">
+      <c r="AZ9" s="8" t="n">
         <v>49979.5</v>
-      </c>
-      <c r="AZ9" s="8" t="n">
-        <v>72152.588</v>
       </c>
       <c r="BA9" s="8" t="n">
         <v>59489.224</v>
       </c>
       <c r="BB9" s="8" t="n">
+        <v>62486.626</v>
+      </c>
+      <c r="BC9" s="8" t="n">
         <v>68382.798</v>
       </c>
-      <c r="BC9" s="8" t="n">
+      <c r="BD9" s="8" t="n">
         <v>73397.06299999999</v>
-      </c>
-      <c r="BD9" s="8" t="n">
-        <v>62486.626</v>
       </c>
       <c r="BE9" s="8" t="n">
         <v>74964.087</v>
@@ -1564,37 +1564,37 @@
         <v>91076.20699999999</v>
       </c>
       <c r="BI9" s="8" t="n">
+        <v>94373.541</v>
+      </c>
+      <c r="BJ9" s="8" t="n">
         <v>107079</v>
       </c>
-      <c r="BJ9" s="8" t="n">
+      <c r="BK9" s="8" t="n">
         <v>110374.642</v>
-      </c>
-      <c r="BK9" s="8" t="n">
-        <v>94373.541</v>
       </c>
       <c r="BL9" s="8" t="n">
         <v>109304.58</v>
       </c>
       <c r="BM9" s="8" t="n">
+        <v>72195.492</v>
+      </c>
+      <c r="BN9" s="8" t="n">
         <v>67802.569</v>
       </c>
-      <c r="BN9" s="8" t="n">
+      <c r="BO9" s="8" t="n">
         <v>60436.423</v>
-      </c>
-      <c r="BO9" s="8" t="n">
-        <v>72195.492</v>
       </c>
       <c r="BP9" s="8" t="n">
         <v>59470.022</v>
       </c>
       <c r="BQ9" s="8" t="n">
+        <v>51773.27</v>
+      </c>
+      <c r="BR9" s="8" t="n">
         <v>40558.146</v>
       </c>
-      <c r="BR9" s="8" t="n">
+      <c r="BS9" s="8" t="n">
         <v>48750.569</v>
-      </c>
-      <c r="BS9" s="8" t="n">
-        <v>51773.27</v>
       </c>
       <c r="BT9" s="8" t="n">
         <v>53504.071</v>
@@ -1691,85 +1691,85 @@
         <v>29402.479</v>
       </c>
       <c r="AD10" s="10" t="n">
+        <v>29224.35</v>
+      </c>
+      <c r="AE10" s="10" t="n">
         <v>29532.823</v>
       </c>
-      <c r="AE10" s="10" t="n">
+      <c r="AF10" s="10" t="n">
         <v>31037.668</v>
-      </c>
-      <c r="AF10" s="10" t="n">
-        <v>29224.35</v>
       </c>
       <c r="AG10" s="10" t="n">
         <v>25517.109</v>
       </c>
       <c r="AH10" s="10" t="n">
+        <v>23169.452</v>
+      </c>
+      <c r="AI10" s="10" t="n">
         <v>24380.027</v>
       </c>
-      <c r="AI10" s="10" t="n">
+      <c r="AJ10" s="10" t="n">
         <v>24642.771</v>
-      </c>
-      <c r="AJ10" s="10" t="n">
-        <v>23169.452</v>
       </c>
       <c r="AK10" s="10" t="n">
         <v>24115.153</v>
       </c>
       <c r="AL10" s="10" t="n">
+        <v>27287.444</v>
+      </c>
+      <c r="AM10" s="10" t="n">
         <v>28841.763</v>
       </c>
-      <c r="AM10" s="10" t="n">
+      <c r="AN10" s="10" t="n">
         <v>27267.688</v>
-      </c>
-      <c r="AN10" s="10" t="n">
-        <v>27287.444</v>
       </c>
       <c r="AO10" s="10" t="n">
         <v>25153.136</v>
       </c>
       <c r="AP10" s="10" t="n">
+        <v>25176.113</v>
+      </c>
+      <c r="AQ10" s="10" t="n">
         <v>18783.717</v>
       </c>
-      <c r="AQ10" s="10" t="n">
+      <c r="AR10" s="10" t="n">
         <v>12292.679</v>
-      </c>
-      <c r="AR10" s="10" t="n">
-        <v>25176.113</v>
       </c>
       <c r="AS10" s="10" t="n">
         <v>13296.816</v>
       </c>
       <c r="AT10" s="10" t="n">
+        <v>11596.118</v>
+      </c>
+      <c r="AU10" s="10" t="n">
         <v>11843.348</v>
       </c>
-      <c r="AU10" s="10" t="n">
+      <c r="AV10" s="10" t="n">
         <v>8734.275</v>
-      </c>
-      <c r="AV10" s="10" t="n">
-        <v>11596.118</v>
       </c>
       <c r="AW10" s="10" t="n">
         <v>14237.082</v>
       </c>
       <c r="AX10" s="10" t="n">
+        <v>16825.423</v>
+      </c>
+      <c r="AY10" s="10" t="n">
         <v>16531.545</v>
       </c>
-      <c r="AY10" s="10" t="n">
+      <c r="AZ10" s="10" t="n">
         <v>18197.965</v>
-      </c>
-      <c r="AZ10" s="10" t="n">
-        <v>16825.423</v>
       </c>
       <c r="BA10" s="10" t="n">
         <v>14979.5</v>
       </c>
       <c r="BB10" s="10" t="n">
+        <v>15170.408</v>
+      </c>
+      <c r="BC10" s="10" t="n">
         <v>15151.99</v>
       </c>
-      <c r="BC10" s="10" t="n">
+      <c r="BD10" s="10" t="n">
         <v>10361.567</v>
-      </c>
-      <c r="BD10" s="10" t="n">
-        <v>15170.408</v>
       </c>
       <c r="BE10" s="10" t="n">
         <v>21148.899</v>
@@ -1784,37 +1784,37 @@
         <v>15768.798</v>
       </c>
       <c r="BI10" s="10" t="n">
+        <v>13986.909</v>
+      </c>
+      <c r="BJ10" s="10" t="n">
         <v>16172.593</v>
       </c>
-      <c r="BJ10" s="10" t="n">
+      <c r="BK10" s="10" t="n">
         <v>11688.581</v>
-      </c>
-      <c r="BK10" s="10" t="n">
-        <v>13986.909</v>
       </c>
       <c r="BL10" s="10" t="n">
         <v>5060.425</v>
       </c>
       <c r="BM10" s="10" t="n">
+        <v>4771.426</v>
+      </c>
+      <c r="BN10" s="10" t="n">
         <v>4487.086</v>
       </c>
-      <c r="BN10" s="10" t="n">
+      <c r="BO10" s="10" t="n">
         <v>4213.647</v>
-      </c>
-      <c r="BO10" s="10" t="n">
-        <v>4771.426</v>
       </c>
       <c r="BP10" s="10" t="n">
         <v>3962.325</v>
       </c>
       <c r="BQ10" s="10" t="n">
+        <v>3809.662</v>
+      </c>
+      <c r="BR10" s="10" t="n">
         <v>3426.143</v>
       </c>
-      <c r="BR10" s="10" t="n">
+      <c r="BS10" s="10" t="n">
         <v>2993.671</v>
-      </c>
-      <c r="BS10" s="10" t="n">
-        <v>3809.662</v>
       </c>
       <c r="BT10" s="10" t="n">
         <v>2803.243</v>
@@ -1911,85 +1911,85 @@
         <v>29402.479</v>
       </c>
       <c r="AD11" s="6" t="n">
+        <v>29224.35</v>
+      </c>
+      <c r="AE11" s="6" t="n">
         <v>29532.823</v>
       </c>
-      <c r="AE11" s="6" t="n">
+      <c r="AF11" s="6" t="n">
         <v>31037.668</v>
-      </c>
-      <c r="AF11" s="6" t="n">
-        <v>29224.35</v>
       </c>
       <c r="AG11" s="6" t="n">
         <v>25517.109</v>
       </c>
       <c r="AH11" s="6" t="n">
+        <v>23169.452</v>
+      </c>
+      <c r="AI11" s="6" t="n">
         <v>24380.027</v>
       </c>
-      <c r="AI11" s="6" t="n">
+      <c r="AJ11" s="6" t="n">
         <v>24642.771</v>
-      </c>
-      <c r="AJ11" s="6" t="n">
-        <v>23169.452</v>
       </c>
       <c r="AK11" s="6" t="n">
         <v>24115.153</v>
       </c>
       <c r="AL11" s="6" t="n">
+        <v>27287.444</v>
+      </c>
+      <c r="AM11" s="6" t="n">
         <v>28841.763</v>
       </c>
-      <c r="AM11" s="6" t="n">
+      <c r="AN11" s="6" t="n">
         <v>27267.688</v>
-      </c>
-      <c r="AN11" s="6" t="n">
-        <v>27287.444</v>
       </c>
       <c r="AO11" s="6" t="n">
         <v>25153.136</v>
       </c>
       <c r="AP11" s="6" t="n">
+        <v>25176.113</v>
+      </c>
+      <c r="AQ11" s="6" t="n">
         <v>18783.717</v>
       </c>
-      <c r="AQ11" s="6" t="n">
+      <c r="AR11" s="6" t="n">
         <v>12292.679</v>
-      </c>
-      <c r="AR11" s="6" t="n">
-        <v>25176.113</v>
       </c>
       <c r="AS11" s="6" t="n">
         <v>13296.816</v>
       </c>
       <c r="AT11" s="6" t="n">
+        <v>11596.118</v>
+      </c>
+      <c r="AU11" s="6" t="n">
         <v>11843.348</v>
       </c>
-      <c r="AU11" s="6" t="n">
+      <c r="AV11" s="6" t="n">
         <v>8734.275</v>
-      </c>
-      <c r="AV11" s="6" t="n">
-        <v>11596.118</v>
       </c>
       <c r="AW11" s="6" t="n">
         <v>14237.082</v>
       </c>
       <c r="AX11" s="6" t="n">
+        <v>16825.423</v>
+      </c>
+      <c r="AY11" s="6" t="n">
         <v>16531.545</v>
       </c>
-      <c r="AY11" s="6" t="n">
+      <c r="AZ11" s="6" t="n">
         <v>18197.965</v>
-      </c>
-      <c r="AZ11" s="6" t="n">
-        <v>16825.423</v>
       </c>
       <c r="BA11" s="6" t="n">
         <v>14979.5</v>
       </c>
       <c r="BB11" s="6" t="n">
+        <v>15170.408</v>
+      </c>
+      <c r="BC11" s="6" t="n">
         <v>15151.99</v>
       </c>
-      <c r="BC11" s="6" t="n">
+      <c r="BD11" s="6" t="n">
         <v>10361.567</v>
-      </c>
-      <c r="BD11" s="6" t="n">
-        <v>15170.408</v>
       </c>
       <c r="BE11" s="6" t="n">
         <v>21148.899</v>
@@ -2004,37 +2004,37 @@
         <v>15768.798</v>
       </c>
       <c r="BI11" s="6" t="n">
+        <v>13986.909</v>
+      </c>
+      <c r="BJ11" s="6" t="n">
         <v>16172.593</v>
       </c>
-      <c r="BJ11" s="6" t="n">
+      <c r="BK11" s="6" t="n">
         <v>11688.581</v>
-      </c>
-      <c r="BK11" s="6" t="n">
-        <v>13986.909</v>
       </c>
       <c r="BL11" s="6" t="n">
         <v>5060.425</v>
       </c>
       <c r="BM11" s="6" t="n">
+        <v>4771.426</v>
+      </c>
+      <c r="BN11" s="6" t="n">
         <v>4487.086</v>
       </c>
-      <c r="BN11" s="6" t="n">
+      <c r="BO11" s="6" t="n">
         <v>4213.647</v>
-      </c>
-      <c r="BO11" s="6" t="n">
-        <v>4771.426</v>
       </c>
       <c r="BP11" s="6" t="n">
         <v>3962.325</v>
       </c>
       <c r="BQ11" s="6" t="n">
+        <v>3809.662</v>
+      </c>
+      <c r="BR11" s="6" t="n">
         <v>3426.143</v>
       </c>
-      <c r="BR11" s="6" t="n">
+      <c r="BS11" s="6" t="n">
         <v>2993.671</v>
-      </c>
-      <c r="BS11" s="6" t="n">
-        <v>3809.662</v>
       </c>
       <c r="BT11" s="6" t="n">
         <v>2803.243</v>
@@ -2053,35 +2053,35 @@
           <t>AVALES</t>
         </is>
       </c>
-      <c r="AT13" s="10" t="n">
+      <c r="AU13" s="10" t="n">
         <v>647.769</v>
       </c>
-      <c r="AU13" s="10" t="n">
+      <c r="AV13" s="10" t="n">
         <v>615.246</v>
       </c>
       <c r="AW13" s="10" t="n">
         <v>2316.352</v>
       </c>
       <c r="AX13" s="10" t="n">
+        <v>2255.795</v>
+      </c>
+      <c r="AY13" s="10" t="n">
         <v>2206.582</v>
       </c>
-      <c r="AY13" s="10" t="n">
+      <c r="AZ13" s="10" t="n">
         <v>2160.542</v>
-      </c>
-      <c r="AZ13" s="10" t="n">
-        <v>2255.795</v>
       </c>
       <c r="BA13" s="10" t="n">
         <v>1948.46</v>
       </c>
       <c r="BB13" s="10" t="n">
+        <v>1888.555</v>
+      </c>
+      <c r="BC13" s="10" t="n">
         <v>1836.706</v>
       </c>
-      <c r="BC13" s="10" t="n">
+      <c r="BD13" s="10" t="n">
         <v>1724.959</v>
-      </c>
-      <c r="BD13" s="10" t="n">
-        <v>1888.555</v>
       </c>
       <c r="BE13" s="10" t="n">
         <v>452.447</v>
@@ -2096,37 +2096,37 @@
         <v>428.573</v>
       </c>
       <c r="BI13" s="10" t="n">
+        <v>378.871</v>
+      </c>
+      <c r="BJ13" s="10" t="n">
         <v>366.125</v>
       </c>
-      <c r="BJ13" s="10" t="n">
+      <c r="BK13" s="10" t="n">
         <v>489.208</v>
-      </c>
-      <c r="BK13" s="10" t="n">
-        <v>378.871</v>
       </c>
       <c r="BL13" s="10" t="n">
         <v>469.085</v>
       </c>
       <c r="BM13" s="10" t="n">
+        <v>456.423</v>
+      </c>
+      <c r="BN13" s="10" t="n">
         <v>434.877</v>
       </c>
-      <c r="BN13" s="10" t="n">
+      <c r="BO13" s="10" t="n">
         <v>392.992</v>
-      </c>
-      <c r="BO13" s="10" t="n">
-        <v>456.423</v>
       </c>
       <c r="BP13" s="10" t="n">
         <v>398.309</v>
       </c>
       <c r="BQ13" s="10" t="n">
+        <v>416.638</v>
+      </c>
+      <c r="BR13" s="10" t="n">
         <v>434.736</v>
       </c>
-      <c r="BR13" s="10" t="n">
+      <c r="BS13" s="10" t="n">
         <v>449.098</v>
-      </c>
-      <c r="BS13" s="10" t="n">
-        <v>416.638</v>
       </c>
       <c r="BT13" s="10" t="n">
         <v>1236.577</v>
@@ -2138,35 +2138,35 @@
           <t xml:space="preserve">  Moneda Local</t>
         </is>
       </c>
-      <c r="AT14" s="6" t="n">
+      <c r="AU14" s="6" t="n">
         <v>157.944</v>
       </c>
-      <c r="AU14" s="6" t="n">
+      <c r="AV14" s="6" t="n">
         <v>93.274</v>
       </c>
       <c r="AW14" s="6" t="n">
         <v>793.271</v>
       </c>
       <c r="AX14" s="6" t="n">
+        <v>741.383</v>
+      </c>
+      <c r="AY14" s="6" t="n">
         <v>682.489</v>
       </c>
-      <c r="AY14" s="6" t="n">
+      <c r="AZ14" s="6" t="n">
         <v>635.0839999999999</v>
-      </c>
-      <c r="AZ14" s="6" t="n">
-        <v>741.383</v>
       </c>
       <c r="BA14" s="6" t="n">
         <v>578.471</v>
       </c>
       <c r="BB14" s="6" t="n">
+        <v>532.465</v>
+      </c>
+      <c r="BC14" s="6" t="n">
         <v>514.795</v>
       </c>
-      <c r="BC14" s="6" t="n">
+      <c r="BD14" s="6" t="n">
         <v>424.013</v>
-      </c>
-      <c r="BD14" s="6" t="n">
-        <v>532.465</v>
       </c>
       <c r="BE14" s="6" t="n">
         <v>69.43300000000001</v>
@@ -2181,37 +2181,37 @@
         <v>95.90600000000001</v>
       </c>
       <c r="BI14" s="6" t="n">
+        <v>81.459</v>
+      </c>
+      <c r="BJ14" s="6" t="n">
         <v>66.41500000000001</v>
       </c>
-      <c r="BJ14" s="6" t="n">
+      <c r="BK14" s="6" t="n">
         <v>48.751</v>
-      </c>
-      <c r="BK14" s="6" t="n">
-        <v>81.459</v>
       </c>
       <c r="BL14" s="6" t="n">
         <v>6.815</v>
       </c>
       <c r="BM14" s="6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="BN14" s="6" t="n">
         <v>0.013</v>
       </c>
-      <c r="BN14" s="6" t="n">
+      <c r="BO14" s="6" t="n">
         <v>0.012</v>
-      </c>
-      <c r="BO14" s="6" t="n">
-        <v>0.014</v>
       </c>
       <c r="BP14" s="6" t="n">
         <v>0.011</v>
       </c>
       <c r="BQ14" s="6" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="BR14" s="6" t="n">
         <v>0.01</v>
       </c>
-      <c r="BR14" s="6" t="n">
+      <c r="BS14" s="6" t="n">
         <v>0.008999999999999999</v>
-      </c>
-      <c r="BS14" s="6" t="n">
-        <v>0.011</v>
       </c>
       <c r="BT14" s="6" t="n">
         <v>0.008</v>
@@ -2223,35 +2223,35 @@
           <t xml:space="preserve">  Moneda Extranjera</t>
         </is>
       </c>
-      <c r="AT15" s="8" t="n">
+      <c r="AU15" s="8" t="n">
         <v>489.825</v>
       </c>
-      <c r="AU15" s="8" t="n">
+      <c r="AV15" s="8" t="n">
         <v>521.972</v>
       </c>
       <c r="AW15" s="8" t="n">
         <v>1523.081</v>
       </c>
       <c r="AX15" s="8" t="n">
+        <v>1514.412</v>
+      </c>
+      <c r="AY15" s="8" t="n">
         <v>1524.094</v>
       </c>
-      <c r="AY15" s="8" t="n">
+      <c r="AZ15" s="8" t="n">
         <v>1525.458</v>
-      </c>
-      <c r="AZ15" s="8" t="n">
-        <v>1514.412</v>
       </c>
       <c r="BA15" s="8" t="n">
         <v>1369.989</v>
       </c>
       <c r="BB15" s="8" t="n">
+        <v>1356.09</v>
+      </c>
+      <c r="BC15" s="8" t="n">
         <v>1321.91</v>
       </c>
-      <c r="BC15" s="8" t="n">
+      <c r="BD15" s="8" t="n">
         <v>1300.946</v>
-      </c>
-      <c r="BD15" s="8" t="n">
-        <v>1356.09</v>
       </c>
       <c r="BE15" s="8" t="n">
         <v>383.014</v>
@@ -2266,37 +2266,37 @@
         <v>332.667</v>
       </c>
       <c r="BI15" s="8" t="n">
+        <v>297.412</v>
+      </c>
+      <c r="BJ15" s="8" t="n">
         <v>299.71</v>
       </c>
-      <c r="BJ15" s="8" t="n">
+      <c r="BK15" s="8" t="n">
         <v>440.458</v>
-      </c>
-      <c r="BK15" s="8" t="n">
-        <v>297.412</v>
       </c>
       <c r="BL15" s="8" t="n">
         <v>462.27</v>
       </c>
       <c r="BM15" s="8" t="n">
+        <v>456.409</v>
+      </c>
+      <c r="BN15" s="8" t="n">
         <v>434.864</v>
       </c>
-      <c r="BN15" s="8" t="n">
+      <c r="BO15" s="8" t="n">
         <v>392.98</v>
-      </c>
-      <c r="BO15" s="8" t="n">
-        <v>456.409</v>
       </c>
       <c r="BP15" s="8" t="n">
         <v>398.298</v>
       </c>
       <c r="BQ15" s="8" t="n">
+        <v>416.627</v>
+      </c>
+      <c r="BR15" s="8" t="n">
         <v>434.726</v>
       </c>
-      <c r="BR15" s="8" t="n">
+      <c r="BS15" s="8" t="n">
         <v>449.089</v>
-      </c>
-      <c r="BS15" s="8" t="n">
-        <v>416.627</v>
       </c>
       <c r="BT15" s="8" t="n">
         <v>1236.569</v>
@@ -2393,85 +2393,85 @@
         <v>3826.76</v>
       </c>
       <c r="AD16" s="10" t="n">
+        <v>4420.799</v>
+      </c>
+      <c r="AE16" s="10" t="n">
         <v>4304.007</v>
       </c>
-      <c r="AE16" s="10" t="n">
+      <c r="AF16" s="10" t="n">
         <v>4270.65</v>
-      </c>
-      <c r="AF16" s="10" t="n">
-        <v>4420.799</v>
       </c>
       <c r="AG16" s="10" t="n">
         <v>3828.346</v>
       </c>
       <c r="AH16" s="10" t="n">
+        <v>3381.49</v>
+      </c>
+      <c r="AI16" s="10" t="n">
         <v>3238.222</v>
       </c>
-      <c r="AI16" s="10" t="n">
+      <c r="AJ16" s="10" t="n">
         <v>1999.728</v>
-      </c>
-      <c r="AJ16" s="10" t="n">
-        <v>3381.49</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>1373.3</v>
       </c>
       <c r="AL16" s="10" t="n">
+        <v>1403.653</v>
+      </c>
+      <c r="AM16" s="10" t="n">
         <v>1017.011</v>
       </c>
-      <c r="AM16" s="10" t="n">
+      <c r="AN16" s="10" t="n">
         <v>715.465</v>
-      </c>
-      <c r="AN16" s="10" t="n">
-        <v>1403.653</v>
       </c>
       <c r="AO16" s="10" t="n">
         <v>2818.058</v>
       </c>
       <c r="AP16" s="10" t="n">
+        <v>2580.23</v>
+      </c>
+      <c r="AQ16" s="10" t="n">
         <v>1803.795</v>
       </c>
-      <c r="AQ16" s="10" t="n">
+      <c r="AR16" s="10" t="n">
         <v>1266.254</v>
-      </c>
-      <c r="AR16" s="10" t="n">
-        <v>2580.23</v>
       </c>
       <c r="AS16" s="10" t="n">
         <v>1361.519</v>
       </c>
       <c r="AT16" s="10" t="n">
+        <v>1090.037</v>
+      </c>
+      <c r="AU16" s="10" t="n">
         <v>1094.156</v>
       </c>
-      <c r="AU16" s="10" t="n">
+      <c r="AV16" s="10" t="n">
         <v>832.389</v>
-      </c>
-      <c r="AV16" s="10" t="n">
-        <v>1090.037</v>
       </c>
       <c r="AW16" s="10" t="n">
         <v>2718.998</v>
       </c>
       <c r="AX16" s="10" t="n">
+        <v>2371.297</v>
+      </c>
+      <c r="AY16" s="10" t="n">
         <v>1720.699</v>
       </c>
-      <c r="AY16" s="10" t="n">
+      <c r="AZ16" s="10" t="n">
         <v>1622.913</v>
-      </c>
-      <c r="AZ16" s="10" t="n">
-        <v>2371.297</v>
       </c>
       <c r="BA16" s="10" t="n">
         <v>1709.605</v>
       </c>
       <c r="BB16" s="10" t="n">
+        <v>1573.87</v>
+      </c>
+      <c r="BC16" s="10" t="n">
         <v>1545.515</v>
       </c>
-      <c r="BC16" s="10" t="n">
+      <c r="BD16" s="10" t="n">
         <v>1508.065</v>
-      </c>
-      <c r="BD16" s="10" t="n">
-        <v>1573.87</v>
       </c>
       <c r="BE16" s="10" t="n">
         <v>2239.309</v>
@@ -2486,37 +2486,37 @@
         <v>2500.464</v>
       </c>
       <c r="BI16" s="10" t="n">
+        <v>2146.535</v>
+      </c>
+      <c r="BJ16" s="10" t="n">
         <v>1785.205</v>
       </c>
-      <c r="BJ16" s="10" t="n">
+      <c r="BK16" s="10" t="n">
         <v>1349.205</v>
-      </c>
-      <c r="BK16" s="10" t="n">
-        <v>2146.535</v>
       </c>
       <c r="BL16" s="10" t="n">
         <v>1017.643</v>
       </c>
       <c r="BM16" s="10" t="n">
+        <v>964.673</v>
+      </c>
+      <c r="BN16" s="10" t="n">
         <v>911.856</v>
       </c>
-      <c r="BN16" s="10" t="n">
+      <c r="BO16" s="10" t="n">
         <v>870.75</v>
-      </c>
-      <c r="BO16" s="10" t="n">
-        <v>964.673</v>
       </c>
       <c r="BP16" s="10" t="n">
         <v>812.47</v>
       </c>
       <c r="BQ16" s="10" t="n">
+        <v>789.662</v>
+      </c>
+      <c r="BR16" s="10" t="n">
         <v>730.296</v>
       </c>
-      <c r="BR16" s="10" t="n">
+      <c r="BS16" s="10" t="n">
         <v>653.532</v>
-      </c>
-      <c r="BS16" s="10" t="n">
-        <v>789.662</v>
       </c>
       <c r="BT16" s="10" t="n">
         <v>615.819</v>
@@ -2601,85 +2601,85 @@
         <v>3801.908</v>
       </c>
       <c r="AD17" s="6" t="n">
+        <v>4395.926</v>
+      </c>
+      <c r="AE17" s="6" t="n">
         <v>4266.925</v>
       </c>
-      <c r="AE17" s="6" t="n">
+      <c r="AF17" s="6" t="n">
         <v>4245.756</v>
-      </c>
-      <c r="AF17" s="6" t="n">
-        <v>4395.926</v>
       </c>
       <c r="AG17" s="6" t="n">
         <v>3803.466</v>
       </c>
       <c r="AH17" s="6" t="n">
+        <v>3356.622</v>
+      </c>
+      <c r="AI17" s="6" t="n">
         <v>3213.347</v>
       </c>
-      <c r="AI17" s="6" t="n">
+      <c r="AJ17" s="6" t="n">
         <v>1974.958</v>
-      </c>
-      <c r="AJ17" s="6" t="n">
-        <v>3356.622</v>
       </c>
       <c r="AK17" s="6" t="n">
         <v>1348.597</v>
       </c>
       <c r="AL17" s="6" t="n">
+        <v>1378.947</v>
+      </c>
+      <c r="AM17" s="6" t="n">
         <v>992.304</v>
       </c>
-      <c r="AM17" s="6" t="n">
+      <c r="AN17" s="6" t="n">
         <v>690.7569999999999</v>
-      </c>
-      <c r="AN17" s="6" t="n">
-        <v>1378.947</v>
       </c>
       <c r="AO17" s="6" t="n">
         <v>2793.351</v>
       </c>
       <c r="AP17" s="6" t="n">
+        <v>2555.524</v>
+      </c>
+      <c r="AQ17" s="6" t="n">
         <v>1779.091</v>
       </c>
-      <c r="AQ17" s="6" t="n">
+      <c r="AR17" s="6" t="n">
         <v>1253.721</v>
-      </c>
-      <c r="AR17" s="6" t="n">
-        <v>2555.524</v>
       </c>
       <c r="AS17" s="6" t="n">
         <v>1348.988</v>
       </c>
       <c r="AT17" s="6" t="n">
+        <v>1052.778</v>
+      </c>
+      <c r="AU17" s="6" t="n">
         <v>1063.231</v>
       </c>
-      <c r="AU17" s="6" t="n">
+      <c r="AV17" s="6" t="n">
         <v>783.646</v>
-      </c>
-      <c r="AV17" s="6" t="n">
-        <v>1052.778</v>
       </c>
       <c r="AW17" s="6" t="n">
         <v>2643.011</v>
       </c>
       <c r="AX17" s="6" t="n">
+        <v>2295.258</v>
+      </c>
+      <c r="AY17" s="6" t="n">
         <v>1632.735</v>
       </c>
-      <c r="AY17" s="6" t="n">
+      <c r="AZ17" s="6" t="n">
         <v>1509.895</v>
-      </c>
-      <c r="AZ17" s="6" t="n">
-        <v>2295.258</v>
       </c>
       <c r="BA17" s="6" t="n">
         <v>1604.373</v>
       </c>
       <c r="BB17" s="6" t="n">
+        <v>1467.631</v>
+      </c>
+      <c r="BC17" s="6" t="n">
         <v>1410.265</v>
       </c>
-      <c r="BC17" s="6" t="n">
+      <c r="BD17" s="6" t="n">
         <v>1367.296</v>
-      </c>
-      <c r="BD17" s="6" t="n">
-        <v>1467.631</v>
       </c>
       <c r="BE17" s="6" t="n">
         <v>2092.457</v>
@@ -2694,37 +2694,37 @@
         <v>2342.934</v>
       </c>
       <c r="BI17" s="6" t="n">
+        <v>1985.757</v>
+      </c>
+      <c r="BJ17" s="6" t="n">
         <v>1616.831</v>
       </c>
-      <c r="BJ17" s="6" t="n">
+      <c r="BK17" s="6" t="n">
         <v>1185.686</v>
-      </c>
-      <c r="BK17" s="6" t="n">
-        <v>1985.757</v>
       </c>
       <c r="BL17" s="6" t="n">
         <v>847.3</v>
       </c>
       <c r="BM17" s="6" t="n">
+        <v>798.9109999999999</v>
+      </c>
+      <c r="BN17" s="6" t="n">
         <v>751.302</v>
       </c>
-      <c r="BN17" s="6" t="n">
+      <c r="BO17" s="6" t="n">
         <v>705.519</v>
-      </c>
-      <c r="BO17" s="6" t="n">
-        <v>798.9109999999999</v>
       </c>
       <c r="BP17" s="6" t="n">
         <v>663.438</v>
       </c>
       <c r="BQ17" s="6" t="n">
+        <v>637.877</v>
+      </c>
+      <c r="BR17" s="6" t="n">
         <v>573.662</v>
       </c>
-      <c r="BR17" s="6" t="n">
+      <c r="BS17" s="6" t="n">
         <v>501.25</v>
-      </c>
-      <c r="BS17" s="6" t="n">
-        <v>637.877</v>
       </c>
       <c r="BT17" s="6" t="n">
         <v>469.366</v>
@@ -2821,85 +2821,85 @@
         <v>24.851</v>
       </c>
       <c r="AD18" s="8" t="n">
+        <v>24.873</v>
+      </c>
+      <c r="AE18" s="8" t="n">
         <v>37.082</v>
       </c>
-      <c r="AE18" s="8" t="n">
+      <c r="AF18" s="8" t="n">
         <v>24.894</v>
-      </c>
-      <c r="AF18" s="8" t="n">
-        <v>24.873</v>
       </c>
       <c r="AG18" s="8" t="n">
         <v>24.881</v>
       </c>
       <c r="AH18" s="8" t="n">
+        <v>24.868</v>
+      </c>
+      <c r="AI18" s="8" t="n">
         <v>24.875</v>
       </c>
-      <c r="AI18" s="8" t="n">
+      <c r="AJ18" s="8" t="n">
         <v>24.77</v>
-      </c>
-      <c r="AJ18" s="8" t="n">
-        <v>24.868</v>
       </c>
       <c r="AK18" s="8" t="n">
         <v>24.703</v>
       </c>
       <c r="AL18" s="8" t="n">
+        <v>24.706</v>
+      </c>
+      <c r="AM18" s="8" t="n">
         <v>24.707</v>
       </c>
-      <c r="AM18" s="8" t="n">
+      <c r="AN18" s="8" t="n">
         <v>24.708</v>
-      </c>
-      <c r="AN18" s="8" t="n">
-        <v>24.706</v>
       </c>
       <c r="AO18" s="8" t="n">
         <v>24.708</v>
       </c>
       <c r="AP18" s="8" t="n">
+        <v>24.706</v>
+      </c>
+      <c r="AQ18" s="8" t="n">
         <v>24.704</v>
       </c>
-      <c r="AQ18" s="8" t="n">
+      <c r="AR18" s="8" t="n">
         <v>12.534</v>
-      </c>
-      <c r="AR18" s="8" t="n">
-        <v>24.706</v>
       </c>
       <c r="AS18" s="8" t="n">
         <v>12.532</v>
       </c>
       <c r="AT18" s="8" t="n">
+        <v>37.259</v>
+      </c>
+      <c r="AU18" s="8" t="n">
         <v>30.925</v>
       </c>
-      <c r="AU18" s="8" t="n">
+      <c r="AV18" s="8" t="n">
         <v>48.742</v>
-      </c>
-      <c r="AV18" s="8" t="n">
-        <v>37.259</v>
       </c>
       <c r="AW18" s="8" t="n">
         <v>75.98699999999999</v>
       </c>
       <c r="AX18" s="8" t="n">
+        <v>76.039</v>
+      </c>
+      <c r="AY18" s="8" t="n">
         <v>87.96299999999999</v>
       </c>
-      <c r="AY18" s="8" t="n">
+      <c r="AZ18" s="8" t="n">
         <v>113.018</v>
-      </c>
-      <c r="AZ18" s="8" t="n">
-        <v>76.039</v>
       </c>
       <c r="BA18" s="8" t="n">
         <v>105.232</v>
       </c>
       <c r="BB18" s="8" t="n">
+        <v>106.239</v>
+      </c>
+      <c r="BC18" s="8" t="n">
         <v>135.25</v>
       </c>
-      <c r="BC18" s="8" t="n">
+      <c r="BD18" s="8" t="n">
         <v>140.768</v>
-      </c>
-      <c r="BD18" s="8" t="n">
-        <v>106.239</v>
       </c>
       <c r="BE18" s="8" t="n">
         <v>146.851</v>
@@ -2914,37 +2914,37 @@
         <v>157.53</v>
       </c>
       <c r="BI18" s="8" t="n">
+        <v>160.778</v>
+      </c>
+      <c r="BJ18" s="8" t="n">
         <v>168.374</v>
       </c>
-      <c r="BJ18" s="8" t="n">
+      <c r="BK18" s="8" t="n">
         <v>163.519</v>
-      </c>
-      <c r="BK18" s="8" t="n">
-        <v>160.778</v>
       </c>
       <c r="BL18" s="8" t="n">
         <v>170.342</v>
       </c>
       <c r="BM18" s="8" t="n">
+        <v>165.762</v>
+      </c>
+      <c r="BN18" s="8" t="n">
         <v>160.553</v>
       </c>
-      <c r="BN18" s="8" t="n">
+      <c r="BO18" s="8" t="n">
         <v>165.231</v>
-      </c>
-      <c r="BO18" s="8" t="n">
-        <v>165.762</v>
       </c>
       <c r="BP18" s="8" t="n">
         <v>149.031</v>
       </c>
       <c r="BQ18" s="8" t="n">
+        <v>151.785</v>
+      </c>
+      <c r="BR18" s="8" t="n">
         <v>156.635</v>
       </c>
-      <c r="BR18" s="8" t="n">
+      <c r="BS18" s="8" t="n">
         <v>152.282</v>
-      </c>
-      <c r="BS18" s="8" t="n">
-        <v>151.785</v>
       </c>
       <c r="BT18" s="8" t="n">
         <v>146.453</v>
@@ -2960,49 +2960,49 @@
         <v>0.311</v>
       </c>
       <c r="AP19" s="10" t="n">
-        <v>0.346</v>
+        <v>0.311</v>
       </c>
       <c r="AQ19" s="10" t="n">
         <v>0.346</v>
       </c>
       <c r="AR19" s="10" t="n">
-        <v>0.311</v>
+        <v>0.346</v>
       </c>
       <c r="AS19" s="10" t="n">
         <v>0.354</v>
       </c>
       <c r="AT19" s="10" t="n">
-        <v>0.338</v>
+        <v>0.354</v>
       </c>
       <c r="AU19" s="10" t="n">
         <v>0.338</v>
       </c>
       <c r="AV19" s="10" t="n">
-        <v>0.354</v>
+        <v>0.338</v>
       </c>
       <c r="AW19" s="10" t="n">
         <v>0.31</v>
       </c>
       <c r="AX19" s="10" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="AY19" s="10" t="n">
         <v>0.309</v>
       </c>
       <c r="AZ19" s="10" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="BA19" s="10" t="n">
         <v>0.309</v>
       </c>
       <c r="BB19" s="10" t="n">
-        <v>0.9</v>
+        <v>0.211</v>
       </c>
       <c r="BC19" s="10" t="n">
         <v>0.9</v>
       </c>
       <c r="BD19" s="10" t="n">
-        <v>0.211</v>
+        <v>0.9</v>
       </c>
       <c r="BE19" s="10" t="n">
         <v>6.457</v>
@@ -3017,37 +3017,37 @@
         <v>24.652</v>
       </c>
       <c r="BI19" s="10" t="n">
+        <v>82.837</v>
+      </c>
+      <c r="BJ19" s="10" t="n">
         <v>87.09099999999999</v>
       </c>
-      <c r="BJ19" s="10" t="n">
+      <c r="BK19" s="10" t="n">
         <v>90.652</v>
-      </c>
-      <c r="BK19" s="10" t="n">
-        <v>82.837</v>
       </c>
       <c r="BL19" s="10" t="n">
         <v>92.206</v>
       </c>
       <c r="BM19" s="10" t="n">
+        <v>104.641</v>
+      </c>
+      <c r="BN19" s="10" t="n">
         <v>107.801</v>
       </c>
-      <c r="BN19" s="10" t="n">
+      <c r="BO19" s="10" t="n">
         <v>107.025</v>
-      </c>
-      <c r="BO19" s="10" t="n">
-        <v>104.641</v>
       </c>
       <c r="BP19" s="10" t="n">
         <v>131.72</v>
       </c>
       <c r="BQ19" s="10" t="n">
+        <v>123.148</v>
+      </c>
+      <c r="BR19" s="10" t="n">
         <v>136.432</v>
       </c>
-      <c r="BR19" s="10" t="n">
+      <c r="BS19" s="10" t="n">
         <v>135.05</v>
-      </c>
-      <c r="BS19" s="10" t="n">
-        <v>123.148</v>
       </c>
       <c r="BT19" s="10" t="n">
         <v>148.395</v>
@@ -3070,49 +3070,49 @@
         <v>0.311</v>
       </c>
       <c r="AP21" s="8" t="n">
-        <v>0.346</v>
+        <v>0.311</v>
       </c>
       <c r="AQ21" s="8" t="n">
         <v>0.346</v>
       </c>
       <c r="AR21" s="8" t="n">
-        <v>0.311</v>
+        <v>0.346</v>
       </c>
       <c r="AS21" s="8" t="n">
         <v>0.354</v>
       </c>
       <c r="AT21" s="8" t="n">
-        <v>0.338</v>
+        <v>0.354</v>
       </c>
       <c r="AU21" s="8" t="n">
         <v>0.338</v>
       </c>
       <c r="AV21" s="8" t="n">
-        <v>0.354</v>
+        <v>0.338</v>
       </c>
       <c r="AW21" s="8" t="n">
         <v>0.31</v>
       </c>
       <c r="AX21" s="8" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="AY21" s="8" t="n">
         <v>0.309</v>
       </c>
       <c r="AZ21" s="8" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="BA21" s="8" t="n">
         <v>0.309</v>
       </c>
       <c r="BB21" s="8" t="n">
-        <v>0.9</v>
+        <v>0.211</v>
       </c>
       <c r="BC21" s="8" t="n">
         <v>0.9</v>
       </c>
       <c r="BD21" s="8" t="n">
-        <v>0.211</v>
+        <v>0.9</v>
       </c>
       <c r="BE21" s="8" t="n">
         <v>6.457</v>
@@ -3127,37 +3127,37 @@
         <v>24.652</v>
       </c>
       <c r="BI21" s="8" t="n">
+        <v>82.837</v>
+      </c>
+      <c r="BJ21" s="8" t="n">
         <v>87.09099999999999</v>
       </c>
-      <c r="BJ21" s="8" t="n">
+      <c r="BK21" s="8" t="n">
         <v>90.652</v>
-      </c>
-      <c r="BK21" s="8" t="n">
-        <v>82.837</v>
       </c>
       <c r="BL21" s="8" t="n">
         <v>92.206</v>
       </c>
       <c r="BM21" s="8" t="n">
+        <v>104.641</v>
+      </c>
+      <c r="BN21" s="8" t="n">
         <v>107.801</v>
       </c>
-      <c r="BN21" s="8" t="n">
+      <c r="BO21" s="8" t="n">
         <v>107.025</v>
-      </c>
-      <c r="BO21" s="8" t="n">
-        <v>104.641</v>
       </c>
       <c r="BP21" s="8" t="n">
         <v>131.72</v>
       </c>
       <c r="BQ21" s="8" t="n">
+        <v>123.148</v>
+      </c>
+      <c r="BR21" s="8" t="n">
         <v>136.432</v>
       </c>
-      <c r="BR21" s="8" t="n">
+      <c r="BS21" s="8" t="n">
         <v>135.05</v>
-      </c>
-      <c r="BS21" s="8" t="n">
-        <v>123.148</v>
       </c>
       <c r="BT21" s="8" t="n">
         <v>148.395</v>
@@ -3254,52 +3254,52 @@
         <v>5.342</v>
       </c>
       <c r="AD22" s="10" t="n">
-        <v>2.672</v>
+        <v>5.342</v>
       </c>
       <c r="AE22" s="10" t="n">
         <v>2.672</v>
       </c>
       <c r="AF22" s="10" t="n">
-        <v>5.342</v>
-      </c>
-      <c r="AQ22" s="10" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="AR22" s="10" t="n">
         <v>2.869</v>
       </c>
       <c r="AS22" s="10" t="n">
         <v>4.551</v>
       </c>
       <c r="AT22" s="10" t="n">
+        <v>9.544</v>
+      </c>
+      <c r="AU22" s="10" t="n">
         <v>9.877000000000001</v>
       </c>
-      <c r="AU22" s="10" t="n">
+      <c r="AV22" s="10" t="n">
         <v>14.27</v>
-      </c>
-      <c r="AV22" s="10" t="n">
-        <v>9.544</v>
       </c>
       <c r="AW22" s="10" t="n">
         <v>14.487</v>
       </c>
       <c r="AX22" s="10" t="n">
+        <v>17.975</v>
+      </c>
+      <c r="AY22" s="10" t="n">
         <v>17.996</v>
       </c>
-      <c r="AY22" s="10" t="n">
+      <c r="AZ22" s="10" t="n">
         <v>22.364</v>
-      </c>
-      <c r="AZ22" s="10" t="n">
-        <v>17.975</v>
       </c>
       <c r="BA22" s="10" t="n">
         <v>22.626</v>
       </c>
       <c r="BB22" s="10" t="n">
+        <v>22.148</v>
+      </c>
+      <c r="BC22" s="10" t="n">
         <v>22.38</v>
       </c>
-      <c r="BC22" s="10" t="n">
+      <c r="BD22" s="10" t="n">
         <v>22.312</v>
-      </c>
-      <c r="BD22" s="10" t="n">
-        <v>22.148</v>
       </c>
       <c r="BE22" s="10" t="n">
         <v>24.003</v>
@@ -3314,37 +3314,37 @@
         <v>41.053</v>
       </c>
       <c r="BI22" s="10" t="n">
+        <v>47.301</v>
+      </c>
+      <c r="BJ22" s="10" t="n">
         <v>47.703</v>
       </c>
-      <c r="BJ22" s="10" t="n">
+      <c r="BK22" s="10" t="n">
         <v>49.29</v>
-      </c>
-      <c r="BK22" s="10" t="n">
-        <v>47.301</v>
       </c>
       <c r="BL22" s="10" t="n">
         <v>49.955</v>
       </c>
       <c r="BM22" s="10" t="n">
+        <v>50.136</v>
+      </c>
+      <c r="BN22" s="10" t="n">
         <v>52.124</v>
       </c>
-      <c r="BN22" s="10" t="n">
+      <c r="BO22" s="10" t="n">
         <v>54.746</v>
-      </c>
-      <c r="BO22" s="10" t="n">
-        <v>50.136</v>
       </c>
       <c r="BP22" s="10" t="n">
         <v>58.323</v>
       </c>
       <c r="BQ22" s="10" t="n">
+        <v>57.197</v>
+      </c>
+      <c r="BR22" s="10" t="n">
         <v>58.908</v>
       </c>
-      <c r="BR22" s="10" t="n">
+      <c r="BS22" s="10" t="n">
         <v>58.067</v>
-      </c>
-      <c r="BS22" s="10" t="n">
-        <v>57.197</v>
       </c>
       <c r="BT22" s="10" t="n">
         <v>58.591</v>
@@ -3448,52 +3448,52 @@
         <v>5.342</v>
       </c>
       <c r="AD24" s="8" t="n">
-        <v>2.672</v>
+        <v>5.342</v>
       </c>
       <c r="AE24" s="8" t="n">
         <v>2.672</v>
       </c>
       <c r="AF24" s="8" t="n">
-        <v>5.342</v>
-      </c>
-      <c r="AQ24" s="8" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="AR24" s="8" t="n">
         <v>2.869</v>
       </c>
       <c r="AS24" s="8" t="n">
         <v>4.551</v>
       </c>
       <c r="AT24" s="8" t="n">
+        <v>9.544</v>
+      </c>
+      <c r="AU24" s="8" t="n">
         <v>9.877000000000001</v>
       </c>
-      <c r="AU24" s="8" t="n">
+      <c r="AV24" s="8" t="n">
         <v>14.27</v>
-      </c>
-      <c r="AV24" s="8" t="n">
-        <v>9.544</v>
       </c>
       <c r="AW24" s="8" t="n">
         <v>14.487</v>
       </c>
       <c r="AX24" s="8" t="n">
+        <v>17.975</v>
+      </c>
+      <c r="AY24" s="8" t="n">
         <v>17.996</v>
       </c>
-      <c r="AY24" s="8" t="n">
+      <c r="AZ24" s="8" t="n">
         <v>22.364</v>
-      </c>
-      <c r="AZ24" s="8" t="n">
-        <v>17.975</v>
       </c>
       <c r="BA24" s="8" t="n">
         <v>22.626</v>
       </c>
       <c r="BB24" s="8" t="n">
+        <v>22.148</v>
+      </c>
+      <c r="BC24" s="8" t="n">
         <v>22.38</v>
       </c>
-      <c r="BC24" s="8" t="n">
+      <c r="BD24" s="8" t="n">
         <v>22.312</v>
-      </c>
-      <c r="BD24" s="8" t="n">
-        <v>22.148</v>
       </c>
       <c r="BE24" s="8" t="n">
         <v>24.003</v>
@@ -3508,37 +3508,37 @@
         <v>41.053</v>
       </c>
       <c r="BI24" s="8" t="n">
+        <v>47.301</v>
+      </c>
+      <c r="BJ24" s="8" t="n">
         <v>47.703</v>
       </c>
-      <c r="BJ24" s="8" t="n">
+      <c r="BK24" s="8" t="n">
         <v>49.29</v>
-      </c>
-      <c r="BK24" s="8" t="n">
-        <v>47.301</v>
       </c>
       <c r="BL24" s="8" t="n">
         <v>49.955</v>
       </c>
       <c r="BM24" s="8" t="n">
+        <v>50.136</v>
+      </c>
+      <c r="BN24" s="8" t="n">
         <v>52.124</v>
       </c>
-      <c r="BN24" s="8" t="n">
+      <c r="BO24" s="8" t="n">
         <v>54.746</v>
-      </c>
-      <c r="BO24" s="8" t="n">
-        <v>50.136</v>
       </c>
       <c r="BP24" s="8" t="n">
         <v>58.323</v>
       </c>
       <c r="BQ24" s="8" t="n">
+        <v>57.197</v>
+      </c>
+      <c r="BR24" s="8" t="n">
         <v>58.908</v>
       </c>
-      <c r="BR24" s="8" t="n">
+      <c r="BS24" s="8" t="n">
         <v>58.067</v>
-      </c>
-      <c r="BS24" s="8" t="n">
-        <v>57.197</v>
       </c>
       <c r="BT24" s="8" t="n">
         <v>58.591</v>
@@ -3635,85 +3635,85 @@
         <v>2388.417</v>
       </c>
       <c r="AD25" s="10" t="n">
+        <v>2378.848</v>
+      </c>
+      <c r="AE25" s="10" t="n">
         <v>2449.762</v>
       </c>
-      <c r="AE25" s="10" t="n">
+      <c r="AF25" s="10" t="n">
         <v>2458.025</v>
-      </c>
-      <c r="AF25" s="10" t="n">
-        <v>2378.848</v>
       </c>
       <c r="AG25" s="10" t="n">
         <v>2533.486</v>
       </c>
       <c r="AH25" s="10" t="n">
+        <v>2534.5</v>
+      </c>
+      <c r="AI25" s="10" t="n">
         <v>2541.45</v>
       </c>
-      <c r="AI25" s="10" t="n">
+      <c r="AJ25" s="10" t="n">
         <v>2499.723</v>
-      </c>
-      <c r="AJ25" s="10" t="n">
-        <v>2534.5</v>
       </c>
       <c r="AK25" s="10" t="n">
         <v>2507.675</v>
       </c>
       <c r="AL25" s="10" t="n">
+        <v>2419.165</v>
+      </c>
+      <c r="AM25" s="10" t="n">
         <v>2425.252</v>
       </c>
-      <c r="AM25" s="10" t="n">
+      <c r="AN25" s="10" t="n">
         <v>2411.904</v>
-      </c>
-      <c r="AN25" s="10" t="n">
-        <v>2419.165</v>
       </c>
       <c r="AO25" s="10" t="n">
         <v>2455.049</v>
       </c>
       <c r="AP25" s="10" t="n">
+        <v>2449.466</v>
+      </c>
+      <c r="AQ25" s="10" t="n">
         <v>2461.07</v>
       </c>
-      <c r="AQ25" s="10" t="n">
+      <c r="AR25" s="10" t="n">
         <v>2503.412</v>
-      </c>
-      <c r="AR25" s="10" t="n">
-        <v>2449.466</v>
       </c>
       <c r="AS25" s="10" t="n">
         <v>2519.063</v>
       </c>
       <c r="AT25" s="10" t="n">
+        <v>2546.585</v>
+      </c>
+      <c r="AU25" s="10" t="n">
         <v>2596.897</v>
       </c>
-      <c r="AU25" s="10" t="n">
+      <c r="AV25" s="10" t="n">
         <v>2543.693</v>
-      </c>
-      <c r="AV25" s="10" t="n">
-        <v>2546.585</v>
       </c>
       <c r="AW25" s="10" t="n">
         <v>2486.753</v>
       </c>
       <c r="AX25" s="10" t="n">
+        <v>2422.603</v>
+      </c>
+      <c r="AY25" s="10" t="n">
         <v>2406.224</v>
       </c>
-      <c r="AY25" s="10" t="n">
+      <c r="AZ25" s="10" t="n">
         <v>2276.961</v>
-      </c>
-      <c r="AZ25" s="10" t="n">
-        <v>2422.603</v>
       </c>
       <c r="BA25" s="10" t="n">
         <v>2256.816</v>
       </c>
       <c r="BB25" s="10" t="n">
+        <v>2223.883</v>
+      </c>
+      <c r="BC25" s="10" t="n">
         <v>2219.731</v>
       </c>
-      <c r="BC25" s="10" t="n">
+      <c r="BD25" s="10" t="n">
         <v>2222.355</v>
-      </c>
-      <c r="BD25" s="10" t="n">
-        <v>2223.883</v>
       </c>
       <c r="BE25" s="10" t="n">
         <v>2285.051</v>
@@ -3728,37 +3728,37 @@
         <v>3369.166</v>
       </c>
       <c r="BI25" s="10" t="n">
+        <v>3430.28</v>
+      </c>
+      <c r="BJ25" s="10" t="n">
         <v>3564.454</v>
       </c>
-      <c r="BJ25" s="10" t="n">
+      <c r="BK25" s="10" t="n">
         <v>3806.945</v>
-      </c>
-      <c r="BK25" s="10" t="n">
-        <v>3430.28</v>
       </c>
       <c r="BL25" s="10" t="n">
         <v>3890.438</v>
       </c>
       <c r="BM25" s="10" t="n">
+        <v>4008.972</v>
+      </c>
+      <c r="BN25" s="10" t="n">
         <v>4021.307</v>
       </c>
-      <c r="BN25" s="10" t="n">
+      <c r="BO25" s="10" t="n">
         <v>4246.817</v>
-      </c>
-      <c r="BO25" s="10" t="n">
-        <v>4008.972</v>
       </c>
       <c r="BP25" s="10" t="n">
         <v>4346.865</v>
       </c>
       <c r="BQ25" s="10" t="n">
+        <v>4275.09</v>
+      </c>
+      <c r="BR25" s="10" t="n">
         <v>4319.425</v>
       </c>
-      <c r="BR25" s="10" t="n">
+      <c r="BS25" s="10" t="n">
         <v>4467.732</v>
-      </c>
-      <c r="BS25" s="10" t="n">
-        <v>4275.09</v>
       </c>
       <c r="BT25" s="10" t="n">
         <v>4437.868</v>
@@ -3862,85 +3862,85 @@
         <v>2388.417</v>
       </c>
       <c r="AD27" s="8" t="n">
+        <v>2378.848</v>
+      </c>
+      <c r="AE27" s="8" t="n">
         <v>2449.762</v>
       </c>
-      <c r="AE27" s="8" t="n">
+      <c r="AF27" s="8" t="n">
         <v>2458.025</v>
-      </c>
-      <c r="AF27" s="8" t="n">
-        <v>2378.848</v>
       </c>
       <c r="AG27" s="8" t="n">
         <v>2533.486</v>
       </c>
       <c r="AH27" s="8" t="n">
+        <v>2534.5</v>
+      </c>
+      <c r="AI27" s="8" t="n">
         <v>2541.45</v>
       </c>
-      <c r="AI27" s="8" t="n">
+      <c r="AJ27" s="8" t="n">
         <v>2499.723</v>
-      </c>
-      <c r="AJ27" s="8" t="n">
-        <v>2534.5</v>
       </c>
       <c r="AK27" s="8" t="n">
         <v>2507.675</v>
       </c>
       <c r="AL27" s="8" t="n">
+        <v>2419.165</v>
+      </c>
+      <c r="AM27" s="8" t="n">
         <v>2425.252</v>
       </c>
-      <c r="AM27" s="8" t="n">
+      <c r="AN27" s="8" t="n">
         <v>2411.904</v>
-      </c>
-      <c r="AN27" s="8" t="n">
-        <v>2419.165</v>
       </c>
       <c r="AO27" s="8" t="n">
         <v>2455.049</v>
       </c>
       <c r="AP27" s="8" t="n">
+        <v>2449.466</v>
+      </c>
+      <c r="AQ27" s="8" t="n">
         <v>2461.07</v>
       </c>
-      <c r="AQ27" s="8" t="n">
+      <c r="AR27" s="8" t="n">
         <v>2503.412</v>
-      </c>
-      <c r="AR27" s="8" t="n">
-        <v>2449.466</v>
       </c>
       <c r="AS27" s="8" t="n">
         <v>2519.063</v>
       </c>
       <c r="AT27" s="8" t="n">
+        <v>2546.585</v>
+      </c>
+      <c r="AU27" s="8" t="n">
         <v>2596.897</v>
       </c>
-      <c r="AU27" s="8" t="n">
+      <c r="AV27" s="8" t="n">
         <v>2543.693</v>
-      </c>
-      <c r="AV27" s="8" t="n">
-        <v>2546.585</v>
       </c>
       <c r="AW27" s="8" t="n">
         <v>2486.753</v>
       </c>
       <c r="AX27" s="8" t="n">
+        <v>2422.603</v>
+      </c>
+      <c r="AY27" s="8" t="n">
         <v>2406.224</v>
       </c>
-      <c r="AY27" s="8" t="n">
+      <c r="AZ27" s="8" t="n">
         <v>2276.961</v>
-      </c>
-      <c r="AZ27" s="8" t="n">
-        <v>2422.603</v>
       </c>
       <c r="BA27" s="8" t="n">
         <v>2256.816</v>
       </c>
       <c r="BB27" s="8" t="n">
+        <v>2223.883</v>
+      </c>
+      <c r="BC27" s="8" t="n">
         <v>2219.731</v>
       </c>
-      <c r="BC27" s="8" t="n">
+      <c r="BD27" s="8" t="n">
         <v>2222.355</v>
-      </c>
-      <c r="BD27" s="8" t="n">
-        <v>2223.883</v>
       </c>
       <c r="BE27" s="8" t="n">
         <v>2285.051</v>
@@ -3955,37 +3955,37 @@
         <v>3369.166</v>
       </c>
       <c r="BI27" s="8" t="n">
+        <v>3430.28</v>
+      </c>
+      <c r="BJ27" s="8" t="n">
         <v>3564.454</v>
       </c>
-      <c r="BJ27" s="8" t="n">
+      <c r="BK27" s="8" t="n">
         <v>3806.945</v>
-      </c>
-      <c r="BK27" s="8" t="n">
-        <v>3430.28</v>
       </c>
       <c r="BL27" s="8" t="n">
         <v>3890.438</v>
       </c>
       <c r="BM27" s="8" t="n">
+        <v>4008.972</v>
+      </c>
+      <c r="BN27" s="8" t="n">
         <v>4021.307</v>
       </c>
-      <c r="BN27" s="8" t="n">
+      <c r="BO27" s="8" t="n">
         <v>4246.817</v>
-      </c>
-      <c r="BO27" s="8" t="n">
-        <v>4008.972</v>
       </c>
       <c r="BP27" s="8" t="n">
         <v>4346.865</v>
       </c>
       <c r="BQ27" s="8" t="n">
+        <v>4275.09</v>
+      </c>
+      <c r="BR27" s="8" t="n">
         <v>4319.425</v>
       </c>
-      <c r="BR27" s="8" t="n">
+      <c r="BS27" s="8" t="n">
         <v>4467.732</v>
-      </c>
-      <c r="BS27" s="8" t="n">
-        <v>4275.09</v>
       </c>
       <c r="BT27" s="8" t="n">
         <v>4437.868</v>
@@ -4082,85 +4082,85 @@
         <v>393.01</v>
       </c>
       <c r="AD28" s="10" t="n">
+        <v>413.619</v>
+      </c>
+      <c r="AE28" s="10" t="n">
         <v>389.251</v>
       </c>
-      <c r="AE28" s="10" t="n">
+      <c r="AF28" s="10" t="n">
         <v>393.881</v>
-      </c>
-      <c r="AF28" s="10" t="n">
-        <v>413.619</v>
       </c>
       <c r="AG28" s="10" t="n">
         <v>396.422</v>
       </c>
       <c r="AH28" s="10" t="n">
+        <v>398.119</v>
+      </c>
+      <c r="AI28" s="10" t="n">
         <v>372.361</v>
       </c>
-      <c r="AI28" s="10" t="n">
+      <c r="AJ28" s="10" t="n">
         <v>375.985</v>
-      </c>
-      <c r="AJ28" s="10" t="n">
-        <v>398.119</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>347.206</v>
       </c>
       <c r="AL28" s="10" t="n">
+        <v>390.971</v>
+      </c>
+      <c r="AM28" s="10" t="n">
         <v>403.52</v>
       </c>
-      <c r="AM28" s="10" t="n">
+      <c r="AN28" s="10" t="n">
         <v>476.121</v>
-      </c>
-      <c r="AN28" s="10" t="n">
-        <v>390.971</v>
       </c>
       <c r="AO28" s="10" t="n">
         <v>562.251</v>
       </c>
       <c r="AP28" s="10" t="n">
+        <v>660.189</v>
+      </c>
+      <c r="AQ28" s="10" t="n">
         <v>684.2140000000001</v>
       </c>
-      <c r="AQ28" s="10" t="n">
+      <c r="AR28" s="10" t="n">
         <v>834.925</v>
-      </c>
-      <c r="AR28" s="10" t="n">
-        <v>660.189</v>
       </c>
       <c r="AS28" s="10" t="n">
         <v>932.4</v>
       </c>
       <c r="AT28" s="10" t="n">
+        <v>975.737</v>
+      </c>
+      <c r="AU28" s="10" t="n">
         <v>972.151</v>
       </c>
-      <c r="AU28" s="10" t="n">
+      <c r="AV28" s="10" t="n">
         <v>1028.042</v>
-      </c>
-      <c r="AV28" s="10" t="n">
-        <v>975.737</v>
       </c>
       <c r="AW28" s="10" t="n">
         <v>987.336</v>
       </c>
       <c r="AX28" s="10" t="n">
+        <v>1005.335</v>
+      </c>
+      <c r="AY28" s="10" t="n">
         <v>966.896</v>
       </c>
-      <c r="AY28" s="10" t="n">
+      <c r="AZ28" s="10" t="n">
         <v>957.261</v>
-      </c>
-      <c r="AZ28" s="10" t="n">
-        <v>1005.335</v>
       </c>
       <c r="BA28" s="10" t="n">
         <v>930.145</v>
       </c>
       <c r="BB28" s="10" t="n">
+        <v>910.802</v>
+      </c>
+      <c r="BC28" s="10" t="n">
         <v>880.783</v>
       </c>
-      <c r="BC28" s="10" t="n">
+      <c r="BD28" s="10" t="n">
         <v>865.679</v>
-      </c>
-      <c r="BD28" s="10" t="n">
-        <v>910.802</v>
       </c>
       <c r="BE28" s="10" t="n">
         <v>928.873</v>
@@ -4175,37 +4175,37 @@
         <v>1211.05</v>
       </c>
       <c r="BI28" s="10" t="n">
+        <v>1332.695</v>
+      </c>
+      <c r="BJ28" s="10" t="n">
         <v>1289.813</v>
       </c>
-      <c r="BJ28" s="10" t="n">
+      <c r="BK28" s="10" t="n">
         <v>1271.603</v>
-      </c>
-      <c r="BK28" s="10" t="n">
-        <v>1332.695</v>
       </c>
       <c r="BL28" s="10" t="n">
         <v>1338.442</v>
       </c>
       <c r="BM28" s="10" t="n">
+        <v>1315.455</v>
+      </c>
+      <c r="BN28" s="10" t="n">
         <v>1301.426</v>
       </c>
-      <c r="BN28" s="10" t="n">
+      <c r="BO28" s="10" t="n">
         <v>1279.989</v>
-      </c>
-      <c r="BO28" s="10" t="n">
-        <v>1315.455</v>
       </c>
       <c r="BP28" s="10" t="n">
         <v>1248.338</v>
       </c>
       <c r="BQ28" s="10" t="n">
+        <v>1228.133</v>
+      </c>
+      <c r="BR28" s="10" t="n">
         <v>1187.271</v>
       </c>
-      <c r="BR28" s="10" t="n">
+      <c r="BS28" s="10" t="n">
         <v>1169.869</v>
-      </c>
-      <c r="BS28" s="10" t="n">
-        <v>1228.133</v>
       </c>
       <c r="BT28" s="10" t="n">
         <v>1235.152</v>
@@ -4309,85 +4309,85 @@
         <v>393.01</v>
       </c>
       <c r="AD30" s="8" t="n">
+        <v>413.619</v>
+      </c>
+      <c r="AE30" s="8" t="n">
         <v>389.251</v>
       </c>
-      <c r="AE30" s="8" t="n">
+      <c r="AF30" s="8" t="n">
         <v>393.881</v>
-      </c>
-      <c r="AF30" s="8" t="n">
-        <v>413.619</v>
       </c>
       <c r="AG30" s="8" t="n">
         <v>396.422</v>
       </c>
       <c r="AH30" s="8" t="n">
+        <v>398.119</v>
+      </c>
+      <c r="AI30" s="8" t="n">
         <v>372.361</v>
       </c>
-      <c r="AI30" s="8" t="n">
+      <c r="AJ30" s="8" t="n">
         <v>375.985</v>
-      </c>
-      <c r="AJ30" s="8" t="n">
-        <v>398.119</v>
       </c>
       <c r="AK30" s="8" t="n">
         <v>347.206</v>
       </c>
       <c r="AL30" s="8" t="n">
+        <v>390.971</v>
+      </c>
+      <c r="AM30" s="8" t="n">
         <v>403.52</v>
       </c>
-      <c r="AM30" s="8" t="n">
+      <c r="AN30" s="8" t="n">
         <v>476.121</v>
-      </c>
-      <c r="AN30" s="8" t="n">
-        <v>390.971</v>
       </c>
       <c r="AO30" s="8" t="n">
         <v>562.251</v>
       </c>
       <c r="AP30" s="8" t="n">
+        <v>660.189</v>
+      </c>
+      <c r="AQ30" s="8" t="n">
         <v>684.2140000000001</v>
       </c>
-      <c r="AQ30" s="8" t="n">
+      <c r="AR30" s="8" t="n">
         <v>834.925</v>
-      </c>
-      <c r="AR30" s="8" t="n">
-        <v>660.189</v>
       </c>
       <c r="AS30" s="8" t="n">
         <v>932.4</v>
       </c>
       <c r="AT30" s="8" t="n">
+        <v>975.737</v>
+      </c>
+      <c r="AU30" s="8" t="n">
         <v>972.151</v>
       </c>
-      <c r="AU30" s="8" t="n">
+      <c r="AV30" s="8" t="n">
         <v>1028.042</v>
-      </c>
-      <c r="AV30" s="8" t="n">
-        <v>975.737</v>
       </c>
       <c r="AW30" s="8" t="n">
         <v>987.336</v>
       </c>
       <c r="AX30" s="8" t="n">
+        <v>1005.335</v>
+      </c>
+      <c r="AY30" s="8" t="n">
         <v>966.896</v>
       </c>
-      <c r="AY30" s="8" t="n">
+      <c r="AZ30" s="8" t="n">
         <v>957.261</v>
-      </c>
-      <c r="AZ30" s="8" t="n">
-        <v>1005.335</v>
       </c>
       <c r="BA30" s="8" t="n">
         <v>930.145</v>
       </c>
       <c r="BB30" s="8" t="n">
+        <v>910.802</v>
+      </c>
+      <c r="BC30" s="8" t="n">
         <v>880.783</v>
       </c>
-      <c r="BC30" s="8" t="n">
+      <c r="BD30" s="8" t="n">
         <v>865.679</v>
-      </c>
-      <c r="BD30" s="8" t="n">
-        <v>910.802</v>
       </c>
       <c r="BE30" s="8" t="n">
         <v>928.873</v>
@@ -4402,37 +4402,37 @@
         <v>1211.05</v>
       </c>
       <c r="BI30" s="8" t="n">
+        <v>1332.695</v>
+      </c>
+      <c r="BJ30" s="8" t="n">
         <v>1289.813</v>
       </c>
-      <c r="BJ30" s="8" t="n">
+      <c r="BK30" s="8" t="n">
         <v>1271.603</v>
-      </c>
-      <c r="BK30" s="8" t="n">
-        <v>1332.695</v>
       </c>
       <c r="BL30" s="8" t="n">
         <v>1338.442</v>
       </c>
       <c r="BM30" s="8" t="n">
+        <v>1315.455</v>
+      </c>
+      <c r="BN30" s="8" t="n">
         <v>1301.426</v>
       </c>
-      <c r="BN30" s="8" t="n">
+      <c r="BO30" s="8" t="n">
         <v>1279.989</v>
-      </c>
-      <c r="BO30" s="8" t="n">
-        <v>1315.455</v>
       </c>
       <c r="BP30" s="8" t="n">
         <v>1248.338</v>
       </c>
       <c r="BQ30" s="8" t="n">
+        <v>1228.133</v>
+      </c>
+      <c r="BR30" s="8" t="n">
         <v>1187.271</v>
       </c>
-      <c r="BR30" s="8" t="n">
+      <c r="BS30" s="8" t="n">
         <v>1169.869</v>
-      </c>
-      <c r="BS30" s="8" t="n">
-        <v>1228.133</v>
       </c>
       <c r="BT30" s="8" t="n">
         <v>1235.152</v>
@@ -4529,85 +4529,85 @@
         <v>1649.103</v>
       </c>
       <c r="AD31" s="10" t="n">
+        <v>1629.66</v>
+      </c>
+      <c r="AE31" s="10" t="n">
         <v>1598.492</v>
       </c>
-      <c r="AE31" s="10" t="n">
+      <c r="AF31" s="10" t="n">
         <v>1583.087</v>
-      </c>
-      <c r="AF31" s="10" t="n">
-        <v>1629.66</v>
       </c>
       <c r="AG31" s="10" t="n">
         <v>1563.333</v>
       </c>
       <c r="AH31" s="10" t="n">
+        <v>1571.751</v>
+      </c>
+      <c r="AI31" s="10" t="n">
         <v>1561.696</v>
       </c>
-      <c r="AI31" s="10" t="n">
+      <c r="AJ31" s="10" t="n">
         <v>1548.818</v>
-      </c>
-      <c r="AJ31" s="10" t="n">
-        <v>1571.751</v>
       </c>
       <c r="AK31" s="10" t="n">
         <v>1548.749</v>
       </c>
       <c r="AL31" s="10" t="n">
+        <v>1555.523</v>
+      </c>
+      <c r="AM31" s="10" t="n">
         <v>1539.892</v>
       </c>
-      <c r="AM31" s="10" t="n">
+      <c r="AN31" s="10" t="n">
         <v>1518.33</v>
-      </c>
-      <c r="AN31" s="10" t="n">
-        <v>1555.523</v>
       </c>
       <c r="AO31" s="10" t="n">
         <v>1496.516</v>
       </c>
       <c r="AP31" s="10" t="n">
+        <v>1477.385</v>
+      </c>
+      <c r="AQ31" s="10" t="n">
         <v>1443.895</v>
       </c>
-      <c r="AQ31" s="10" t="n">
+      <c r="AR31" s="10" t="n">
         <v>1404.065</v>
-      </c>
-      <c r="AR31" s="10" t="n">
-        <v>1477.385</v>
       </c>
       <c r="AS31" s="10" t="n">
         <v>1400.459</v>
       </c>
       <c r="AT31" s="10" t="n">
+        <v>1358.018</v>
+      </c>
+      <c r="AU31" s="10" t="n">
         <v>1339.865</v>
       </c>
-      <c r="AU31" s="10" t="n">
+      <c r="AV31" s="10" t="n">
         <v>1296.104</v>
-      </c>
-      <c r="AV31" s="10" t="n">
-        <v>1358.018</v>
       </c>
       <c r="AW31" s="10" t="n">
         <v>1252.168</v>
       </c>
       <c r="AX31" s="10" t="n">
+        <v>1126.912</v>
+      </c>
+      <c r="AY31" s="10" t="n">
         <v>1057.004</v>
       </c>
-      <c r="AY31" s="10" t="n">
+      <c r="AZ31" s="10" t="n">
         <v>954.506</v>
-      </c>
-      <c r="AZ31" s="10" t="n">
-        <v>1126.912</v>
       </c>
       <c r="BA31" s="10" t="n">
         <v>909.832</v>
       </c>
       <c r="BB31" s="10" t="n">
+        <v>856.087</v>
+      </c>
+      <c r="BC31" s="10" t="n">
         <v>832.607</v>
       </c>
-      <c r="BC31" s="10" t="n">
+      <c r="BD31" s="10" t="n">
         <v>790.222</v>
-      </c>
-      <c r="BD31" s="10" t="n">
-        <v>856.087</v>
       </c>
       <c r="BE31" s="10" t="n">
         <v>827.0359999999999</v>
@@ -4622,37 +4622,37 @@
         <v>1592.911</v>
       </c>
       <c r="BI31" s="10" t="n">
+        <v>1616.242</v>
+      </c>
+      <c r="BJ31" s="10" t="n">
         <v>1725.033</v>
       </c>
-      <c r="BJ31" s="10" t="n">
+      <c r="BK31" s="10" t="n">
         <v>1805.862</v>
-      </c>
-      <c r="BK31" s="10" t="n">
-        <v>1616.242</v>
       </c>
       <c r="BL31" s="10" t="n">
         <v>1880.529</v>
       </c>
       <c r="BM31" s="10" t="n">
+        <v>1931.196</v>
+      </c>
+      <c r="BN31" s="10" t="n">
         <v>1953.64</v>
       </c>
-      <c r="BN31" s="10" t="n">
+      <c r="BO31" s="10" t="n">
         <v>1981.338</v>
-      </c>
-      <c r="BO31" s="10" t="n">
-        <v>1931.196</v>
       </c>
       <c r="BP31" s="10" t="n">
         <v>2135.428</v>
       </c>
       <c r="BQ31" s="10" t="n">
+        <v>2027.82</v>
+      </c>
+      <c r="BR31" s="10" t="n">
         <v>2202.965</v>
       </c>
-      <c r="BR31" s="10" t="n">
+      <c r="BS31" s="10" t="n">
         <v>2243.103</v>
-      </c>
-      <c r="BS31" s="10" t="n">
-        <v>2027.82</v>
       </c>
       <c r="BT31" s="10" t="n">
         <v>2328.555</v>
@@ -4756,85 +4756,85 @@
         <v>1649.103</v>
       </c>
       <c r="AD33" s="8" t="n">
+        <v>1629.66</v>
+      </c>
+      <c r="AE33" s="8" t="n">
         <v>1598.492</v>
       </c>
-      <c r="AE33" s="8" t="n">
+      <c r="AF33" s="8" t="n">
         <v>1583.087</v>
-      </c>
-      <c r="AF33" s="8" t="n">
-        <v>1629.66</v>
       </c>
       <c r="AG33" s="8" t="n">
         <v>1563.333</v>
       </c>
       <c r="AH33" s="8" t="n">
+        <v>1571.751</v>
+      </c>
+      <c r="AI33" s="8" t="n">
         <v>1561.696</v>
       </c>
-      <c r="AI33" s="8" t="n">
+      <c r="AJ33" s="8" t="n">
         <v>1548.818</v>
-      </c>
-      <c r="AJ33" s="8" t="n">
-        <v>1571.751</v>
       </c>
       <c r="AK33" s="8" t="n">
         <v>1548.749</v>
       </c>
       <c r="AL33" s="8" t="n">
+        <v>1555.523</v>
+      </c>
+      <c r="AM33" s="8" t="n">
         <v>1539.892</v>
       </c>
-      <c r="AM33" s="8" t="n">
+      <c r="AN33" s="8" t="n">
         <v>1518.33</v>
-      </c>
-      <c r="AN33" s="8" t="n">
-        <v>1555.523</v>
       </c>
       <c r="AO33" s="8" t="n">
         <v>1496.516</v>
       </c>
       <c r="AP33" s="8" t="n">
+        <v>1477.385</v>
+      </c>
+      <c r="AQ33" s="8" t="n">
         <v>1443.895</v>
       </c>
-      <c r="AQ33" s="8" t="n">
+      <c r="AR33" s="8" t="n">
         <v>1404.065</v>
-      </c>
-      <c r="AR33" s="8" t="n">
-        <v>1477.385</v>
       </c>
       <c r="AS33" s="8" t="n">
         <v>1400.459</v>
       </c>
       <c r="AT33" s="8" t="n">
+        <v>1358.018</v>
+      </c>
+      <c r="AU33" s="8" t="n">
         <v>1339.865</v>
       </c>
-      <c r="AU33" s="8" t="n">
+      <c r="AV33" s="8" t="n">
         <v>1296.104</v>
-      </c>
-      <c r="AV33" s="8" t="n">
-        <v>1358.018</v>
       </c>
       <c r="AW33" s="8" t="n">
         <v>1252.168</v>
       </c>
       <c r="AX33" s="8" t="n">
+        <v>1126.912</v>
+      </c>
+      <c r="AY33" s="8" t="n">
         <v>1057.004</v>
       </c>
-      <c r="AY33" s="8" t="n">
+      <c r="AZ33" s="8" t="n">
         <v>954.506</v>
-      </c>
-      <c r="AZ33" s="8" t="n">
-        <v>1126.912</v>
       </c>
       <c r="BA33" s="8" t="n">
         <v>909.832</v>
       </c>
       <c r="BB33" s="8" t="n">
+        <v>856.087</v>
+      </c>
+      <c r="BC33" s="8" t="n">
         <v>832.607</v>
       </c>
-      <c r="BC33" s="8" t="n">
+      <c r="BD33" s="8" t="n">
         <v>790.222</v>
-      </c>
-      <c r="BD33" s="8" t="n">
-        <v>856.087</v>
       </c>
       <c r="BE33" s="8" t="n">
         <v>827.0359999999999</v>
@@ -4849,37 +4849,37 @@
         <v>1592.911</v>
       </c>
       <c r="BI33" s="8" t="n">
+        <v>1616.242</v>
+      </c>
+      <c r="BJ33" s="8" t="n">
         <v>1725.033</v>
       </c>
-      <c r="BJ33" s="8" t="n">
+      <c r="BK33" s="8" t="n">
         <v>1805.862</v>
-      </c>
-      <c r="BK33" s="8" t="n">
-        <v>1616.242</v>
       </c>
       <c r="BL33" s="8" t="n">
         <v>1880.529</v>
       </c>
       <c r="BM33" s="8" t="n">
+        <v>1931.196</v>
+      </c>
+      <c r="BN33" s="8" t="n">
         <v>1953.64</v>
       </c>
-      <c r="BN33" s="8" t="n">
+      <c r="BO33" s="8" t="n">
         <v>1981.338</v>
-      </c>
-      <c r="BO33" s="8" t="n">
-        <v>1931.196</v>
       </c>
       <c r="BP33" s="8" t="n">
         <v>2135.428</v>
       </c>
       <c r="BQ33" s="8" t="n">
+        <v>2027.82</v>
+      </c>
+      <c r="BR33" s="8" t="n">
         <v>2202.965</v>
       </c>
-      <c r="BR33" s="8" t="n">
+      <c r="BS33" s="8" t="n">
         <v>2243.103</v>
-      </c>
-      <c r="BS33" s="8" t="n">
-        <v>2027.82</v>
       </c>
       <c r="BT33" s="8" t="n">
         <v>2328.555</v>
@@ -5003,85 +5003,85 @@
         <v>34905.995</v>
       </c>
       <c r="AD37" s="10" t="n">
+        <v>35851.974</v>
+      </c>
+      <c r="AE37" s="10" t="n">
         <v>47175.955</v>
       </c>
-      <c r="AE37" s="10" t="n">
+      <c r="AF37" s="10" t="n">
         <v>51196.389</v>
-      </c>
-      <c r="AF37" s="10" t="n">
-        <v>35851.974</v>
       </c>
       <c r="AG37" s="10" t="n">
         <v>37753.504</v>
       </c>
       <c r="AH37" s="10" t="n">
+        <v>37811.954</v>
+      </c>
+      <c r="AI37" s="10" t="n">
         <v>39845.014</v>
       </c>
-      <c r="AI37" s="10" t="n">
+      <c r="AJ37" s="10" t="n">
         <v>40164.172</v>
-      </c>
-      <c r="AJ37" s="10" t="n">
-        <v>37811.954</v>
       </c>
       <c r="AK37" s="10" t="n">
         <v>44595.632</v>
       </c>
       <c r="AL37" s="10" t="n">
+        <v>51628.365</v>
+      </c>
+      <c r="AM37" s="10" t="n">
         <v>51213.888</v>
       </c>
-      <c r="AM37" s="10" t="n">
+      <c r="AN37" s="10" t="n">
         <v>53423.532</v>
-      </c>
-      <c r="AN37" s="10" t="n">
-        <v>51628.365</v>
       </c>
       <c r="AO37" s="10" t="n">
         <v>56408.676</v>
       </c>
       <c r="AP37" s="10" t="n">
+        <v>63373.974</v>
+      </c>
+      <c r="AQ37" s="10" t="n">
         <v>71862.876</v>
       </c>
-      <c r="AQ37" s="10" t="n">
+      <c r="AR37" s="10" t="n">
         <v>66107.50999999999</v>
-      </c>
-      <c r="AR37" s="10" t="n">
-        <v>63373.974</v>
       </c>
       <c r="AS37" s="10" t="n">
         <v>72410.78200000001</v>
       </c>
       <c r="AT37" s="10" t="n">
+        <v>77986.981</v>
+      </c>
+      <c r="AU37" s="10" t="n">
         <v>80420.71799999999</v>
       </c>
-      <c r="AU37" s="10" t="n">
+      <c r="AV37" s="10" t="n">
         <v>64165.773</v>
-      </c>
-      <c r="AV37" s="10" t="n">
-        <v>77986.981</v>
       </c>
       <c r="AW37" s="10" t="n">
         <v>63538.624</v>
       </c>
       <c r="AX37" s="10" t="n">
+        <v>67722.173</v>
+      </c>
+      <c r="AY37" s="10" t="n">
         <v>74263.848</v>
       </c>
-      <c r="AY37" s="10" t="n">
+      <c r="AZ37" s="10" t="n">
         <v>44214.977</v>
-      </c>
-      <c r="AZ37" s="10" t="n">
-        <v>67722.173</v>
       </c>
       <c r="BA37" s="10" t="n">
         <v>50786.317</v>
       </c>
       <c r="BB37" s="10" t="n">
+        <v>53129.104</v>
+      </c>
+      <c r="BC37" s="10" t="n">
         <v>52407.734</v>
       </c>
-      <c r="BC37" s="10" t="n">
+      <c r="BD37" s="10" t="n">
         <v>56632.955</v>
-      </c>
-      <c r="BD37" s="10" t="n">
-        <v>53129.104</v>
       </c>
       <c r="BE37" s="10" t="n">
         <v>60166.942</v>
@@ -5096,37 +5096,37 @@
         <v>90545.04300000001</v>
       </c>
       <c r="BI37" s="10" t="n">
+        <v>108432.728</v>
+      </c>
+      <c r="BJ37" s="10" t="n">
         <v>135448.318</v>
       </c>
-      <c r="BJ37" s="10" t="n">
+      <c r="BK37" s="10" t="n">
         <v>139723.91</v>
-      </c>
-      <c r="BK37" s="10" t="n">
-        <v>108432.728</v>
       </c>
       <c r="BL37" s="10" t="n">
         <v>123788.774</v>
       </c>
       <c r="BM37" s="10" t="n">
+        <v>102760.014</v>
+      </c>
+      <c r="BN37" s="10" t="n">
         <v>121555.319</v>
       </c>
-      <c r="BN37" s="10" t="n">
+      <c r="BO37" s="10" t="n">
         <v>114184.831</v>
-      </c>
-      <c r="BO37" s="10" t="n">
-        <v>102760.014</v>
       </c>
       <c r="BP37" s="10" t="n">
         <v>147228.082</v>
       </c>
       <c r="BQ37" s="10" t="n">
+        <v>151587.225</v>
+      </c>
+      <c r="BR37" s="10" t="n">
         <v>138329.843</v>
       </c>
-      <c r="BR37" s="10" t="n">
+      <c r="BS37" s="10" t="n">
         <v>131137.071</v>
-      </c>
-      <c r="BS37" s="10" t="n">
-        <v>151587.225</v>
       </c>
       <c r="BT37" s="10" t="n">
         <v>125730.772</v>
@@ -5223,85 +5223,85 @@
         <v>11208.036</v>
       </c>
       <c r="AD38" s="6" t="n">
+        <v>12294.863</v>
+      </c>
+      <c r="AE38" s="6" t="n">
         <v>13651.657</v>
       </c>
-      <c r="AE38" s="6" t="n">
+      <c r="AF38" s="6" t="n">
         <v>16488.215</v>
-      </c>
-      <c r="AF38" s="6" t="n">
-        <v>12294.863</v>
       </c>
       <c r="AG38" s="6" t="n">
         <v>13780.263</v>
       </c>
       <c r="AH38" s="6" t="n">
+        <v>13003.56</v>
+      </c>
+      <c r="AI38" s="6" t="n">
         <v>12692.741</v>
       </c>
-      <c r="AI38" s="6" t="n">
+      <c r="AJ38" s="6" t="n">
         <v>13150.92</v>
-      </c>
-      <c r="AJ38" s="6" t="n">
-        <v>13003.56</v>
       </c>
       <c r="AK38" s="6" t="n">
         <v>15761.487</v>
       </c>
       <c r="AL38" s="6" t="n">
+        <v>21449.512</v>
+      </c>
+      <c r="AM38" s="6" t="n">
         <v>24426.833</v>
       </c>
-      <c r="AM38" s="6" t="n">
+      <c r="AN38" s="6" t="n">
         <v>25221.953</v>
-      </c>
-      <c r="AN38" s="6" t="n">
-        <v>21449.512</v>
       </c>
       <c r="AO38" s="6" t="n">
         <v>27696.172</v>
       </c>
       <c r="AP38" s="6" t="n">
+        <v>24727.377</v>
+      </c>
+      <c r="AQ38" s="6" t="n">
         <v>27539.528</v>
       </c>
-      <c r="AQ38" s="6" t="n">
+      <c r="AR38" s="6" t="n">
         <v>20028.794</v>
-      </c>
-      <c r="AR38" s="6" t="n">
-        <v>24727.377</v>
       </c>
       <c r="AS38" s="6" t="n">
         <v>28271.873</v>
       </c>
       <c r="AT38" s="6" t="n">
+        <v>22845.922</v>
+      </c>
+      <c r="AU38" s="6" t="n">
         <v>26193.283</v>
       </c>
-      <c r="AU38" s="6" t="n">
+      <c r="AV38" s="6" t="n">
         <v>23973.362</v>
-      </c>
-      <c r="AV38" s="6" t="n">
-        <v>22845.922</v>
       </c>
       <c r="AW38" s="6" t="n">
         <v>24217.011</v>
       </c>
       <c r="AX38" s="6" t="n">
+        <v>26149.903</v>
+      </c>
+      <c r="AY38" s="6" t="n">
         <v>22999.344</v>
       </c>
-      <c r="AY38" s="6" t="n">
+      <c r="AZ38" s="6" t="n">
         <v>24551.767</v>
-      </c>
-      <c r="AZ38" s="6" t="n">
-        <v>26149.903</v>
       </c>
       <c r="BA38" s="6" t="n">
         <v>27680.273</v>
       </c>
       <c r="BB38" s="6" t="n">
+        <v>31958.178</v>
+      </c>
+      <c r="BC38" s="6" t="n">
         <v>30968.937</v>
       </c>
-      <c r="BC38" s="6" t="n">
+      <c r="BD38" s="6" t="n">
         <v>31081.714</v>
-      </c>
-      <c r="BD38" s="6" t="n">
-        <v>31958.178</v>
       </c>
       <c r="BE38" s="6" t="n">
         <v>33608.127</v>
@@ -5316,37 +5316,37 @@
         <v>37256.619</v>
       </c>
       <c r="BI38" s="6" t="n">
+        <v>48025.517</v>
+      </c>
+      <c r="BJ38" s="6" t="n">
         <v>57191.617</v>
       </c>
-      <c r="BJ38" s="6" t="n">
+      <c r="BK38" s="6" t="n">
         <v>56061.979</v>
-      </c>
-      <c r="BK38" s="6" t="n">
-        <v>48025.517</v>
       </c>
       <c r="BL38" s="6" t="n">
         <v>38164.41</v>
       </c>
       <c r="BM38" s="6" t="n">
+        <v>51799.481</v>
+      </c>
+      <c r="BN38" s="6" t="n">
         <v>72995.872</v>
       </c>
-      <c r="BN38" s="6" t="n">
+      <c r="BO38" s="6" t="n">
         <v>73094.70299999999</v>
-      </c>
-      <c r="BO38" s="6" t="n">
-        <v>51799.481</v>
       </c>
       <c r="BP38" s="6" t="n">
         <v>106336.26</v>
       </c>
       <c r="BQ38" s="6" t="n">
+        <v>119134.972</v>
+      </c>
+      <c r="BR38" s="6" t="n">
         <v>120390.421</v>
       </c>
-      <c r="BR38" s="6" t="n">
+      <c r="BS38" s="6" t="n">
         <v>111522.46</v>
-      </c>
-      <c r="BS38" s="6" t="n">
-        <v>119134.972</v>
       </c>
       <c r="BT38" s="6" t="n">
         <v>105013.207</v>
@@ -5443,85 +5443,85 @@
         <v>23697.959</v>
       </c>
       <c r="AD39" s="8" t="n">
+        <v>23557.11</v>
+      </c>
+      <c r="AE39" s="8" t="n">
         <v>33524.297</v>
       </c>
-      <c r="AE39" s="8" t="n">
+      <c r="AF39" s="8" t="n">
         <v>34708.173</v>
-      </c>
-      <c r="AF39" s="8" t="n">
-        <v>23557.11</v>
       </c>
       <c r="AG39" s="8" t="n">
         <v>23973.24</v>
       </c>
       <c r="AH39" s="8" t="n">
+        <v>24808.395</v>
+      </c>
+      <c r="AI39" s="8" t="n">
         <v>27152.272</v>
       </c>
-      <c r="AI39" s="8" t="n">
+      <c r="AJ39" s="8" t="n">
         <v>27013.252</v>
-      </c>
-      <c r="AJ39" s="8" t="n">
-        <v>24808.395</v>
       </c>
       <c r="AK39" s="8" t="n">
         <v>28834.145</v>
       </c>
       <c r="AL39" s="8" t="n">
+        <v>30178.853</v>
+      </c>
+      <c r="AM39" s="8" t="n">
         <v>26787.055</v>
       </c>
-      <c r="AM39" s="8" t="n">
+      <c r="AN39" s="8" t="n">
         <v>28201.579</v>
-      </c>
-      <c r="AN39" s="8" t="n">
-        <v>30178.853</v>
       </c>
       <c r="AO39" s="8" t="n">
         <v>28712.504</v>
       </c>
       <c r="AP39" s="8" t="n">
+        <v>38646.597</v>
+      </c>
+      <c r="AQ39" s="8" t="n">
         <v>44323.347</v>
       </c>
-      <c r="AQ39" s="8" t="n">
+      <c r="AR39" s="8" t="n">
         <v>46078.715</v>
-      </c>
-      <c r="AR39" s="8" t="n">
-        <v>38646.597</v>
       </c>
       <c r="AS39" s="8" t="n">
         <v>44138.909</v>
       </c>
       <c r="AT39" s="8" t="n">
+        <v>55141.06</v>
+      </c>
+      <c r="AU39" s="8" t="n">
         <v>54227.435</v>
       </c>
-      <c r="AU39" s="8" t="n">
+      <c r="AV39" s="8" t="n">
         <v>40192.411</v>
-      </c>
-      <c r="AV39" s="8" t="n">
-        <v>55141.06</v>
       </c>
       <c r="AW39" s="8" t="n">
         <v>39321.612</v>
       </c>
       <c r="AX39" s="8" t="n">
+        <v>41572.27</v>
+      </c>
+      <c r="AY39" s="8" t="n">
         <v>51264.504</v>
       </c>
-      <c r="AY39" s="8" t="n">
+      <c r="AZ39" s="8" t="n">
         <v>19663.21</v>
-      </c>
-      <c r="AZ39" s="8" t="n">
-        <v>41572.27</v>
       </c>
       <c r="BA39" s="8" t="n">
         <v>23106.044</v>
       </c>
       <c r="BB39" s="8" t="n">
+        <v>21170.926</v>
+      </c>
+      <c r="BC39" s="8" t="n">
         <v>21438.797</v>
       </c>
-      <c r="BC39" s="8" t="n">
+      <c r="BD39" s="8" t="n">
         <v>25551.242</v>
-      </c>
-      <c r="BD39" s="8" t="n">
-        <v>21170.926</v>
       </c>
       <c r="BE39" s="8" t="n">
         <v>26558.815</v>
@@ -5536,37 +5536,37 @@
         <v>53288.424</v>
       </c>
       <c r="BI39" s="8" t="n">
+        <v>60407.212</v>
+      </c>
+      <c r="BJ39" s="8" t="n">
         <v>78256.701</v>
       </c>
-      <c r="BJ39" s="8" t="n">
+      <c r="BK39" s="8" t="n">
         <v>83661.932</v>
-      </c>
-      <c r="BK39" s="8" t="n">
-        <v>60407.212</v>
       </c>
       <c r="BL39" s="8" t="n">
         <v>85624.364</v>
       </c>
       <c r="BM39" s="8" t="n">
+        <v>50960.533</v>
+      </c>
+      <c r="BN39" s="8" t="n">
         <v>48559.447</v>
       </c>
-      <c r="BN39" s="8" t="n">
+      <c r="BO39" s="8" t="n">
         <v>41090.128</v>
-      </c>
-      <c r="BO39" s="8" t="n">
-        <v>50960.533</v>
       </c>
       <c r="BP39" s="8" t="n">
         <v>40891.822</v>
       </c>
       <c r="BQ39" s="8" t="n">
+        <v>32452.253</v>
+      </c>
+      <c r="BR39" s="8" t="n">
         <v>17939.421</v>
       </c>
-      <c r="BR39" s="8" t="n">
+      <c r="BS39" s="8" t="n">
         <v>19614.611</v>
-      </c>
-      <c r="BS39" s="8" t="n">
-        <v>32452.253</v>
       </c>
       <c r="BT39" s="8" t="n">
         <v>20717.565</v>
@@ -5663,85 +5663,85 @@
         <v>532.823</v>
       </c>
       <c r="AD40" s="10" t="n">
+        <v>552.25</v>
+      </c>
+      <c r="AE40" s="10" t="n">
         <v>577.326</v>
       </c>
-      <c r="AE40" s="10" t="n">
+      <c r="AF40" s="10" t="n">
         <v>604.033</v>
-      </c>
-      <c r="AF40" s="10" t="n">
-        <v>552.25</v>
       </c>
       <c r="AG40" s="10" t="n">
         <v>642.602</v>
       </c>
       <c r="AH40" s="10" t="n">
+        <v>662.178</v>
+      </c>
+      <c r="AI40" s="10" t="n">
         <v>694.236</v>
       </c>
-      <c r="AI40" s="10" t="n">
+      <c r="AJ40" s="10" t="n">
         <v>715.588</v>
-      </c>
-      <c r="AJ40" s="10" t="n">
-        <v>662.178</v>
       </c>
       <c r="AK40" s="10" t="n">
         <v>761.504</v>
       </c>
       <c r="AL40" s="10" t="n">
+        <v>782.641</v>
+      </c>
+      <c r="AM40" s="10" t="n">
         <v>802.02</v>
       </c>
-      <c r="AM40" s="10" t="n">
+      <c r="AN40" s="10" t="n">
         <v>831.033</v>
-      </c>
-      <c r="AN40" s="10" t="n">
-        <v>782.641</v>
       </c>
       <c r="AO40" s="10" t="n">
         <v>882.4160000000001</v>
       </c>
       <c r="AP40" s="10" t="n">
+        <v>932.376</v>
+      </c>
+      <c r="AQ40" s="10" t="n">
         <v>950.0309999999999</v>
       </c>
-      <c r="AQ40" s="10" t="n">
+      <c r="AR40" s="10" t="n">
         <v>1080.982</v>
-      </c>
-      <c r="AR40" s="10" t="n">
-        <v>932.376</v>
       </c>
       <c r="AS40" s="10" t="n">
         <v>1116.796</v>
       </c>
       <c r="AT40" s="10" t="n">
+        <v>1173.389</v>
+      </c>
+      <c r="AU40" s="10" t="n">
         <v>1193.187</v>
       </c>
-      <c r="AU40" s="10" t="n">
+      <c r="AV40" s="10" t="n">
         <v>1330.834</v>
-      </c>
-      <c r="AV40" s="10" t="n">
-        <v>1173.389</v>
       </c>
       <c r="AW40" s="10" t="n">
         <v>1311.229</v>
       </c>
       <c r="AX40" s="10" t="n">
+        <v>1335.888</v>
+      </c>
+      <c r="AY40" s="10" t="n">
         <v>1278.48</v>
       </c>
-      <c r="AY40" s="10" t="n">
+      <c r="AZ40" s="10" t="n">
         <v>1268.744</v>
-      </c>
-      <c r="AZ40" s="10" t="n">
-        <v>1335.888</v>
       </c>
       <c r="BA40" s="10" t="n">
         <v>1250.876</v>
       </c>
       <c r="BB40" s="10" t="n">
+        <v>1243.745</v>
+      </c>
+      <c r="BC40" s="10" t="n">
         <v>1218.707</v>
       </c>
-      <c r="BC40" s="10" t="n">
+      <c r="BD40" s="10" t="n">
         <v>1197.431</v>
-      </c>
-      <c r="BD40" s="10" t="n">
-        <v>1243.745</v>
       </c>
       <c r="BE40" s="10" t="n">
         <v>1210.822</v>
@@ -5756,37 +5756,37 @@
         <v>1520.572</v>
       </c>
       <c r="BI40" s="10" t="n">
+        <v>1566.554</v>
+      </c>
+      <c r="BJ40" s="10" t="n">
         <v>1612.318</v>
       </c>
-      <c r="BJ40" s="10" t="n">
+      <c r="BK40" s="10" t="n">
         <v>1661.602</v>
-      </c>
-      <c r="BK40" s="10" t="n">
-        <v>1566.554</v>
       </c>
       <c r="BL40" s="10" t="n">
         <v>2709.931</v>
       </c>
       <c r="BM40" s="10" t="n">
+        <v>1624.876</v>
+      </c>
+      <c r="BN40" s="10" t="n">
         <v>1647.86</v>
       </c>
-      <c r="BN40" s="10" t="n">
+      <c r="BO40" s="10" t="n">
         <v>1603.134</v>
-      </c>
-      <c r="BO40" s="10" t="n">
-        <v>1624.876</v>
       </c>
       <c r="BP40" s="10" t="n">
         <v>1622.169</v>
       </c>
       <c r="BQ40" s="10" t="n">
+        <v>1521.765</v>
+      </c>
+      <c r="BR40" s="10" t="n">
         <v>1509.161</v>
       </c>
-      <c r="BR40" s="10" t="n">
+      <c r="BS40" s="10" t="n">
         <v>1446.49</v>
-      </c>
-      <c r="BS40" s="10" t="n">
-        <v>1521.765</v>
       </c>
       <c r="BT40" s="10" t="n">
         <v>1474.355</v>
@@ -5890,85 +5890,85 @@
         <v>532.823</v>
       </c>
       <c r="AD42" s="8" t="n">
+        <v>552.25</v>
+      </c>
+      <c r="AE42" s="8" t="n">
         <v>577.326</v>
       </c>
-      <c r="AE42" s="8" t="n">
+      <c r="AF42" s="8" t="n">
         <v>604.033</v>
-      </c>
-      <c r="AF42" s="8" t="n">
-        <v>552.25</v>
       </c>
       <c r="AG42" s="8" t="n">
         <v>642.602</v>
       </c>
       <c r="AH42" s="8" t="n">
+        <v>662.178</v>
+      </c>
+      <c r="AI42" s="8" t="n">
         <v>694.236</v>
       </c>
-      <c r="AI42" s="8" t="n">
+      <c r="AJ42" s="8" t="n">
         <v>715.588</v>
-      </c>
-      <c r="AJ42" s="8" t="n">
-        <v>662.178</v>
       </c>
       <c r="AK42" s="8" t="n">
         <v>761.504</v>
       </c>
       <c r="AL42" s="8" t="n">
+        <v>782.641</v>
+      </c>
+      <c r="AM42" s="8" t="n">
         <v>802.02</v>
       </c>
-      <c r="AM42" s="8" t="n">
+      <c r="AN42" s="8" t="n">
         <v>831.033</v>
-      </c>
-      <c r="AN42" s="8" t="n">
-        <v>782.641</v>
       </c>
       <c r="AO42" s="8" t="n">
         <v>882.4160000000001</v>
       </c>
       <c r="AP42" s="8" t="n">
+        <v>932.376</v>
+      </c>
+      <c r="AQ42" s="8" t="n">
         <v>950.0309999999999</v>
       </c>
-      <c r="AQ42" s="8" t="n">
+      <c r="AR42" s="8" t="n">
         <v>1080.982</v>
-      </c>
-      <c r="AR42" s="8" t="n">
-        <v>932.376</v>
       </c>
       <c r="AS42" s="8" t="n">
         <v>1116.796</v>
       </c>
       <c r="AT42" s="8" t="n">
+        <v>1173.389</v>
+      </c>
+      <c r="AU42" s="8" t="n">
         <v>1193.187</v>
       </c>
-      <c r="AU42" s="8" t="n">
+      <c r="AV42" s="8" t="n">
         <v>1330.834</v>
-      </c>
-      <c r="AV42" s="8" t="n">
-        <v>1173.389</v>
       </c>
       <c r="AW42" s="8" t="n">
         <v>1311.229</v>
       </c>
       <c r="AX42" s="8" t="n">
+        <v>1335.888</v>
+      </c>
+      <c r="AY42" s="8" t="n">
         <v>1278.48</v>
       </c>
-      <c r="AY42" s="8" t="n">
+      <c r="AZ42" s="8" t="n">
         <v>1268.744</v>
-      </c>
-      <c r="AZ42" s="8" t="n">
-        <v>1335.888</v>
       </c>
       <c r="BA42" s="8" t="n">
         <v>1250.876</v>
       </c>
       <c r="BB42" s="8" t="n">
+        <v>1243.745</v>
+      </c>
+      <c r="BC42" s="8" t="n">
         <v>1218.707</v>
       </c>
-      <c r="BC42" s="8" t="n">
+      <c r="BD42" s="8" t="n">
         <v>1197.431</v>
-      </c>
-      <c r="BD42" s="8" t="n">
-        <v>1243.745</v>
       </c>
       <c r="BE42" s="8" t="n">
         <v>1210.822</v>
@@ -5983,37 +5983,37 @@
         <v>1520.572</v>
       </c>
       <c r="BI42" s="8" t="n">
+        <v>1566.554</v>
+      </c>
+      <c r="BJ42" s="8" t="n">
         <v>1612.318</v>
       </c>
-      <c r="BJ42" s="8" t="n">
+      <c r="BK42" s="8" t="n">
         <v>1661.602</v>
-      </c>
-      <c r="BK42" s="8" t="n">
-        <v>1566.554</v>
       </c>
       <c r="BL42" s="8" t="n">
         <v>2709.931</v>
       </c>
       <c r="BM42" s="8" t="n">
+        <v>1624.876</v>
+      </c>
+      <c r="BN42" s="8" t="n">
         <v>1647.86</v>
       </c>
-      <c r="BN42" s="8" t="n">
+      <c r="BO42" s="8" t="n">
         <v>1603.134</v>
-      </c>
-      <c r="BO42" s="8" t="n">
-        <v>1624.876</v>
       </c>
       <c r="BP42" s="8" t="n">
         <v>1622.169</v>
       </c>
       <c r="BQ42" s="8" t="n">
+        <v>1521.765</v>
+      </c>
+      <c r="BR42" s="8" t="n">
         <v>1509.161</v>
       </c>
-      <c r="BR42" s="8" t="n">
+      <c r="BS42" s="8" t="n">
         <v>1446.49</v>
-      </c>
-      <c r="BS42" s="8" t="n">
-        <v>1521.765</v>
       </c>
       <c r="BT42" s="8" t="n">
         <v>1474.355</v>
@@ -6032,85 +6032,85 @@
         <v>2968.788</v>
       </c>
       <c r="AD43" s="10" t="n">
+        <v>2805.204</v>
+      </c>
+      <c r="AE43" s="10" t="n">
         <v>4349.089</v>
       </c>
-      <c r="AE43" s="10" t="n">
+      <c r="AF43" s="10" t="n">
         <v>4364.484</v>
-      </c>
-      <c r="AF43" s="10" t="n">
-        <v>2805.204</v>
       </c>
       <c r="AG43" s="10" t="n">
         <v>4294.922</v>
       </c>
       <c r="AH43" s="10" t="n">
+        <v>3952.881</v>
+      </c>
+      <c r="AI43" s="10" t="n">
         <v>4500.308</v>
       </c>
-      <c r="AI43" s="10" t="n">
+      <c r="AJ43" s="10" t="n">
         <v>4548.246</v>
-      </c>
-      <c r="AJ43" s="10" t="n">
-        <v>3952.881</v>
       </c>
       <c r="AK43" s="10" t="n">
         <v>4253.937</v>
       </c>
       <c r="AL43" s="10" t="n">
+        <v>3323.505</v>
+      </c>
+      <c r="AM43" s="10" t="n">
         <v>5665.214</v>
       </c>
-      <c r="AM43" s="10" t="n">
+      <c r="AN43" s="10" t="n">
         <v>5753.368</v>
-      </c>
-      <c r="AN43" s="10" t="n">
-        <v>3323.505</v>
       </c>
       <c r="AO43" s="10" t="n">
         <v>5789.491</v>
       </c>
       <c r="AP43" s="10" t="n">
+        <v>5944.629</v>
+      </c>
+      <c r="AQ43" s="10" t="n">
         <v>3850.447</v>
       </c>
-      <c r="AQ43" s="10" t="n">
+      <c r="AR43" s="10" t="n">
         <v>3817.485</v>
-      </c>
-      <c r="AR43" s="10" t="n">
-        <v>5944.629</v>
       </c>
       <c r="AS43" s="10" t="n">
         <v>3815.392</v>
       </c>
       <c r="AT43" s="10" t="n">
+        <v>3971.336</v>
+      </c>
+      <c r="AU43" s="10" t="n">
         <v>2131.543</v>
       </c>
-      <c r="AU43" s="10" t="n">
+      <c r="AV43" s="10" t="n">
         <v>2088.264</v>
-      </c>
-      <c r="AV43" s="10" t="n">
-        <v>3971.336</v>
       </c>
       <c r="AW43" s="10" t="n">
         <v>2116.67</v>
       </c>
       <c r="AX43" s="10" t="n">
+        <v>2105.276</v>
+      </c>
+      <c r="AY43" s="10" t="n">
         <v>2314.27</v>
       </c>
-      <c r="AY43" s="10" t="n">
+      <c r="AZ43" s="10" t="n">
         <v>2410.435</v>
-      </c>
-      <c r="AZ43" s="10" t="n">
-        <v>2105.276</v>
       </c>
       <c r="BA43" s="10" t="n">
         <v>2476.048</v>
       </c>
       <c r="BB43" s="10" t="n">
+        <v>2381.958</v>
+      </c>
+      <c r="BC43" s="10" t="n">
         <v>2323.122</v>
       </c>
-      <c r="BC43" s="10" t="n">
+      <c r="BD43" s="10" t="n">
         <v>2071.109</v>
-      </c>
-      <c r="BD43" s="10" t="n">
-        <v>2381.958</v>
       </c>
       <c r="BE43" s="10" t="n">
         <v>2040.633</v>
@@ -6122,37 +6122,37 @@
         <v>812.932</v>
       </c>
       <c r="BI43" s="10" t="n">
+        <v>867.311</v>
+      </c>
+      <c r="BJ43" s="10" t="n">
         <v>857.1</v>
       </c>
-      <c r="BJ43" s="10" t="n">
+      <c r="BK43" s="10" t="n">
         <v>1061.882</v>
-      </c>
-      <c r="BK43" s="10" t="n">
-        <v>867.311</v>
       </c>
       <c r="BL43" s="10" t="n">
         <v>902.817</v>
       </c>
       <c r="BM43" s="10" t="n">
+        <v>826.351</v>
+      </c>
+      <c r="BN43" s="10" t="n">
         <v>814.397</v>
       </c>
-      <c r="BN43" s="10" t="n">
+      <c r="BO43" s="10" t="n">
         <v>798.643</v>
-      </c>
-      <c r="BO43" s="10" t="n">
-        <v>826.351</v>
       </c>
       <c r="BP43" s="10" t="n">
         <v>754.8440000000001</v>
       </c>
       <c r="BQ43" s="10" t="n">
+        <v>695.827</v>
+      </c>
+      <c r="BR43" s="10" t="n">
         <v>736.3630000000001</v>
       </c>
-      <c r="BR43" s="10" t="n">
+      <c r="BS43" s="10" t="n">
         <v>645.1609999999999</v>
-      </c>
-      <c r="BS43" s="10" t="n">
-        <v>695.827</v>
       </c>
       <c r="BT43" s="10" t="n">
         <v>639.396</v>
@@ -6178,85 +6178,85 @@
         <v>2968.788</v>
       </c>
       <c r="AD45" s="8" t="n">
+        <v>2805.204</v>
+      </c>
+      <c r="AE45" s="8" t="n">
         <v>4349.089</v>
       </c>
-      <c r="AE45" s="8" t="n">
+      <c r="AF45" s="8" t="n">
         <v>4364.484</v>
-      </c>
-      <c r="AF45" s="8" t="n">
-        <v>2805.204</v>
       </c>
       <c r="AG45" s="8" t="n">
         <v>4294.922</v>
       </c>
       <c r="AH45" s="8" t="n">
+        <v>3952.881</v>
+      </c>
+      <c r="AI45" s="8" t="n">
         <v>4500.308</v>
       </c>
-      <c r="AI45" s="8" t="n">
+      <c r="AJ45" s="8" t="n">
         <v>4548.246</v>
-      </c>
-      <c r="AJ45" s="8" t="n">
-        <v>3952.881</v>
       </c>
       <c r="AK45" s="8" t="n">
         <v>4253.937</v>
       </c>
       <c r="AL45" s="8" t="n">
+        <v>3323.505</v>
+      </c>
+      <c r="AM45" s="8" t="n">
         <v>5665.214</v>
       </c>
-      <c r="AM45" s="8" t="n">
+      <c r="AN45" s="8" t="n">
         <v>5753.368</v>
-      </c>
-      <c r="AN45" s="8" t="n">
-        <v>3323.505</v>
       </c>
       <c r="AO45" s="8" t="n">
         <v>5789.491</v>
       </c>
       <c r="AP45" s="8" t="n">
+        <v>5944.629</v>
+      </c>
+      <c r="AQ45" s="8" t="n">
         <v>3850.447</v>
       </c>
-      <c r="AQ45" s="8" t="n">
+      <c r="AR45" s="8" t="n">
         <v>3817.485</v>
-      </c>
-      <c r="AR45" s="8" t="n">
-        <v>5944.629</v>
       </c>
       <c r="AS45" s="8" t="n">
         <v>3815.392</v>
       </c>
       <c r="AT45" s="8" t="n">
+        <v>3971.336</v>
+      </c>
+      <c r="AU45" s="8" t="n">
         <v>2131.543</v>
       </c>
-      <c r="AU45" s="8" t="n">
+      <c r="AV45" s="8" t="n">
         <v>2088.264</v>
-      </c>
-      <c r="AV45" s="8" t="n">
-        <v>3971.336</v>
       </c>
       <c r="AW45" s="8" t="n">
         <v>2116.67</v>
       </c>
       <c r="AX45" s="8" t="n">
+        <v>2105.276</v>
+      </c>
+      <c r="AY45" s="8" t="n">
         <v>2314.27</v>
       </c>
-      <c r="AY45" s="8" t="n">
+      <c r="AZ45" s="8" t="n">
         <v>2410.435</v>
-      </c>
-      <c r="AZ45" s="8" t="n">
-        <v>2105.276</v>
       </c>
       <c r="BA45" s="8" t="n">
         <v>2476.048</v>
       </c>
       <c r="BB45" s="8" t="n">
+        <v>2381.958</v>
+      </c>
+      <c r="BC45" s="8" t="n">
         <v>2323.122</v>
       </c>
-      <c r="BC45" s="8" t="n">
+      <c r="BD45" s="8" t="n">
         <v>2071.109</v>
-      </c>
-      <c r="BD45" s="8" t="n">
-        <v>2381.958</v>
       </c>
       <c r="BE45" s="8" t="n">
         <v>2040.633</v>
@@ -6268,37 +6268,37 @@
         <v>812.932</v>
       </c>
       <c r="BI45" s="8" t="n">
+        <v>867.311</v>
+      </c>
+      <c r="BJ45" s="8" t="n">
         <v>857.1</v>
       </c>
-      <c r="BJ45" s="8" t="n">
+      <c r="BK45" s="8" t="n">
         <v>1061.882</v>
-      </c>
-      <c r="BK45" s="8" t="n">
-        <v>867.311</v>
       </c>
       <c r="BL45" s="8" t="n">
         <v>902.817</v>
       </c>
       <c r="BM45" s="8" t="n">
+        <v>826.351</v>
+      </c>
+      <c r="BN45" s="8" t="n">
         <v>814.397</v>
       </c>
-      <c r="BN45" s="8" t="n">
+      <c r="BO45" s="8" t="n">
         <v>798.643</v>
-      </c>
-      <c r="BO45" s="8" t="n">
-        <v>826.351</v>
       </c>
       <c r="BP45" s="8" t="n">
         <v>754.8440000000001</v>
       </c>
       <c r="BQ45" s="8" t="n">
+        <v>695.827</v>
+      </c>
+      <c r="BR45" s="8" t="n">
         <v>736.3630000000001</v>
       </c>
-      <c r="BR45" s="8" t="n">
+      <c r="BS45" s="8" t="n">
         <v>645.1609999999999</v>
-      </c>
-      <c r="BS45" s="8" t="n">
-        <v>695.827</v>
       </c>
       <c r="BT45" s="8" t="n">
         <v>639.396</v>
@@ -6749,85 +6749,85 @@
         <v>11.305</v>
       </c>
       <c r="AD52" s="10" t="n">
+        <v>11.553</v>
+      </c>
+      <c r="AE52" s="10" t="n">
         <v>11.885</v>
       </c>
-      <c r="AE52" s="10" t="n">
+      <c r="AF52" s="10" t="n">
         <v>11.904</v>
-      </c>
-      <c r="AF52" s="10" t="n">
-        <v>11.553</v>
       </c>
       <c r="AG52" s="10" t="n">
         <v>11.694</v>
       </c>
       <c r="AH52" s="10" t="n">
+        <v>12.061</v>
+      </c>
+      <c r="AI52" s="10" t="n">
         <v>11.868</v>
       </c>
-      <c r="AI52" s="10" t="n">
+      <c r="AJ52" s="10" t="n">
         <v>11.975</v>
-      </c>
-      <c r="AJ52" s="10" t="n">
-        <v>12.061</v>
       </c>
       <c r="AK52" s="10" t="n">
         <v>11.313</v>
       </c>
       <c r="AL52" s="10" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="AM52" s="10" t="n">
         <v>12.275</v>
       </c>
-      <c r="AM52" s="10" t="n">
+      <c r="AN52" s="10" t="n">
         <v>12.61</v>
-      </c>
-      <c r="AN52" s="10" t="n">
-        <v>11.675</v>
       </c>
       <c r="AO52" s="10" t="n">
         <v>12.767</v>
       </c>
       <c r="AP52" s="10" t="n">
+        <v>13.216</v>
+      </c>
+      <c r="AQ52" s="10" t="n">
         <v>12.614</v>
       </c>
-      <c r="AQ52" s="10" t="n">
+      <c r="AR52" s="10" t="n">
         <v>12.804</v>
-      </c>
-      <c r="AR52" s="10" t="n">
-        <v>13.216</v>
       </c>
       <c r="AS52" s="10" t="n">
         <v>12.828</v>
       </c>
       <c r="AT52" s="10" t="n">
+        <v>12.746</v>
+      </c>
+      <c r="AU52" s="10" t="n">
         <v>12.871</v>
       </c>
-      <c r="AU52" s="10" t="n">
+      <c r="AV52" s="10" t="n">
         <v>12.452</v>
-      </c>
-      <c r="AV52" s="10" t="n">
-        <v>12.746</v>
       </c>
       <c r="AW52" s="10" t="n">
         <v>12.948</v>
       </c>
       <c r="AX52" s="10" t="n">
+        <v>12.753</v>
+      </c>
+      <c r="AY52" s="10" t="n">
         <v>12.799</v>
       </c>
-      <c r="AY52" s="10" t="n">
+      <c r="AZ52" s="10" t="n">
         <v>13.142</v>
-      </c>
-      <c r="AZ52" s="10" t="n">
-        <v>12.753</v>
       </c>
       <c r="BA52" s="10" t="n">
         <v>13.687</v>
       </c>
       <c r="BB52" s="10" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="BC52" s="10" t="n">
         <v>17.286</v>
       </c>
-      <c r="BC52" s="10" t="n">
+      <c r="BD52" s="10" t="n">
         <v>16.694</v>
-      </c>
-      <c r="BD52" s="10" t="n">
-        <v>13.35</v>
       </c>
       <c r="BE52" s="10" t="n">
         <v>15.801</v>
@@ -6842,37 +6842,37 @@
         <v>12.409</v>
       </c>
       <c r="BI52" s="10" t="n">
+        <v>13.688</v>
+      </c>
+      <c r="BJ52" s="10" t="n">
         <v>13.729</v>
       </c>
-      <c r="BJ52" s="10" t="n">
+      <c r="BK52" s="10" t="n">
         <v>15.097</v>
-      </c>
-      <c r="BK52" s="10" t="n">
-        <v>13.688</v>
       </c>
       <c r="BL52" s="10" t="n">
         <v>14.654</v>
       </c>
       <c r="BM52" s="10" t="n">
+        <v>14.373</v>
+      </c>
+      <c r="BN52" s="10" t="n">
         <v>14.185</v>
       </c>
-      <c r="BN52" s="10" t="n">
+      <c r="BO52" s="10" t="n">
         <v>14.594</v>
-      </c>
-      <c r="BO52" s="10" t="n">
-        <v>14.373</v>
       </c>
       <c r="BP52" s="10" t="n">
         <v>12.626</v>
       </c>
       <c r="BQ52" s="10" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="BR52" s="10" t="n">
         <v>13.326</v>
       </c>
-      <c r="BR52" s="10" t="n">
+      <c r="BS52" s="10" t="n">
         <v>13.281</v>
-      </c>
-      <c r="BS52" s="10" t="n">
-        <v>13.023</v>
       </c>
       <c r="BT52" s="10" t="n">
         <v>13.046</v>
@@ -6976,85 +6976,85 @@
         <v>11.305</v>
       </c>
       <c r="AD54" s="8" t="n">
+        <v>11.553</v>
+      </c>
+      <c r="AE54" s="8" t="n">
         <v>11.885</v>
       </c>
-      <c r="AE54" s="8" t="n">
+      <c r="AF54" s="8" t="n">
         <v>11.904</v>
-      </c>
-      <c r="AF54" s="8" t="n">
-        <v>11.553</v>
       </c>
       <c r="AG54" s="8" t="n">
         <v>11.694</v>
       </c>
       <c r="AH54" s="8" t="n">
+        <v>12.061</v>
+      </c>
+      <c r="AI54" s="8" t="n">
         <v>11.868</v>
       </c>
-      <c r="AI54" s="8" t="n">
+      <c r="AJ54" s="8" t="n">
         <v>11.975</v>
-      </c>
-      <c r="AJ54" s="8" t="n">
-        <v>12.061</v>
       </c>
       <c r="AK54" s="8" t="n">
         <v>11.313</v>
       </c>
       <c r="AL54" s="8" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="AM54" s="8" t="n">
         <v>12.275</v>
       </c>
-      <c r="AM54" s="8" t="n">
+      <c r="AN54" s="8" t="n">
         <v>12.61</v>
-      </c>
-      <c r="AN54" s="8" t="n">
-        <v>11.675</v>
       </c>
       <c r="AO54" s="8" t="n">
         <v>12.767</v>
       </c>
       <c r="AP54" s="8" t="n">
+        <v>13.216</v>
+      </c>
+      <c r="AQ54" s="8" t="n">
         <v>12.614</v>
       </c>
-      <c r="AQ54" s="8" t="n">
+      <c r="AR54" s="8" t="n">
         <v>12.804</v>
-      </c>
-      <c r="AR54" s="8" t="n">
-        <v>13.216</v>
       </c>
       <c r="AS54" s="8" t="n">
         <v>12.828</v>
       </c>
       <c r="AT54" s="8" t="n">
+        <v>12.746</v>
+      </c>
+      <c r="AU54" s="8" t="n">
         <v>12.871</v>
       </c>
-      <c r="AU54" s="8" t="n">
+      <c r="AV54" s="8" t="n">
         <v>12.452</v>
-      </c>
-      <c r="AV54" s="8" t="n">
-        <v>12.746</v>
       </c>
       <c r="AW54" s="8" t="n">
         <v>12.948</v>
       </c>
       <c r="AX54" s="8" t="n">
+        <v>12.753</v>
+      </c>
+      <c r="AY54" s="8" t="n">
         <v>12.799</v>
       </c>
-      <c r="AY54" s="8" t="n">
+      <c r="AZ54" s="8" t="n">
         <v>13.142</v>
-      </c>
-      <c r="AZ54" s="8" t="n">
-        <v>12.753</v>
       </c>
       <c r="BA54" s="8" t="n">
         <v>13.687</v>
       </c>
       <c r="BB54" s="8" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="BC54" s="8" t="n">
         <v>17.286</v>
       </c>
-      <c r="BC54" s="8" t="n">
+      <c r="BD54" s="8" t="n">
         <v>16.694</v>
-      </c>
-      <c r="BD54" s="8" t="n">
-        <v>13.35</v>
       </c>
       <c r="BE54" s="8" t="n">
         <v>15.801</v>
@@ -7069,37 +7069,37 @@
         <v>12.409</v>
       </c>
       <c r="BI54" s="8" t="n">
+        <v>13.688</v>
+      </c>
+      <c r="BJ54" s="8" t="n">
         <v>13.729</v>
       </c>
-      <c r="BJ54" s="8" t="n">
+      <c r="BK54" s="8" t="n">
         <v>15.097</v>
-      </c>
-      <c r="BK54" s="8" t="n">
-        <v>13.688</v>
       </c>
       <c r="BL54" s="8" t="n">
         <v>14.654</v>
       </c>
       <c r="BM54" s="8" t="n">
+        <v>14.373</v>
+      </c>
+      <c r="BN54" s="8" t="n">
         <v>14.185</v>
       </c>
-      <c r="BN54" s="8" t="n">
+      <c r="BO54" s="8" t="n">
         <v>14.594</v>
-      </c>
-      <c r="BO54" s="8" t="n">
-        <v>14.373</v>
       </c>
       <c r="BP54" s="8" t="n">
         <v>12.626</v>
       </c>
       <c r="BQ54" s="8" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="BR54" s="8" t="n">
         <v>13.326</v>
       </c>
-      <c r="BR54" s="8" t="n">
+      <c r="BS54" s="8" t="n">
         <v>13.281</v>
-      </c>
-      <c r="BS54" s="8" t="n">
-        <v>13.023</v>
       </c>
       <c r="BT54" s="8" t="n">
         <v>13.046</v>
@@ -7111,47 +7111,47 @@
           <t>FMI</t>
         </is>
       </c>
-      <c r="AP55" s="10" t="n">
+      <c r="AQ55" s="10" t="n">
         <v>825.544</v>
       </c>
-      <c r="AQ55" s="10" t="n">
+      <c r="AR55" s="10" t="n">
         <v>891.0410000000001</v>
       </c>
       <c r="AS55" s="10" t="n">
         <v>1872.981</v>
       </c>
       <c r="AT55" s="10" t="n">
+        <v>1908.41</v>
+      </c>
+      <c r="AU55" s="10" t="n">
         <v>3134.044</v>
       </c>
-      <c r="AU55" s="10" t="n">
+      <c r="AV55" s="10" t="n">
         <v>5040.084</v>
-      </c>
-      <c r="AV55" s="10" t="n">
-        <v>1908.41</v>
       </c>
       <c r="AW55" s="10" t="n">
         <v>6897.342</v>
       </c>
       <c r="AX55" s="10" t="n">
+        <v>9616.444</v>
+      </c>
+      <c r="AY55" s="10" t="n">
         <v>13191.321</v>
       </c>
-      <c r="AY55" s="10" t="n">
+      <c r="AZ55" s="10" t="n">
         <v>18417.506</v>
-      </c>
-      <c r="AZ55" s="10" t="n">
-        <v>9616.444</v>
       </c>
       <c r="BA55" s="10" t="n">
         <v>24534.229</v>
       </c>
       <c r="BB55" s="10" t="n">
+        <v>29654.092</v>
+      </c>
+      <c r="BC55" s="10" t="n">
         <v>35363.508</v>
       </c>
-      <c r="BC55" s="10" t="n">
+      <c r="BD55" s="10" t="n">
         <v>36549.964</v>
-      </c>
-      <c r="BD55" s="10" t="n">
-        <v>29654.092</v>
       </c>
       <c r="BE55" s="10" t="n">
         <v>37826.16</v>
@@ -7166,37 +7166,37 @@
         <v>26213.968</v>
       </c>
       <c r="BI55" s="10" t="n">
+        <v>21752.236</v>
+      </c>
+      <c r="BJ55" s="10" t="n">
         <v>16266.774</v>
       </c>
-      <c r="BJ55" s="10" t="n">
+      <c r="BK55" s="10" t="n">
         <v>13563.823</v>
-      </c>
-      <c r="BK55" s="10" t="n">
-        <v>21752.236</v>
       </c>
       <c r="BL55" s="10" t="n">
         <v>10144.747</v>
       </c>
       <c r="BM55" s="10" t="n">
+        <v>8720.124</v>
+      </c>
+      <c r="BN55" s="10" t="n">
         <v>6726.601</v>
       </c>
-      <c r="BN55" s="10" t="n">
+      <c r="BO55" s="10" t="n">
         <v>6672.556</v>
-      </c>
-      <c r="BO55" s="10" t="n">
-        <v>8720.124</v>
       </c>
       <c r="BP55" s="10" t="n">
         <v>5686.654</v>
       </c>
       <c r="BQ55" s="10" t="n">
+        <v>6488.388</v>
+      </c>
+      <c r="BR55" s="10" t="n">
         <v>9329.125</v>
       </c>
-      <c r="BR55" s="10" t="n">
+      <c r="BS55" s="10" t="n">
         <v>10731.841</v>
-      </c>
-      <c r="BS55" s="10" t="n">
-        <v>6488.388</v>
       </c>
       <c r="BT55" s="10" t="n">
         <v>11622.991</v>
@@ -7215,47 +7215,47 @@
           <t xml:space="preserve">  Moneda Extranjera</t>
         </is>
       </c>
-      <c r="AP57" s="8" t="n">
+      <c r="AQ57" s="8" t="n">
         <v>825.544</v>
       </c>
-      <c r="AQ57" s="8" t="n">
+      <c r="AR57" s="8" t="n">
         <v>891.0410000000001</v>
       </c>
       <c r="AS57" s="8" t="n">
         <v>1872.981</v>
       </c>
       <c r="AT57" s="8" t="n">
+        <v>1908.41</v>
+      </c>
+      <c r="AU57" s="8" t="n">
         <v>3134.044</v>
       </c>
-      <c r="AU57" s="8" t="n">
+      <c r="AV57" s="8" t="n">
         <v>5040.084</v>
-      </c>
-      <c r="AV57" s="8" t="n">
-        <v>1908.41</v>
       </c>
       <c r="AW57" s="8" t="n">
         <v>6897.342</v>
       </c>
       <c r="AX57" s="8" t="n">
+        <v>9616.444</v>
+      </c>
+      <c r="AY57" s="8" t="n">
         <v>13191.321</v>
       </c>
-      <c r="AY57" s="8" t="n">
+      <c r="AZ57" s="8" t="n">
         <v>18417.506</v>
-      </c>
-      <c r="AZ57" s="8" t="n">
-        <v>9616.444</v>
       </c>
       <c r="BA57" s="8" t="n">
         <v>24534.229</v>
       </c>
       <c r="BB57" s="8" t="n">
+        <v>29654.092</v>
+      </c>
+      <c r="BC57" s="8" t="n">
         <v>35363.508</v>
       </c>
-      <c r="BC57" s="8" t="n">
+      <c r="BD57" s="8" t="n">
         <v>36549.964</v>
-      </c>
-      <c r="BD57" s="8" t="n">
-        <v>29654.092</v>
       </c>
       <c r="BE57" s="8" t="n">
         <v>37826.16</v>
@@ -7270,37 +7270,37 @@
         <v>26213.968</v>
       </c>
       <c r="BI57" s="8" t="n">
+        <v>21752.236</v>
+      </c>
+      <c r="BJ57" s="8" t="n">
         <v>16266.774</v>
       </c>
-      <c r="BJ57" s="8" t="n">
+      <c r="BK57" s="8" t="n">
         <v>13563.823</v>
-      </c>
-      <c r="BK57" s="8" t="n">
-        <v>21752.236</v>
       </c>
       <c r="BL57" s="8" t="n">
         <v>10144.747</v>
       </c>
       <c r="BM57" s="8" t="n">
+        <v>8720.124</v>
+      </c>
+      <c r="BN57" s="8" t="n">
         <v>6726.601</v>
       </c>
-      <c r="BN57" s="8" t="n">
+      <c r="BO57" s="8" t="n">
         <v>6672.556</v>
-      </c>
-      <c r="BO57" s="8" t="n">
-        <v>8720.124</v>
       </c>
       <c r="BP57" s="8" t="n">
         <v>5686.654</v>
       </c>
       <c r="BQ57" s="8" t="n">
+        <v>6488.388</v>
+      </c>
+      <c r="BR57" s="8" t="n">
         <v>9329.125</v>
       </c>
-      <c r="BR57" s="8" t="n">
+      <c r="BS57" s="8" t="n">
         <v>10731.841</v>
-      </c>
-      <c r="BS57" s="8" t="n">
-        <v>6488.388</v>
       </c>
       <c r="BT57" s="8" t="n">
         <v>11622.991</v>
@@ -7397,85 +7397,85 @@
         <v>24.479</v>
       </c>
       <c r="AD58" s="10" t="n">
+        <v>22.556</v>
+      </c>
+      <c r="AE58" s="10" t="n">
         <v>23.514</v>
       </c>
-      <c r="AE58" s="10" t="n">
+      <c r="AF58" s="10" t="n">
         <v>24.363</v>
-      </c>
-      <c r="AF58" s="10" t="n">
-        <v>22.556</v>
       </c>
       <c r="AG58" s="10" t="n">
         <v>26.941</v>
       </c>
       <c r="AH58" s="10" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AI58" s="10" t="n">
         <v>25.751</v>
       </c>
-      <c r="AI58" s="10" t="n">
+      <c r="AJ58" s="10" t="n">
         <v>26.359</v>
-      </c>
-      <c r="AJ58" s="10" t="n">
-        <v>25.03</v>
       </c>
       <c r="AK58" s="10" t="n">
         <v>28.156</v>
       </c>
       <c r="AL58" s="10" t="n">
+        <v>28.481</v>
+      </c>
+      <c r="AM58" s="10" t="n">
         <v>30.607</v>
       </c>
-      <c r="AM58" s="10" t="n">
+      <c r="AN58" s="10" t="n">
         <v>32.288</v>
-      </c>
-      <c r="AN58" s="10" t="n">
-        <v>28.481</v>
       </c>
       <c r="AO58" s="10" t="n">
         <v>36.519</v>
       </c>
       <c r="AP58" s="10" t="n">
+        <v>35.981</v>
+      </c>
+      <c r="AQ58" s="10" t="n">
         <v>37.255</v>
       </c>
-      <c r="AQ58" s="10" t="n">
+      <c r="AR58" s="10" t="n">
         <v>36.95</v>
-      </c>
-      <c r="AR58" s="10" t="n">
-        <v>35.981</v>
       </c>
       <c r="AS58" s="10" t="n">
         <v>45.402</v>
       </c>
       <c r="AT58" s="10" t="n">
+        <v>50.844</v>
+      </c>
+      <c r="AU58" s="10" t="n">
         <v>49.154</v>
       </c>
-      <c r="AU58" s="10" t="n">
+      <c r="AV58" s="10" t="n">
         <v>53.23</v>
-      </c>
-      <c r="AV58" s="10" t="n">
-        <v>50.844</v>
       </c>
       <c r="AW58" s="10" t="n">
         <v>58.719</v>
       </c>
       <c r="AX58" s="10" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="AY58" s="10" t="n">
         <v>70.658</v>
       </c>
-      <c r="AY58" s="10" t="n">
+      <c r="AZ58" s="10" t="n">
         <v>73.319</v>
-      </c>
-      <c r="AZ58" s="10" t="n">
-        <v>58.3</v>
       </c>
       <c r="BA58" s="10" t="n">
         <v>75.17400000000001</v>
       </c>
       <c r="BB58" s="10" t="n">
+        <v>77.904</v>
+      </c>
+      <c r="BC58" s="10" t="n">
         <v>80.407</v>
       </c>
-      <c r="BC58" s="10" t="n">
+      <c r="BD58" s="10" t="n">
         <v>85.718</v>
-      </c>
-      <c r="BD58" s="10" t="n">
-        <v>77.904</v>
       </c>
       <c r="BE58" s="10" t="n">
         <v>94.848</v>
@@ -7490,37 +7490,37 @@
         <v>173.946</v>
       </c>
       <c r="BI58" s="10" t="n">
+        <v>180.774</v>
+      </c>
+      <c r="BJ58" s="10" t="n">
         <v>188.288</v>
       </c>
-      <c r="BJ58" s="10" t="n">
+      <c r="BK58" s="10" t="n">
         <v>186.23</v>
-      </c>
-      <c r="BK58" s="10" t="n">
-        <v>180.774</v>
       </c>
       <c r="BL58" s="10" t="n">
         <v>186.077</v>
       </c>
       <c r="BM58" s="10" t="n">
+        <v>195.563</v>
+      </c>
+      <c r="BN58" s="10" t="n">
         <v>194.699</v>
       </c>
-      <c r="BN58" s="10" t="n">
+      <c r="BO58" s="10" t="n">
         <v>214.054</v>
-      </c>
-      <c r="BO58" s="10" t="n">
-        <v>195.563</v>
       </c>
       <c r="BP58" s="10" t="n">
         <v>218.05</v>
       </c>
       <c r="BQ58" s="10" t="n">
+        <v>207.226</v>
+      </c>
+      <c r="BR58" s="10" t="n">
         <v>203.109</v>
       </c>
-      <c r="BR58" s="10" t="n">
+      <c r="BS58" s="10" t="n">
         <v>199.548</v>
-      </c>
-      <c r="BS58" s="10" t="n">
-        <v>207.226</v>
       </c>
       <c r="BT58" s="10" t="n">
         <v>200.013</v>
@@ -7624,85 +7624,85 @@
         <v>24.479</v>
       </c>
       <c r="AD60" s="8" t="n">
+        <v>22.556</v>
+      </c>
+      <c r="AE60" s="8" t="n">
         <v>23.514</v>
       </c>
-      <c r="AE60" s="8" t="n">
+      <c r="AF60" s="8" t="n">
         <v>24.363</v>
-      </c>
-      <c r="AF60" s="8" t="n">
-        <v>22.556</v>
       </c>
       <c r="AG60" s="8" t="n">
         <v>26.941</v>
       </c>
       <c r="AH60" s="8" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AI60" s="8" t="n">
         <v>25.751</v>
       </c>
-      <c r="AI60" s="8" t="n">
+      <c r="AJ60" s="8" t="n">
         <v>26.359</v>
-      </c>
-      <c r="AJ60" s="8" t="n">
-        <v>25.03</v>
       </c>
       <c r="AK60" s="8" t="n">
         <v>28.156</v>
       </c>
       <c r="AL60" s="8" t="n">
+        <v>28.481</v>
+      </c>
+      <c r="AM60" s="8" t="n">
         <v>30.607</v>
       </c>
-      <c r="AM60" s="8" t="n">
+      <c r="AN60" s="8" t="n">
         <v>32.288</v>
-      </c>
-      <c r="AN60" s="8" t="n">
-        <v>28.481</v>
       </c>
       <c r="AO60" s="8" t="n">
         <v>36.519</v>
       </c>
       <c r="AP60" s="8" t="n">
+        <v>35.981</v>
+      </c>
+      <c r="AQ60" s="8" t="n">
         <v>37.255</v>
       </c>
-      <c r="AQ60" s="8" t="n">
+      <c r="AR60" s="8" t="n">
         <v>36.95</v>
-      </c>
-      <c r="AR60" s="8" t="n">
-        <v>35.981</v>
       </c>
       <c r="AS60" s="8" t="n">
         <v>45.402</v>
       </c>
       <c r="AT60" s="8" t="n">
+        <v>50.844</v>
+      </c>
+      <c r="AU60" s="8" t="n">
         <v>49.154</v>
       </c>
-      <c r="AU60" s="8" t="n">
+      <c r="AV60" s="8" t="n">
         <v>53.23</v>
-      </c>
-      <c r="AV60" s="8" t="n">
-        <v>50.844</v>
       </c>
       <c r="AW60" s="8" t="n">
         <v>58.719</v>
       </c>
       <c r="AX60" s="8" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="AY60" s="8" t="n">
         <v>70.658</v>
       </c>
-      <c r="AY60" s="8" t="n">
+      <c r="AZ60" s="8" t="n">
         <v>73.319</v>
-      </c>
-      <c r="AZ60" s="8" t="n">
-        <v>58.3</v>
       </c>
       <c r="BA60" s="8" t="n">
         <v>75.17400000000001</v>
       </c>
       <c r="BB60" s="8" t="n">
+        <v>77.904</v>
+      </c>
+      <c r="BC60" s="8" t="n">
         <v>80.407</v>
       </c>
-      <c r="BC60" s="8" t="n">
+      <c r="BD60" s="8" t="n">
         <v>85.718</v>
-      </c>
-      <c r="BD60" s="8" t="n">
-        <v>77.904</v>
       </c>
       <c r="BE60" s="8" t="n">
         <v>94.848</v>
@@ -7717,37 +7717,37 @@
         <v>173.946</v>
       </c>
       <c r="BI60" s="8" t="n">
+        <v>180.774</v>
+      </c>
+      <c r="BJ60" s="8" t="n">
         <v>188.288</v>
       </c>
-      <c r="BJ60" s="8" t="n">
+      <c r="BK60" s="8" t="n">
         <v>186.23</v>
-      </c>
-      <c r="BK60" s="8" t="n">
-        <v>180.774</v>
       </c>
       <c r="BL60" s="8" t="n">
         <v>186.077</v>
       </c>
       <c r="BM60" s="8" t="n">
+        <v>195.563</v>
+      </c>
+      <c r="BN60" s="8" t="n">
         <v>194.699</v>
       </c>
-      <c r="BN60" s="8" t="n">
+      <c r="BO60" s="8" t="n">
         <v>214.054</v>
-      </c>
-      <c r="BO60" s="8" t="n">
-        <v>195.563</v>
       </c>
       <c r="BP60" s="8" t="n">
         <v>218.05</v>
       </c>
       <c r="BQ60" s="8" t="n">
+        <v>207.226</v>
+      </c>
+      <c r="BR60" s="8" t="n">
         <v>203.109</v>
       </c>
-      <c r="BR60" s="8" t="n">
+      <c r="BS60" s="8" t="n">
         <v>199.548</v>
-      </c>
-      <c r="BS60" s="8" t="n">
-        <v>207.226</v>
       </c>
       <c r="BT60" s="8" t="n">
         <v>200.013</v>
@@ -7844,85 +7844,85 @@
         <v>9875.093000000001</v>
       </c>
       <c r="AD61" s="10" t="n">
+        <v>9473.919</v>
+      </c>
+      <c r="AE61" s="10" t="n">
         <v>9230.136</v>
       </c>
-      <c r="AE61" s="10" t="n">
+      <c r="AF61" s="10" t="n">
         <v>8023.498</v>
-      </c>
-      <c r="AF61" s="10" t="n">
-        <v>9473.919</v>
       </c>
       <c r="AG61" s="10" t="n">
         <v>8943.546</v>
       </c>
       <c r="AH61" s="10" t="n">
+        <v>7745.858</v>
+      </c>
+      <c r="AI61" s="10" t="n">
         <v>10243.582</v>
       </c>
-      <c r="AI61" s="10" t="n">
+      <c r="AJ61" s="10" t="n">
         <v>11411.557</v>
-      </c>
-      <c r="AJ61" s="10" t="n">
-        <v>7745.858</v>
       </c>
       <c r="AK61" s="10" t="n">
         <v>25935.592</v>
       </c>
       <c r="AL61" s="10" t="n">
+        <v>24521.385</v>
+      </c>
+      <c r="AM61" s="10" t="n">
         <v>27673.581</v>
       </c>
-      <c r="AM61" s="10" t="n">
+      <c r="AN61" s="10" t="n">
         <v>27762.326</v>
-      </c>
-      <c r="AN61" s="10" t="n">
-        <v>24521.385</v>
       </c>
       <c r="AO61" s="10" t="n">
         <v>31869.387</v>
       </c>
       <c r="AP61" s="10" t="n">
+        <v>29916.721</v>
+      </c>
+      <c r="AQ61" s="10" t="n">
         <v>24321.52</v>
       </c>
-      <c r="AQ61" s="10" t="n">
+      <c r="AR61" s="10" t="n">
         <v>23486.933</v>
-      </c>
-      <c r="AR61" s="10" t="n">
-        <v>29916.721</v>
       </c>
       <c r="AS61" s="10" t="n">
         <v>28037.188</v>
       </c>
       <c r="AT61" s="10" t="n">
+        <v>27902.815</v>
+      </c>
+      <c r="AU61" s="10" t="n">
         <v>29983.049</v>
       </c>
-      <c r="AU61" s="10" t="n">
+      <c r="AV61" s="10" t="n">
         <v>25937.165</v>
-      </c>
-      <c r="AV61" s="10" t="n">
-        <v>27902.815</v>
       </c>
       <c r="AW61" s="10" t="n">
         <v>24004.568</v>
       </c>
       <c r="AX61" s="10" t="n">
+        <v>18912.987</v>
+      </c>
+      <c r="AY61" s="10" t="n">
         <v>20589.159</v>
       </c>
-      <c r="AY61" s="10" t="n">
+      <c r="AZ61" s="10" t="n">
         <v>14326.279</v>
-      </c>
-      <c r="AZ61" s="10" t="n">
-        <v>18912.987</v>
       </c>
       <c r="BA61" s="10" t="n">
         <v>11555.574</v>
       </c>
       <c r="BB61" s="10" t="n">
+        <v>11951.528</v>
+      </c>
+      <c r="BC61" s="10" t="n">
         <v>16419.262</v>
       </c>
-      <c r="BC61" s="10" t="n">
+      <c r="BD61" s="10" t="n">
         <v>21817.648</v>
-      </c>
-      <c r="BD61" s="10" t="n">
-        <v>11951.528</v>
       </c>
       <c r="BE61" s="10" t="n">
         <v>23734.136</v>
@@ -7937,37 +7937,37 @@
         <v>32612.792</v>
       </c>
       <c r="BI61" s="10" t="n">
+        <v>15905.84</v>
+      </c>
+      <c r="BJ61" s="10" t="n">
         <v>11369.687</v>
       </c>
-      <c r="BJ61" s="10" t="n">
+      <c r="BK61" s="10" t="n">
         <v>12032.681</v>
-      </c>
-      <c r="BK61" s="10" t="n">
-        <v>15905.84</v>
       </c>
       <c r="BL61" s="10" t="n">
         <v>6486.231</v>
       </c>
       <c r="BM61" s="10" t="n">
+        <v>3636.31</v>
+      </c>
+      <c r="BN61" s="10" t="n">
         <v>21151.617</v>
       </c>
-      <c r="BN61" s="10" t="n">
+      <c r="BO61" s="10" t="n">
         <v>33644.848</v>
-      </c>
-      <c r="BO61" s="10" t="n">
-        <v>3636.31</v>
       </c>
       <c r="BP61" s="10" t="n">
         <v>29694.519</v>
       </c>
       <c r="BQ61" s="10" t="n">
+        <v>33744.452</v>
+      </c>
+      <c r="BR61" s="10" t="n">
         <v>31971.761</v>
       </c>
-      <c r="BR61" s="10" t="n">
+      <c r="BS61" s="10" t="n">
         <v>36809.35</v>
-      </c>
-      <c r="BS61" s="10" t="n">
-        <v>33744.452</v>
       </c>
       <c r="BT61" s="10" t="n">
         <v>55278.275</v>
@@ -8064,85 +8064,85 @@
         <v>7661.288</v>
       </c>
       <c r="AD62" s="6" t="n">
+        <v>7560.392</v>
+      </c>
+      <c r="AE62" s="6" t="n">
         <v>7675.193</v>
       </c>
-      <c r="AE62" s="6" t="n">
+      <c r="AF62" s="6" t="n">
         <v>6704.152</v>
-      </c>
-      <c r="AF62" s="6" t="n">
-        <v>7560.392</v>
       </c>
       <c r="AG62" s="6" t="n">
         <v>7691.67</v>
       </c>
       <c r="AH62" s="6" t="n">
+        <v>6534.458</v>
+      </c>
+      <c r="AI62" s="6" t="n">
         <v>5405.064</v>
       </c>
-      <c r="AI62" s="6" t="n">
+      <c r="AJ62" s="6" t="n">
         <v>4589.396</v>
-      </c>
-      <c r="AJ62" s="6" t="n">
-        <v>6534.458</v>
       </c>
       <c r="AK62" s="6" t="n">
         <v>15283.705</v>
       </c>
       <c r="AL62" s="6" t="n">
+        <v>10835.399</v>
+      </c>
+      <c r="AM62" s="6" t="n">
         <v>10926.675</v>
       </c>
-      <c r="AM62" s="6" t="n">
+      <c r="AN62" s="6" t="n">
         <v>9948.302</v>
-      </c>
-      <c r="AN62" s="6" t="n">
-        <v>10835.399</v>
       </c>
       <c r="AO62" s="6" t="n">
         <v>14427.557</v>
       </c>
       <c r="AP62" s="6" t="n">
+        <v>11614.447</v>
+      </c>
+      <c r="AQ62" s="6" t="n">
         <v>7836.097</v>
       </c>
-      <c r="AQ62" s="6" t="n">
+      <c r="AR62" s="6" t="n">
         <v>9062.347</v>
-      </c>
-      <c r="AR62" s="6" t="n">
-        <v>11614.447</v>
       </c>
       <c r="AS62" s="6" t="n">
         <v>15031.713</v>
       </c>
       <c r="AT62" s="6" t="n">
+        <v>14527.106</v>
+      </c>
+      <c r="AU62" s="6" t="n">
         <v>15457.401</v>
       </c>
-      <c r="AU62" s="6" t="n">
+      <c r="AV62" s="6" t="n">
         <v>12208.144</v>
-      </c>
-      <c r="AV62" s="6" t="n">
-        <v>14527.106</v>
       </c>
       <c r="AW62" s="6" t="n">
         <v>12564.854</v>
       </c>
       <c r="AX62" s="6" t="n">
+        <v>8248.200999999999</v>
+      </c>
+      <c r="AY62" s="6" t="n">
         <v>12168.683</v>
       </c>
-      <c r="AY62" s="6" t="n">
+      <c r="AZ62" s="6" t="n">
         <v>12667.529</v>
-      </c>
-      <c r="AZ62" s="6" t="n">
-        <v>8248.200999999999</v>
       </c>
       <c r="BA62" s="6" t="n">
         <v>9859.268</v>
       </c>
       <c r="BB62" s="6" t="n">
+        <v>10226.158</v>
+      </c>
+      <c r="BC62" s="6" t="n">
         <v>14636.297</v>
       </c>
-      <c r="BC62" s="6" t="n">
+      <c r="BD62" s="6" t="n">
         <v>19981.713</v>
-      </c>
-      <c r="BD62" s="6" t="n">
-        <v>10226.158</v>
       </c>
       <c r="BE62" s="6" t="n">
         <v>21847.182</v>
@@ -8157,37 +8157,37 @@
         <v>30918.845</v>
       </c>
       <c r="BI62" s="6" t="n">
+        <v>13920.488</v>
+      </c>
+      <c r="BJ62" s="6" t="n">
         <v>9300.42</v>
       </c>
-      <c r="BJ62" s="6" t="n">
+      <c r="BK62" s="6" t="n">
         <v>10072.539</v>
-      </c>
-      <c r="BK62" s="6" t="n">
-        <v>13920.488</v>
       </c>
       <c r="BL62" s="6" t="n">
         <v>5267.267</v>
       </c>
       <c r="BM62" s="6" t="n">
+        <v>2433.776</v>
+      </c>
+      <c r="BN62" s="6" t="n">
         <v>19956.132</v>
       </c>
-      <c r="BN62" s="6" t="n">
+      <c r="BO62" s="6" t="n">
         <v>32447.587</v>
-      </c>
-      <c r="BO62" s="6" t="n">
-        <v>2433.776</v>
       </c>
       <c r="BP62" s="6" t="n">
         <v>28497.608</v>
       </c>
       <c r="BQ62" s="6" t="n">
+        <v>32248.199</v>
+      </c>
+      <c r="BR62" s="6" t="n">
         <v>30258.846</v>
       </c>
-      <c r="BR62" s="6" t="n">
+      <c r="BS62" s="6" t="n">
         <v>30002.908</v>
-      </c>
-      <c r="BS62" s="6" t="n">
-        <v>32248.199</v>
       </c>
       <c r="BT62" s="6" t="n">
         <v>46649.728</v>
@@ -8266,85 +8266,85 @@
         <v>2213.805</v>
       </c>
       <c r="AD63" s="8" t="n">
+        <v>1913.528</v>
+      </c>
+      <c r="AE63" s="8" t="n">
         <v>1554.943</v>
       </c>
-      <c r="AE63" s="8" t="n">
+      <c r="AF63" s="8" t="n">
         <v>1319.347</v>
-      </c>
-      <c r="AF63" s="8" t="n">
-        <v>1913.528</v>
       </c>
       <c r="AG63" s="8" t="n">
         <v>1251.876</v>
       </c>
       <c r="AH63" s="8" t="n">
+        <v>1211.4</v>
+      </c>
+      <c r="AI63" s="8" t="n">
         <v>4838.517</v>
       </c>
-      <c r="AI63" s="8" t="n">
+      <c r="AJ63" s="8" t="n">
         <v>6822.161</v>
-      </c>
-      <c r="AJ63" s="8" t="n">
-        <v>1211.4</v>
       </c>
       <c r="AK63" s="8" t="n">
         <v>10651.887</v>
       </c>
       <c r="AL63" s="8" t="n">
+        <v>13685.986</v>
+      </c>
+      <c r="AM63" s="8" t="n">
         <v>16746.906</v>
       </c>
-      <c r="AM63" s="8" t="n">
+      <c r="AN63" s="8" t="n">
         <v>17814.024</v>
-      </c>
-      <c r="AN63" s="8" t="n">
-        <v>13685.986</v>
       </c>
       <c r="AO63" s="8" t="n">
         <v>17441.831</v>
       </c>
       <c r="AP63" s="8" t="n">
+        <v>18302.274</v>
+      </c>
+      <c r="AQ63" s="8" t="n">
         <v>16485.423</v>
       </c>
-      <c r="AQ63" s="8" t="n">
+      <c r="AR63" s="8" t="n">
         <v>14424.586</v>
-      </c>
-      <c r="AR63" s="8" t="n">
-        <v>18302.274</v>
       </c>
       <c r="AS63" s="8" t="n">
         <v>13005.475</v>
       </c>
       <c r="AT63" s="8" t="n">
+        <v>13375.709</v>
+      </c>
+      <c r="AU63" s="8" t="n">
         <v>14525.648</v>
       </c>
-      <c r="AU63" s="8" t="n">
+      <c r="AV63" s="8" t="n">
         <v>13729.021</v>
-      </c>
-      <c r="AV63" s="8" t="n">
-        <v>13375.709</v>
       </c>
       <c r="AW63" s="8" t="n">
         <v>11439.714</v>
       </c>
       <c r="AX63" s="8" t="n">
+        <v>10664.785</v>
+      </c>
+      <c r="AY63" s="8" t="n">
         <v>8420.476000000001</v>
       </c>
-      <c r="AY63" s="8" t="n">
+      <c r="AZ63" s="8" t="n">
         <v>1658.75</v>
-      </c>
-      <c r="AZ63" s="8" t="n">
-        <v>10664.785</v>
       </c>
       <c r="BA63" s="8" t="n">
         <v>1696.306</v>
       </c>
       <c r="BB63" s="8" t="n">
+        <v>1725.371</v>
+      </c>
+      <c r="BC63" s="8" t="n">
         <v>1782.965</v>
       </c>
-      <c r="BC63" s="8" t="n">
+      <c r="BD63" s="8" t="n">
         <v>1835.935</v>
-      </c>
-      <c r="BD63" s="8" t="n">
-        <v>1725.371</v>
       </c>
       <c r="BE63" s="8" t="n">
         <v>1886.954</v>
@@ -8359,37 +8359,37 @@
         <v>1693.947</v>
       </c>
       <c r="BI63" s="8" t="n">
+        <v>1985.352</v>
+      </c>
+      <c r="BJ63" s="8" t="n">
         <v>2069.268</v>
       </c>
-      <c r="BJ63" s="8" t="n">
+      <c r="BK63" s="8" t="n">
         <v>1960.142</v>
-      </c>
-      <c r="BK63" s="8" t="n">
-        <v>1985.352</v>
       </c>
       <c r="BL63" s="8" t="n">
         <v>1218.965</v>
       </c>
       <c r="BM63" s="8" t="n">
+        <v>1202.535</v>
+      </c>
+      <c r="BN63" s="8" t="n">
         <v>1195.486</v>
       </c>
-      <c r="BN63" s="8" t="n">
+      <c r="BO63" s="8" t="n">
         <v>1197.261</v>
-      </c>
-      <c r="BO63" s="8" t="n">
-        <v>1202.535</v>
       </c>
       <c r="BP63" s="8" t="n">
         <v>1196.911</v>
       </c>
       <c r="BQ63" s="8" t="n">
+        <v>1496.253</v>
+      </c>
+      <c r="BR63" s="8" t="n">
         <v>1712.915</v>
       </c>
-      <c r="BR63" s="8" t="n">
+      <c r="BS63" s="8" t="n">
         <v>6806.442</v>
-      </c>
-      <c r="BS63" s="8" t="n">
-        <v>1496.253</v>
       </c>
       <c r="BT63" s="8" t="n">
         <v>8628.547</v>
@@ -8615,61 +8615,61 @@
         </is>
       </c>
       <c r="AL67" s="10" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AM67" s="10" t="n">
         <v>0.87</v>
       </c>
-      <c r="AM67" s="10" t="n">
+      <c r="AN67" s="10" t="n">
         <v>1.818</v>
-      </c>
-      <c r="AN67" s="10" t="n">
-        <v>0.376</v>
       </c>
       <c r="AO67" s="10" t="n">
         <v>3.359</v>
       </c>
       <c r="AP67" s="10" t="n">
+        <v>5.386</v>
+      </c>
+      <c r="AQ67" s="10" t="n">
         <v>6.566</v>
       </c>
-      <c r="AQ67" s="10" t="n">
+      <c r="AR67" s="10" t="n">
         <v>8.888</v>
-      </c>
-      <c r="AR67" s="10" t="n">
-        <v>5.386</v>
       </c>
       <c r="AS67" s="10" t="n">
         <v>9.824</v>
       </c>
       <c r="AT67" s="10" t="n">
+        <v>11.187</v>
+      </c>
+      <c r="AU67" s="10" t="n">
         <v>12.324</v>
       </c>
-      <c r="AU67" s="10" t="n">
+      <c r="AV67" s="10" t="n">
         <v>13.028</v>
-      </c>
-      <c r="AV67" s="10" t="n">
-        <v>11.187</v>
       </c>
       <c r="AW67" s="10" t="n">
         <v>14.321</v>
       </c>
       <c r="AX67" s="10" t="n">
+        <v>16.329</v>
+      </c>
+      <c r="AY67" s="10" t="n">
         <v>16.982</v>
       </c>
-      <c r="AY67" s="10" t="n">
+      <c r="AZ67" s="10" t="n">
         <v>18.826</v>
-      </c>
-      <c r="AZ67" s="10" t="n">
-        <v>16.329</v>
       </c>
       <c r="BA67" s="10" t="n">
         <v>20.741</v>
       </c>
       <c r="BB67" s="10" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="BC67" s="10" t="n">
         <v>24.455</v>
       </c>
-      <c r="BC67" s="10" t="n">
+      <c r="BD67" s="10" t="n">
         <v>25.798</v>
-      </c>
-      <c r="BD67" s="10" t="n">
-        <v>22.65</v>
       </c>
       <c r="BE67" s="10" t="n">
         <v>31.318</v>
@@ -8684,37 +8684,37 @@
         <v>39.159</v>
       </c>
       <c r="BI67" s="10" t="n">
+        <v>41.048</v>
+      </c>
+      <c r="BJ67" s="10" t="n">
         <v>40.823</v>
       </c>
-      <c r="BJ67" s="10" t="n">
+      <c r="BK67" s="10" t="n">
         <v>43.785</v>
-      </c>
-      <c r="BK67" s="10" t="n">
-        <v>41.048</v>
       </c>
       <c r="BL67" s="10" t="n">
         <v>43.9</v>
       </c>
       <c r="BM67" s="10" t="n">
+        <v>43.621</v>
+      </c>
+      <c r="BN67" s="10" t="n">
         <v>43.234</v>
       </c>
-      <c r="BN67" s="10" t="n">
+      <c r="BO67" s="10" t="n">
         <v>42.985</v>
-      </c>
-      <c r="BO67" s="10" t="n">
-        <v>43.621</v>
       </c>
       <c r="BP67" s="10" t="n">
         <v>42.725</v>
       </c>
       <c r="BQ67" s="10" t="n">
+        <v>42.516</v>
+      </c>
+      <c r="BR67" s="10" t="n">
         <v>42.146</v>
       </c>
-      <c r="BR67" s="10" t="n">
+      <c r="BS67" s="10" t="n">
         <v>41.785</v>
-      </c>
-      <c r="BS67" s="10" t="n">
-        <v>42.516</v>
       </c>
       <c r="BT67" s="10" t="n">
         <v>40.356</v>
@@ -8734,61 +8734,61 @@
         </is>
       </c>
       <c r="AL69" s="8" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AM69" s="8" t="n">
         <v>0.87</v>
       </c>
-      <c r="AM69" s="8" t="n">
+      <c r="AN69" s="8" t="n">
         <v>1.818</v>
-      </c>
-      <c r="AN69" s="8" t="n">
-        <v>0.376</v>
       </c>
       <c r="AO69" s="8" t="n">
         <v>3.359</v>
       </c>
       <c r="AP69" s="8" t="n">
+        <v>5.386</v>
+      </c>
+      <c r="AQ69" s="8" t="n">
         <v>6.566</v>
       </c>
-      <c r="AQ69" s="8" t="n">
+      <c r="AR69" s="8" t="n">
         <v>8.888</v>
-      </c>
-      <c r="AR69" s="8" t="n">
-        <v>5.386</v>
       </c>
       <c r="AS69" s="8" t="n">
         <v>9.824</v>
       </c>
       <c r="AT69" s="8" t="n">
+        <v>11.187</v>
+      </c>
+      <c r="AU69" s="8" t="n">
         <v>12.324</v>
       </c>
-      <c r="AU69" s="8" t="n">
+      <c r="AV69" s="8" t="n">
         <v>13.028</v>
-      </c>
-      <c r="AV69" s="8" t="n">
-        <v>11.187</v>
       </c>
       <c r="AW69" s="8" t="n">
         <v>14.321</v>
       </c>
       <c r="AX69" s="8" t="n">
+        <v>16.329</v>
+      </c>
+      <c r="AY69" s="8" t="n">
         <v>16.982</v>
       </c>
-      <c r="AY69" s="8" t="n">
+      <c r="AZ69" s="8" t="n">
         <v>18.826</v>
-      </c>
-      <c r="AZ69" s="8" t="n">
-        <v>16.329</v>
       </c>
       <c r="BA69" s="8" t="n">
         <v>20.741</v>
       </c>
       <c r="BB69" s="8" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="BC69" s="8" t="n">
         <v>24.455</v>
       </c>
-      <c r="BC69" s="8" t="n">
+      <c r="BD69" s="8" t="n">
         <v>25.798</v>
-      </c>
-      <c r="BD69" s="8" t="n">
-        <v>22.65</v>
       </c>
       <c r="BE69" s="8" t="n">
         <v>31.318</v>
@@ -8803,37 +8803,37 @@
         <v>39.159</v>
       </c>
       <c r="BI69" s="8" t="n">
+        <v>41.048</v>
+      </c>
+      <c r="BJ69" s="8" t="n">
         <v>40.823</v>
       </c>
-      <c r="BJ69" s="8" t="n">
+      <c r="BK69" s="8" t="n">
         <v>43.785</v>
-      </c>
-      <c r="BK69" s="8" t="n">
-        <v>41.048</v>
       </c>
       <c r="BL69" s="8" t="n">
         <v>43.9</v>
       </c>
       <c r="BM69" s="8" t="n">
+        <v>43.621</v>
+      </c>
+      <c r="BN69" s="8" t="n">
         <v>43.234</v>
       </c>
-      <c r="BN69" s="8" t="n">
+      <c r="BO69" s="8" t="n">
         <v>42.985</v>
-      </c>
-      <c r="BO69" s="8" t="n">
-        <v>43.621</v>
       </c>
       <c r="BP69" s="8" t="n">
         <v>42.725</v>
       </c>
       <c r="BQ69" s="8" t="n">
+        <v>42.516</v>
+      </c>
+      <c r="BR69" s="8" t="n">
         <v>42.146</v>
       </c>
-      <c r="BR69" s="8" t="n">
+      <c r="BS69" s="8" t="n">
         <v>41.785</v>
-      </c>
-      <c r="BS69" s="8" t="n">
-        <v>42.516</v>
       </c>
       <c r="BT69" s="8" t="n">
         <v>40.356</v>
@@ -8939,54 +8939,54 @@
         <v>517.0650000000001</v>
       </c>
       <c r="AD73" s="10" t="n">
+        <v>516.9059999999999</v>
+      </c>
+      <c r="AE73" s="10" t="n">
         <v>472.938</v>
       </c>
-      <c r="AE73" s="10" t="n">
+      <c r="AF73" s="10" t="n">
         <v>473.242</v>
-      </c>
-      <c r="AF73" s="10" t="n">
-        <v>516.9059999999999</v>
       </c>
       <c r="AG73" s="10" t="n">
         <v>1281.836</v>
       </c>
       <c r="AH73" s="10" t="n">
+        <v>426.773</v>
+      </c>
+      <c r="AI73" s="10" t="n">
         <v>393.851</v>
       </c>
-      <c r="AI73" s="10" t="n">
+      <c r="AJ73" s="10" t="n">
         <v>398.528</v>
-      </c>
-      <c r="AJ73" s="10" t="n">
-        <v>426.773</v>
       </c>
       <c r="AK73" s="10" t="n">
         <v>1833.286</v>
       </c>
       <c r="AL73" s="10" t="n">
+        <v>811.285</v>
+      </c>
+      <c r="AM73" s="10" t="n">
         <v>794.8200000000001</v>
       </c>
-      <c r="AM73" s="10" t="n">
+      <c r="AN73" s="10" t="n">
         <v>784.105</v>
-      </c>
-      <c r="AN73" s="10" t="n">
-        <v>811.285</v>
       </c>
       <c r="AO73" s="10" t="n">
         <v>1597.773</v>
       </c>
       <c r="AP73" s="10" t="n">
+        <v>537.879</v>
+      </c>
+      <c r="AQ73" s="10" t="n">
         <v>530.955</v>
       </c>
-      <c r="AQ73" s="10" t="n">
+      <c r="AR73" s="10" t="n">
         <v>520.347</v>
-      </c>
-      <c r="AR73" s="10" t="n">
-        <v>537.879</v>
       </c>
       <c r="AS73" s="10" t="n">
         <v>1532.23</v>
       </c>
-      <c r="AV73" s="10" t="n">
+      <c r="AT73" s="10" t="n">
         <v>503.2</v>
       </c>
     </row>
@@ -9027,13 +9027,13 @@
         <v>1312.99</v>
       </c>
       <c r="AL74" s="6" t="n">
+        <v>286.778</v>
+      </c>
+      <c r="AM74" s="6" t="n">
         <v>265.756</v>
       </c>
-      <c r="AM74" s="6" t="n">
+      <c r="AN74" s="6" t="n">
         <v>254.711</v>
-      </c>
-      <c r="AN74" s="6" t="n">
-        <v>286.778</v>
       </c>
       <c r="AO74" s="6" t="n">
         <v>1065.292</v>
@@ -9085,54 +9085,54 @@
         <v>517.0650000000001</v>
       </c>
       <c r="AD75" s="8" t="n">
+        <v>516.9059999999999</v>
+      </c>
+      <c r="AE75" s="8" t="n">
         <v>472.938</v>
       </c>
-      <c r="AE75" s="8" t="n">
+      <c r="AF75" s="8" t="n">
         <v>473.242</v>
-      </c>
-      <c r="AF75" s="8" t="n">
-        <v>516.9059999999999</v>
       </c>
       <c r="AG75" s="8" t="n">
         <v>428.318</v>
       </c>
       <c r="AH75" s="8" t="n">
+        <v>426.773</v>
+      </c>
+      <c r="AI75" s="8" t="n">
         <v>393.851</v>
       </c>
-      <c r="AI75" s="8" t="n">
+      <c r="AJ75" s="8" t="n">
         <v>398.528</v>
-      </c>
-      <c r="AJ75" s="8" t="n">
-        <v>426.773</v>
       </c>
       <c r="AK75" s="8" t="n">
         <v>520.296</v>
       </c>
       <c r="AL75" s="8" t="n">
+        <v>524.5069999999999</v>
+      </c>
+      <c r="AM75" s="8" t="n">
         <v>529.063</v>
       </c>
-      <c r="AM75" s="8" t="n">
+      <c r="AN75" s="8" t="n">
         <v>529.394</v>
-      </c>
-      <c r="AN75" s="8" t="n">
-        <v>524.5069999999999</v>
       </c>
       <c r="AO75" s="8" t="n">
         <v>532.481</v>
       </c>
       <c r="AP75" s="8" t="n">
+        <v>537.879</v>
+      </c>
+      <c r="AQ75" s="8" t="n">
         <v>530.955</v>
       </c>
-      <c r="AQ75" s="8" t="n">
+      <c r="AR75" s="8" t="n">
         <v>520.347</v>
-      </c>
-      <c r="AR75" s="8" t="n">
-        <v>537.879</v>
       </c>
       <c r="AS75" s="8" t="n">
         <v>519.225</v>
       </c>
-      <c r="AV75" s="8" t="n">
+      <c r="AT75" s="8" t="n">
         <v>503.2</v>
       </c>
     </row>
@@ -9415,35 +9415,35 @@
       <c r="AB82" s="10" t="n">
         <v>148.958</v>
       </c>
-      <c r="AT82" s="10" t="n">
+      <c r="AU82" s="10" t="n">
         <v>45.312</v>
       </c>
-      <c r="AU82" s="10" t="n">
+      <c r="AV82" s="10" t="n">
         <v>28.026</v>
       </c>
       <c r="AW82" s="10" t="n">
         <v>1319.59</v>
       </c>
       <c r="AX82" s="10" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="AY82" s="10" t="n">
         <v>14.708</v>
       </c>
-      <c r="AY82" s="10" t="n">
+      <c r="AZ82" s="10" t="n">
         <v>13.257</v>
-      </c>
-      <c r="AZ82" s="10" t="n">
-        <v>14.98</v>
       </c>
       <c r="BA82" s="10" t="n">
         <v>855.76</v>
       </c>
       <c r="BB82" s="10" t="n">
+        <v>12.228</v>
+      </c>
+      <c r="BC82" s="10" t="n">
         <v>11.974</v>
       </c>
-      <c r="BC82" s="10" t="n">
+      <c r="BD82" s="10" t="n">
         <v>12.697</v>
-      </c>
-      <c r="BD82" s="10" t="n">
-        <v>12.228</v>
       </c>
       <c r="BE82" s="10" t="n">
         <v>840.653</v>
@@ -9458,37 +9458,37 @@
         <v>1031</v>
       </c>
       <c r="BI82" s="10" t="n">
+        <v>14.769</v>
+      </c>
+      <c r="BJ82" s="10" t="n">
         <v>15.034</v>
       </c>
-      <c r="BJ82" s="10" t="n">
+      <c r="BK82" s="10" t="n">
         <v>13.674</v>
-      </c>
-      <c r="BK82" s="10" t="n">
-        <v>14.769</v>
       </c>
       <c r="BL82" s="10" t="n">
         <v>8.151999999999999</v>
       </c>
       <c r="BM82" s="10" t="n">
+        <v>13.147</v>
+      </c>
+      <c r="BN82" s="10" t="n">
         <v>16.184</v>
       </c>
-      <c r="BN82" s="10" t="n">
+      <c r="BO82" s="10" t="n">
         <v>17.227</v>
-      </c>
-      <c r="BO82" s="10" t="n">
-        <v>13.147</v>
       </c>
       <c r="BP82" s="10" t="n">
         <v>986.316</v>
       </c>
       <c r="BQ82" s="10" t="n">
+        <v>18.387</v>
+      </c>
+      <c r="BR82" s="10" t="n">
         <v>17.965</v>
       </c>
-      <c r="BR82" s="10" t="n">
+      <c r="BS82" s="10" t="n">
         <v>16.528</v>
-      </c>
-      <c r="BS82" s="10" t="n">
-        <v>18.387</v>
       </c>
       <c r="BT82" s="10" t="n">
         <v>16.527</v>
@@ -9509,35 +9509,35 @@
       <c r="K83" s="6" t="n">
         <v>2368.421</v>
       </c>
-      <c r="AT83" s="6" t="n">
+      <c r="AU83" s="6" t="n">
         <v>12.671</v>
       </c>
-      <c r="AU83" s="6" t="n">
+      <c r="AV83" s="6" t="n">
         <v>10.156</v>
       </c>
       <c r="AW83" s="6" t="n">
         <v>1301.719</v>
       </c>
       <c r="AX83" s="6" t="n">
+        <v>11.307</v>
+      </c>
+      <c r="AY83" s="6" t="n">
         <v>11.035</v>
       </c>
-      <c r="AY83" s="6" t="n">
+      <c r="AZ83" s="6" t="n">
         <v>10.852</v>
-      </c>
-      <c r="AZ83" s="6" t="n">
-        <v>11.307</v>
       </c>
       <c r="BA83" s="6" t="n">
         <v>854.579</v>
       </c>
       <c r="BB83" s="6" t="n">
+        <v>11.047</v>
+      </c>
+      <c r="BC83" s="6" t="n">
         <v>11.974</v>
       </c>
-      <c r="BC83" s="6" t="n">
+      <c r="BD83" s="6" t="n">
         <v>12.697</v>
-      </c>
-      <c r="BD83" s="6" t="n">
-        <v>11.047</v>
       </c>
       <c r="BE83" s="6" t="n">
         <v>840.653</v>
@@ -9552,37 +9552,37 @@
         <v>1031</v>
       </c>
       <c r="BI83" s="6" t="n">
+        <v>14.769</v>
+      </c>
+      <c r="BJ83" s="6" t="n">
         <v>15.034</v>
       </c>
-      <c r="BJ83" s="6" t="n">
+      <c r="BK83" s="6" t="n">
         <v>13.674</v>
-      </c>
-      <c r="BK83" s="6" t="n">
-        <v>14.769</v>
       </c>
       <c r="BL83" s="6" t="n">
         <v>8.151999999999999</v>
       </c>
       <c r="BM83" s="6" t="n">
+        <v>13.147</v>
+      </c>
+      <c r="BN83" s="6" t="n">
         <v>16.184</v>
       </c>
-      <c r="BN83" s="6" t="n">
+      <c r="BO83" s="6" t="n">
         <v>17.227</v>
-      </c>
-      <c r="BO83" s="6" t="n">
-        <v>13.147</v>
       </c>
       <c r="BP83" s="6" t="n">
         <v>986.316</v>
       </c>
       <c r="BQ83" s="6" t="n">
+        <v>18.387</v>
+      </c>
+      <c r="BR83" s="6" t="n">
         <v>17.965</v>
       </c>
-      <c r="BR83" s="6" t="n">
+      <c r="BS83" s="6" t="n">
         <v>16.528</v>
-      </c>
-      <c r="BS83" s="6" t="n">
-        <v>18.387</v>
       </c>
       <c r="BT83" s="6" t="n">
         <v>16.527</v>
@@ -9663,10 +9663,10 @@
       <c r="AB84" s="8" t="n">
         <v>148.958</v>
       </c>
-      <c r="AT84" s="8" t="n">
+      <c r="AU84" s="8" t="n">
         <v>32.641</v>
       </c>
-      <c r="AU84" s="8" t="n">
+      <c r="AV84" s="8" t="n">
         <v>17.871</v>
       </c>
       <c r="AW84" s="8" t="n">
@@ -9676,15 +9676,15 @@
         <v>3.673</v>
       </c>
       <c r="AY84" s="8" t="n">
+        <v>3.673</v>
+      </c>
+      <c r="AZ84" s="8" t="n">
         <v>2.406</v>
-      </c>
-      <c r="AZ84" s="8" t="n">
-        <v>3.673</v>
       </c>
       <c r="BA84" s="8" t="n">
         <v>1.181</v>
       </c>
-      <c r="BD84" s="8" t="n">
+      <c r="BB84" s="8" t="n">
         <v>1.181</v>
       </c>
     </row>
@@ -9779,85 +9779,85 @@
         <v>897.367</v>
       </c>
       <c r="AD85" s="10" t="n">
+        <v>1321.336</v>
+      </c>
+      <c r="AE85" s="10" t="n">
         <v>1426.822</v>
       </c>
-      <c r="AE85" s="10" t="n">
+      <c r="AF85" s="10" t="n">
         <v>1409.661</v>
-      </c>
-      <c r="AF85" s="10" t="n">
-        <v>1321.336</v>
       </c>
       <c r="AG85" s="10" t="n">
         <v>1237.702</v>
       </c>
       <c r="AH85" s="10" t="n">
+        <v>1206.295</v>
+      </c>
+      <c r="AI85" s="10" t="n">
         <v>1277.221</v>
       </c>
-      <c r="AI85" s="10" t="n">
+      <c r="AJ85" s="10" t="n">
         <v>1325.546</v>
-      </c>
-      <c r="AJ85" s="10" t="n">
-        <v>1206.295</v>
       </c>
       <c r="AK85" s="10" t="n">
         <v>1062.342</v>
       </c>
       <c r="AL85" s="10" t="n">
+        <v>759.288</v>
+      </c>
+      <c r="AM85" s="10" t="n">
         <v>543.631</v>
       </c>
-      <c r="AM85" s="10" t="n">
+      <c r="AN85" s="10" t="n">
         <v>538.191</v>
-      </c>
-      <c r="AN85" s="10" t="n">
-        <v>759.288</v>
       </c>
       <c r="AO85" s="10" t="n">
         <v>321.521</v>
       </c>
       <c r="AP85" s="10" t="n">
+        <v>342.09</v>
+      </c>
+      <c r="AQ85" s="10" t="n">
         <v>108.333</v>
       </c>
-      <c r="AQ85" s="10" t="n">
+      <c r="AR85" s="10" t="n">
         <v>83.816</v>
-      </c>
-      <c r="AR85" s="10" t="n">
-        <v>342.09</v>
       </c>
       <c r="AS85" s="10" t="n">
         <v>98.88</v>
       </c>
       <c r="AT85" s="10" t="n">
+        <v>80.328</v>
+      </c>
+      <c r="AU85" s="10" t="n">
         <v>91.587</v>
       </c>
-      <c r="AU85" s="10" t="n">
+      <c r="AV85" s="10" t="n">
         <v>73.35599999999999</v>
-      </c>
-      <c r="AV85" s="10" t="n">
-        <v>80.328</v>
       </c>
       <c r="AW85" s="10" t="n">
         <v>80.009</v>
       </c>
       <c r="AX85" s="10" t="n">
+        <v>64.011</v>
+      </c>
+      <c r="AY85" s="10" t="n">
         <v>62.47</v>
       </c>
-      <c r="AY85" s="10" t="n">
+      <c r="AZ85" s="10" t="n">
         <v>61.435</v>
-      </c>
-      <c r="AZ85" s="10" t="n">
-        <v>64.011</v>
       </c>
       <c r="BA85" s="10" t="n">
         <v>61.127</v>
       </c>
       <c r="BB85" s="10" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="BC85" s="10" t="n">
         <v>67.786</v>
       </c>
-      <c r="BC85" s="10" t="n">
+      <c r="BD85" s="10" t="n">
         <v>71.883</v>
-      </c>
-      <c r="BD85" s="10" t="n">
-        <v>62.54</v>
       </c>
       <c r="BE85" s="10" t="n">
         <v>75.874</v>
@@ -9872,37 +9872,37 @@
         <v>83.801</v>
       </c>
       <c r="BI85" s="10" t="n">
+        <v>83.696</v>
+      </c>
+      <c r="BJ85" s="10" t="n">
         <v>85.19799999999999</v>
       </c>
-      <c r="BJ85" s="10" t="n">
+      <c r="BK85" s="10" t="n">
         <v>77.49299999999999</v>
-      </c>
-      <c r="BK85" s="10" t="n">
-        <v>83.696</v>
       </c>
       <c r="BL85" s="10" t="n">
         <v>46.198</v>
       </c>
       <c r="BM85" s="10" t="n">
+        <v>74.428</v>
+      </c>
+      <c r="BN85" s="10" t="n">
         <v>91.62</v>
       </c>
-      <c r="BN85" s="10" t="n">
+      <c r="BO85" s="10" t="n">
         <v>97.526</v>
-      </c>
-      <c r="BO85" s="10" t="n">
-        <v>74.428</v>
       </c>
       <c r="BP85" s="10" t="n">
         <v>100.733</v>
       </c>
       <c r="BQ85" s="10" t="n">
+        <v>104.095</v>
+      </c>
+      <c r="BR85" s="10" t="n">
         <v>101.704</v>
       </c>
-      <c r="BR85" s="10" t="n">
+      <c r="BS85" s="10" t="n">
         <v>281.136</v>
-      </c>
-      <c r="BS85" s="10" t="n">
-        <v>104.095</v>
       </c>
       <c r="BT85" s="10" t="n">
         <v>278.778</v>
@@ -9999,85 +9999,85 @@
         <v>897.367</v>
       </c>
       <c r="AD86" s="6" t="n">
+        <v>1321.336</v>
+      </c>
+      <c r="AE86" s="6" t="n">
         <v>0.063</v>
       </c>
-      <c r="AE86" s="6" t="n">
+      <c r="AF86" s="6" t="n">
         <v>1409.661</v>
-      </c>
-      <c r="AF86" s="6" t="n">
-        <v>1321.336</v>
       </c>
       <c r="AG86" s="6" t="n">
         <v>1237.702</v>
       </c>
       <c r="AH86" s="6" t="n">
+        <v>1206.295</v>
+      </c>
+      <c r="AI86" s="6" t="n">
         <v>1277.221</v>
       </c>
-      <c r="AI86" s="6" t="n">
+      <c r="AJ86" s="6" t="n">
         <v>1325.546</v>
-      </c>
-      <c r="AJ86" s="6" t="n">
-        <v>1206.295</v>
       </c>
       <c r="AK86" s="6" t="n">
         <v>1062.342</v>
       </c>
       <c r="AL86" s="6" t="n">
+        <v>759.288</v>
+      </c>
+      <c r="AM86" s="6" t="n">
         <v>543.631</v>
       </c>
-      <c r="AM86" s="6" t="n">
+      <c r="AN86" s="6" t="n">
         <v>538.191</v>
-      </c>
-      <c r="AN86" s="6" t="n">
-        <v>759.288</v>
       </c>
       <c r="AO86" s="6" t="n">
         <v>321.521</v>
       </c>
       <c r="AP86" s="6" t="n">
+        <v>342.09</v>
+      </c>
+      <c r="AQ86" s="6" t="n">
         <v>108.333</v>
       </c>
-      <c r="AQ86" s="6" t="n">
+      <c r="AR86" s="6" t="n">
         <v>83.816</v>
-      </c>
-      <c r="AR86" s="6" t="n">
-        <v>342.09</v>
       </c>
       <c r="AS86" s="6" t="n">
         <v>98.88</v>
       </c>
       <c r="AT86" s="6" t="n">
+        <v>80.328</v>
+      </c>
+      <c r="AU86" s="6" t="n">
         <v>91.587</v>
       </c>
-      <c r="AU86" s="6" t="n">
+      <c r="AV86" s="6" t="n">
         <v>73.35599999999999</v>
-      </c>
-      <c r="AV86" s="6" t="n">
-        <v>80.328</v>
       </c>
       <c r="AW86" s="6" t="n">
         <v>80.009</v>
       </c>
       <c r="AX86" s="6" t="n">
+        <v>64.011</v>
+      </c>
+      <c r="AY86" s="6" t="n">
         <v>62.47</v>
       </c>
-      <c r="AY86" s="6" t="n">
+      <c r="AZ86" s="6" t="n">
         <v>61.435</v>
-      </c>
-      <c r="AZ86" s="6" t="n">
-        <v>64.011</v>
       </c>
       <c r="BA86" s="6" t="n">
         <v>61.127</v>
       </c>
       <c r="BB86" s="6" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="BC86" s="6" t="n">
         <v>67.786</v>
       </c>
-      <c r="BC86" s="6" t="n">
+      <c r="BD86" s="6" t="n">
         <v>71.883</v>
-      </c>
-      <c r="BD86" s="6" t="n">
-        <v>62.54</v>
       </c>
       <c r="BE86" s="6" t="n">
         <v>75.874</v>
@@ -10092,37 +10092,37 @@
         <v>83.801</v>
       </c>
       <c r="BI86" s="6" t="n">
+        <v>83.696</v>
+      </c>
+      <c r="BJ86" s="6" t="n">
         <v>85.19799999999999</v>
       </c>
-      <c r="BJ86" s="6" t="n">
+      <c r="BK86" s="6" t="n">
         <v>77.49299999999999</v>
-      </c>
-      <c r="BK86" s="6" t="n">
-        <v>83.696</v>
       </c>
       <c r="BL86" s="6" t="n">
         <v>46.198</v>
       </c>
       <c r="BM86" s="6" t="n">
+        <v>74.428</v>
+      </c>
+      <c r="BN86" s="6" t="n">
         <v>91.62</v>
       </c>
-      <c r="BN86" s="6" t="n">
+      <c r="BO86" s="6" t="n">
         <v>97.526</v>
-      </c>
-      <c r="BO86" s="6" t="n">
-        <v>74.428</v>
       </c>
       <c r="BP86" s="6" t="n">
         <v>100.733</v>
       </c>
       <c r="BQ86" s="6" t="n">
+        <v>104.095</v>
+      </c>
+      <c r="BR86" s="6" t="n">
         <v>101.704</v>
       </c>
-      <c r="BR86" s="6" t="n">
+      <c r="BS86" s="6" t="n">
         <v>281.136</v>
-      </c>
-      <c r="BS86" s="6" t="n">
-        <v>104.095</v>
       </c>
       <c r="BT86" s="6" t="n">
         <v>278.778</v>
@@ -10149,7 +10149,7 @@
       <c r="P87" s="8" t="n">
         <v>1073.023</v>
       </c>
-      <c r="AD87" s="8" t="n">
+      <c r="AE87" s="8" t="n">
         <v>1426.759</v>
       </c>
     </row>
@@ -10437,19 +10437,19 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
+          <t>03/2015</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr">
+        <is>
           <t>06/2015</t>
         </is>
       </c>
-      <c r="AE5" s="2" t="inlineStr">
+      <c r="AF5" s="2" t="inlineStr">
         <is>
           <t>09/2015</t>
         </is>
       </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>03/2015</t>
-        </is>
-      </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
           <t>12/2015</t>
@@ -10457,19 +10457,19 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
+          <t>03/2016</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
           <t>06/2016</t>
         </is>
       </c>
-      <c r="AI5" s="2" t="inlineStr">
+      <c r="AJ5" s="2" t="inlineStr">
         <is>
           <t>09/2016</t>
         </is>
       </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>03/2016</t>
-        </is>
-      </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
           <t>12/2016</t>
@@ -10477,19 +10477,19 @@
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
+          <t>03/2017</t>
+        </is>
+      </c>
+      <c r="AM5" s="2" t="inlineStr">
+        <is>
           <t>06/2017</t>
         </is>
       </c>
-      <c r="AM5" s="2" t="inlineStr">
+      <c r="AN5" s="2" t="inlineStr">
         <is>
           <t>09/2017</t>
         </is>
       </c>
-      <c r="AN5" s="2" t="inlineStr">
-        <is>
-          <t>03/2017</t>
-        </is>
-      </c>
       <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>12/2017</t>
@@ -10497,19 +10497,19 @@
       </c>
       <c r="AP5" s="2" t="inlineStr">
         <is>
+          <t>03/2018</t>
+        </is>
+      </c>
+      <c r="AQ5" s="2" t="inlineStr">
+        <is>
           <t>06/2018</t>
         </is>
       </c>
-      <c r="AQ5" s="2" t="inlineStr">
+      <c r="AR5" s="2" t="inlineStr">
         <is>
           <t>09/2018</t>
         </is>
       </c>
-      <c r="AR5" s="2" t="inlineStr">
-        <is>
-          <t>03/2018</t>
-        </is>
-      </c>
       <c r="AS5" s="2" t="inlineStr">
         <is>
           <t>12/2018</t>
@@ -10517,19 +10517,19 @@
       </c>
       <c r="AT5" s="2" t="inlineStr">
         <is>
+          <t>03/2019</t>
+        </is>
+      </c>
+      <c r="AU5" s="2" t="inlineStr">
+        <is>
           <t>06/2019</t>
         </is>
       </c>
-      <c r="AU5" s="2" t="inlineStr">
+      <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>09/2019</t>
         </is>
       </c>
-      <c r="AV5" s="2" t="inlineStr">
-        <is>
-          <t>03/2019</t>
-        </is>
-      </c>
       <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>12/2019</t>
@@ -10537,19 +10537,19 @@
       </c>
       <c r="AX5" s="2" t="inlineStr">
         <is>
+          <t>03/2020</t>
+        </is>
+      </c>
+      <c r="AY5" s="2" t="inlineStr">
+        <is>
           <t>06/2020</t>
         </is>
       </c>
-      <c r="AY5" s="2" t="inlineStr">
+      <c r="AZ5" s="2" t="inlineStr">
         <is>
           <t>09/2020</t>
         </is>
       </c>
-      <c r="AZ5" s="2" t="inlineStr">
-        <is>
-          <t>03/2020</t>
-        </is>
-      </c>
       <c r="BA5" s="2" t="inlineStr">
         <is>
           <t>12/2020</t>
@@ -10557,19 +10557,19 @@
       </c>
       <c r="BB5" s="2" t="inlineStr">
         <is>
+          <t>03/2021</t>
+        </is>
+      </c>
+      <c r="BC5" s="2" t="inlineStr">
+        <is>
           <t>06/2021</t>
         </is>
       </c>
-      <c r="BC5" s="2" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr">
         <is>
           <t>09/2021</t>
         </is>
       </c>
-      <c r="BD5" s="2" t="inlineStr">
-        <is>
-          <t>03/2021</t>
-        </is>
-      </c>
       <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>12/2021</t>
@@ -10592,19 +10592,19 @@
       </c>
       <c r="BI5" s="2" t="inlineStr">
         <is>
+          <t>03/2023</t>
+        </is>
+      </c>
+      <c r="BJ5" s="2" t="inlineStr">
+        <is>
           <t>06/2023</t>
         </is>
       </c>
-      <c r="BJ5" s="2" t="inlineStr">
+      <c r="BK5" s="2" t="inlineStr">
         <is>
           <t>09/2023</t>
         </is>
       </c>
-      <c r="BK5" s="2" t="inlineStr">
-        <is>
-          <t>03/2023</t>
-        </is>
-      </c>
       <c r="BL5" s="2" t="inlineStr">
         <is>
           <t>12/2023</t>
@@ -10612,19 +10612,19 @@
       </c>
       <c r="BM5" s="2" t="inlineStr">
         <is>
+          <t>03/2024</t>
+        </is>
+      </c>
+      <c r="BN5" s="2" t="inlineStr">
+        <is>
           <t>06/2024</t>
         </is>
       </c>
-      <c r="BN5" s="2" t="inlineStr">
+      <c r="BO5" s="2" t="inlineStr">
         <is>
           <t>09/2024</t>
         </is>
       </c>
-      <c r="BO5" s="2" t="inlineStr">
-        <is>
-          <t>03/2024</t>
-        </is>
-      </c>
       <c r="BP5" s="2" t="inlineStr">
         <is>
           <t>12/2024</t>
@@ -10632,17 +10632,17 @@
       </c>
       <c r="BQ5" s="2" t="inlineStr">
         <is>
+          <t>03/2025</t>
+        </is>
+      </c>
+      <c r="BR5" s="2" t="inlineStr">
+        <is>
           <t>06/2025</t>
         </is>
       </c>
-      <c r="BR5" s="2" t="inlineStr">
+      <c r="BS5" s="2" t="inlineStr">
         <is>
           <t>09/2025</t>
-        </is>
-      </c>
-      <c r="BS5" s="2" t="inlineStr">
-        <is>
-          <t>03/2025</t>
         </is>
       </c>
       <c r="BT5" s="2" t="inlineStr">
@@ -10742,85 +10742,85 @@
         <v>87398.026</v>
       </c>
       <c r="AD6" s="13" t="n">
+        <v>88628.315</v>
+      </c>
+      <c r="AE6" s="13" t="n">
         <v>101544.673</v>
       </c>
-      <c r="AE6" s="13" t="n">
+      <c r="AF6" s="13" t="n">
         <v>105853.556</v>
-      </c>
-      <c r="AF6" s="13" t="n">
-        <v>88628.315</v>
       </c>
       <c r="AG6" s="13" t="n">
         <v>88031.443</v>
       </c>
       <c r="AH6" s="13" t="n">
+        <v>82898.344</v>
+      </c>
+      <c r="AI6" s="13" t="n">
         <v>89085.586</v>
       </c>
-      <c r="AI6" s="13" t="n">
+      <c r="AJ6" s="13" t="n">
         <v>89668.997</v>
-      </c>
-      <c r="AJ6" s="13" t="n">
-        <v>82898.344</v>
       </c>
       <c r="AK6" s="13" t="n">
         <v>108373.846</v>
       </c>
       <c r="AL6" s="13" t="n">
+        <v>114923.759</v>
+      </c>
+      <c r="AM6" s="13" t="n">
         <v>120964.344</v>
       </c>
-      <c r="AM6" s="13" t="n">
+      <c r="AN6" s="13" t="n">
         <v>121528.779</v>
-      </c>
-      <c r="AN6" s="13" t="n">
-        <v>114923.759</v>
       </c>
       <c r="AO6" s="13" t="n">
         <v>129453.821</v>
       </c>
       <c r="AP6" s="13" t="n">
+        <v>133492.536</v>
+      </c>
+      <c r="AQ6" s="13" t="n">
         <v>127729.768</v>
       </c>
-      <c r="AQ6" s="13" t="n">
+      <c r="AR6" s="13" t="n">
         <v>114397.896</v>
-      </c>
-      <c r="AR6" s="13" t="n">
-        <v>133492.536</v>
       </c>
       <c r="AS6" s="13" t="n">
         <v>128760.041</v>
       </c>
       <c r="AT6" s="13" t="n">
+        <v>131470.208</v>
+      </c>
+      <c r="AU6" s="13" t="n">
         <v>135870.769</v>
       </c>
-      <c r="AU6" s="13" t="n">
+      <c r="AV6" s="13" t="n">
         <v>114099.147</v>
-      </c>
-      <c r="AV6" s="13" t="n">
-        <v>131470.208</v>
       </c>
       <c r="AW6" s="13" t="n">
         <v>123970.792</v>
       </c>
       <c r="AX6" s="13" t="n">
+        <v>126488.075</v>
+      </c>
+      <c r="AY6" s="13" t="n">
         <v>137325.236</v>
       </c>
-      <c r="AY6" s="13" t="n">
+      <c r="AZ6" s="13" t="n">
         <v>107614.027</v>
-      </c>
-      <c r="AZ6" s="13" t="n">
-        <v>126488.075</v>
       </c>
       <c r="BA6" s="13" t="n">
         <v>115106.815</v>
       </c>
       <c r="BB6" s="13" t="n">
+        <v>121915.052</v>
+      </c>
+      <c r="BC6" s="13" t="n">
         <v>131144.842</v>
       </c>
-      <c r="BC6" s="13" t="n">
+      <c r="BD6" s="13" t="n">
         <v>136697.946</v>
-      </c>
-      <c r="BD6" s="13" t="n">
-        <v>121915.052</v>
       </c>
       <c r="BE6" s="13" t="n">
         <v>154646.713</v>
@@ -10835,37 +10835,37 @@
         <v>178574.111</v>
       </c>
       <c r="BI6" s="13" t="n">
+        <v>172472.135</v>
+      </c>
+      <c r="BJ6" s="13" t="n">
         <v>191527.107</v>
       </c>
-      <c r="BJ6" s="13" t="n">
+      <c r="BK6" s="13" t="n">
         <v>189523.345</v>
-      </c>
-      <c r="BK6" s="13" t="n">
-        <v>172472.135</v>
       </c>
       <c r="BL6" s="13" t="n">
         <v>158705.147</v>
       </c>
       <c r="BM6" s="13" t="n">
+        <v>132086.675</v>
+      </c>
+      <c r="BN6" s="13" t="n">
         <v>166100.777</v>
       </c>
-      <c r="BN6" s="13" t="n">
+      <c r="BO6" s="13" t="n">
         <v>171012.644</v>
-      </c>
-      <c r="BO6" s="13" t="n">
-        <v>132086.675</v>
       </c>
       <c r="BP6" s="13" t="n">
         <v>200016.714</v>
       </c>
       <c r="BQ6" s="13" t="n">
+        <v>207726.473</v>
+      </c>
+      <c r="BR6" s="13" t="n">
         <v>195326.897</v>
       </c>
-      <c r="BR6" s="13" t="n">
+      <c r="BS6" s="13" t="n">
         <v>194068.53</v>
-      </c>
-      <c r="BS6" s="13" t="n">
-        <v>207726.473</v>
       </c>
       <c r="BT6" s="13" t="n">
         <v>208734.929</v>
@@ -10962,85 +10962,85 @@
         <v>29402.479</v>
       </c>
       <c r="AD7" s="10" t="n">
+        <v>29224.35</v>
+      </c>
+      <c r="AE7" s="10" t="n">
         <v>29532.823</v>
       </c>
-      <c r="AE7" s="10" t="n">
+      <c r="AF7" s="10" t="n">
         <v>31037.668</v>
-      </c>
-      <c r="AF7" s="10" t="n">
-        <v>29224.35</v>
       </c>
       <c r="AG7" s="10" t="n">
         <v>25517.109</v>
       </c>
       <c r="AH7" s="10" t="n">
+        <v>23169.452</v>
+      </c>
+      <c r="AI7" s="10" t="n">
         <v>24380.027</v>
       </c>
-      <c r="AI7" s="10" t="n">
+      <c r="AJ7" s="10" t="n">
         <v>24642.771</v>
-      </c>
-      <c r="AJ7" s="10" t="n">
-        <v>23169.452</v>
       </c>
       <c r="AK7" s="10" t="n">
         <v>24115.153</v>
       </c>
       <c r="AL7" s="10" t="n">
+        <v>27287.444</v>
+      </c>
+      <c r="AM7" s="10" t="n">
         <v>28841.763</v>
       </c>
-      <c r="AM7" s="10" t="n">
+      <c r="AN7" s="10" t="n">
         <v>27267.688</v>
-      </c>
-      <c r="AN7" s="10" t="n">
-        <v>27287.444</v>
       </c>
       <c r="AO7" s="10" t="n">
         <v>25153.136</v>
       </c>
       <c r="AP7" s="10" t="n">
+        <v>25176.113</v>
+      </c>
+      <c r="AQ7" s="10" t="n">
         <v>18783.717</v>
       </c>
-      <c r="AQ7" s="10" t="n">
+      <c r="AR7" s="10" t="n">
         <v>12292.679</v>
-      </c>
-      <c r="AR7" s="10" t="n">
-        <v>25176.113</v>
       </c>
       <c r="AS7" s="10" t="n">
         <v>13296.816</v>
       </c>
       <c r="AT7" s="10" t="n">
+        <v>11596.118</v>
+      </c>
+      <c r="AU7" s="10" t="n">
         <v>11843.348</v>
       </c>
-      <c r="AU7" s="10" t="n">
+      <c r="AV7" s="10" t="n">
         <v>8734.275</v>
-      </c>
-      <c r="AV7" s="10" t="n">
-        <v>11596.118</v>
       </c>
       <c r="AW7" s="10" t="n">
         <v>14237.082</v>
       </c>
       <c r="AX7" s="10" t="n">
+        <v>16825.423</v>
+      </c>
+      <c r="AY7" s="10" t="n">
         <v>16531.545</v>
       </c>
-      <c r="AY7" s="10" t="n">
+      <c r="AZ7" s="10" t="n">
         <v>18197.965</v>
-      </c>
-      <c r="AZ7" s="10" t="n">
-        <v>16825.423</v>
       </c>
       <c r="BA7" s="10" t="n">
         <v>14979.5</v>
       </c>
       <c r="BB7" s="10" t="n">
+        <v>15170.408</v>
+      </c>
+      <c r="BC7" s="10" t="n">
         <v>15151.99</v>
       </c>
-      <c r="BC7" s="10" t="n">
+      <c r="BD7" s="10" t="n">
         <v>10361.567</v>
-      </c>
-      <c r="BD7" s="10" t="n">
-        <v>15170.408</v>
       </c>
       <c r="BE7" s="10" t="n">
         <v>21148.899</v>
@@ -11055,37 +11055,37 @@
         <v>15768.798</v>
       </c>
       <c r="BI7" s="10" t="n">
+        <v>13986.909</v>
+      </c>
+      <c r="BJ7" s="10" t="n">
         <v>16172.593</v>
       </c>
-      <c r="BJ7" s="10" t="n">
+      <c r="BK7" s="10" t="n">
         <v>11688.581</v>
-      </c>
-      <c r="BK7" s="10" t="n">
-        <v>13986.909</v>
       </c>
       <c r="BL7" s="10" t="n">
         <v>5060.425</v>
       </c>
       <c r="BM7" s="10" t="n">
+        <v>4771.426</v>
+      </c>
+      <c r="BN7" s="10" t="n">
         <v>4487.086</v>
       </c>
-      <c r="BN7" s="10" t="n">
+      <c r="BO7" s="10" t="n">
         <v>4213.647</v>
-      </c>
-      <c r="BO7" s="10" t="n">
-        <v>4771.426</v>
       </c>
       <c r="BP7" s="10" t="n">
         <v>3962.325</v>
       </c>
       <c r="BQ7" s="10" t="n">
+        <v>3809.662</v>
+      </c>
+      <c r="BR7" s="10" t="n">
         <v>3426.143</v>
       </c>
-      <c r="BR7" s="10" t="n">
+      <c r="BS7" s="10" t="n">
         <v>2993.671</v>
-      </c>
-      <c r="BS7" s="10" t="n">
-        <v>3809.662</v>
       </c>
       <c r="BT7" s="10" t="n">
         <v>2803.243</v>
@@ -11097,35 +11097,35 @@
           <t>AVALES</t>
         </is>
       </c>
-      <c r="AT8" s="10" t="n">
+      <c r="AU8" s="10" t="n">
         <v>647.769</v>
       </c>
-      <c r="AU8" s="10" t="n">
+      <c r="AV8" s="10" t="n">
         <v>615.246</v>
       </c>
       <c r="AW8" s="10" t="n">
         <v>2316.352</v>
       </c>
       <c r="AX8" s="10" t="n">
+        <v>2255.795</v>
+      </c>
+      <c r="AY8" s="10" t="n">
         <v>2206.582</v>
       </c>
-      <c r="AY8" s="10" t="n">
+      <c r="AZ8" s="10" t="n">
         <v>2160.542</v>
-      </c>
-      <c r="AZ8" s="10" t="n">
-        <v>2255.795</v>
       </c>
       <c r="BA8" s="10" t="n">
         <v>1948.46</v>
       </c>
       <c r="BB8" s="10" t="n">
+        <v>1888.555</v>
+      </c>
+      <c r="BC8" s="10" t="n">
         <v>1836.706</v>
       </c>
-      <c r="BC8" s="10" t="n">
+      <c r="BD8" s="10" t="n">
         <v>1724.959</v>
-      </c>
-      <c r="BD8" s="10" t="n">
-        <v>1888.555</v>
       </c>
       <c r="BE8" s="10" t="n">
         <v>452.447</v>
@@ -11140,37 +11140,37 @@
         <v>428.573</v>
       </c>
       <c r="BI8" s="10" t="n">
+        <v>378.871</v>
+      </c>
+      <c r="BJ8" s="10" t="n">
         <v>366.125</v>
       </c>
-      <c r="BJ8" s="10" t="n">
+      <c r="BK8" s="10" t="n">
         <v>489.208</v>
-      </c>
-      <c r="BK8" s="10" t="n">
-        <v>378.871</v>
       </c>
       <c r="BL8" s="10" t="n">
         <v>469.085</v>
       </c>
       <c r="BM8" s="10" t="n">
+        <v>456.423</v>
+      </c>
+      <c r="BN8" s="10" t="n">
         <v>434.877</v>
       </c>
-      <c r="BN8" s="10" t="n">
+      <c r="BO8" s="10" t="n">
         <v>392.992</v>
-      </c>
-      <c r="BO8" s="10" t="n">
-        <v>456.423</v>
       </c>
       <c r="BP8" s="10" t="n">
         <v>398.309</v>
       </c>
       <c r="BQ8" s="10" t="n">
+        <v>416.638</v>
+      </c>
+      <c r="BR8" s="10" t="n">
         <v>434.736</v>
       </c>
-      <c r="BR8" s="10" t="n">
+      <c r="BS8" s="10" t="n">
         <v>449.098</v>
-      </c>
-      <c r="BS8" s="10" t="n">
-        <v>416.638</v>
       </c>
       <c r="BT8" s="10" t="n">
         <v>1236.577</v>
@@ -11267,85 +11267,85 @@
         <v>3826.76</v>
       </c>
       <c r="AD9" s="10" t="n">
+        <v>4420.799</v>
+      </c>
+      <c r="AE9" s="10" t="n">
         <v>4304.007</v>
       </c>
-      <c r="AE9" s="10" t="n">
+      <c r="AF9" s="10" t="n">
         <v>4270.65</v>
-      </c>
-      <c r="AF9" s="10" t="n">
-        <v>4420.799</v>
       </c>
       <c r="AG9" s="10" t="n">
         <v>3828.346</v>
       </c>
       <c r="AH9" s="10" t="n">
+        <v>3381.49</v>
+      </c>
+      <c r="AI9" s="10" t="n">
         <v>3238.222</v>
       </c>
-      <c r="AI9" s="10" t="n">
+      <c r="AJ9" s="10" t="n">
         <v>1999.728</v>
-      </c>
-      <c r="AJ9" s="10" t="n">
-        <v>3381.49</v>
       </c>
       <c r="AK9" s="10" t="n">
         <v>1373.3</v>
       </c>
       <c r="AL9" s="10" t="n">
+        <v>1403.653</v>
+      </c>
+      <c r="AM9" s="10" t="n">
         <v>1017.011</v>
       </c>
-      <c r="AM9" s="10" t="n">
+      <c r="AN9" s="10" t="n">
         <v>715.465</v>
-      </c>
-      <c r="AN9" s="10" t="n">
-        <v>1403.653</v>
       </c>
       <c r="AO9" s="10" t="n">
         <v>2818.058</v>
       </c>
       <c r="AP9" s="10" t="n">
+        <v>2580.23</v>
+      </c>
+      <c r="AQ9" s="10" t="n">
         <v>1803.795</v>
       </c>
-      <c r="AQ9" s="10" t="n">
+      <c r="AR9" s="10" t="n">
         <v>1266.254</v>
-      </c>
-      <c r="AR9" s="10" t="n">
-        <v>2580.23</v>
       </c>
       <c r="AS9" s="10" t="n">
         <v>1361.519</v>
       </c>
       <c r="AT9" s="10" t="n">
+        <v>1090.037</v>
+      </c>
+      <c r="AU9" s="10" t="n">
         <v>1094.156</v>
       </c>
-      <c r="AU9" s="10" t="n">
+      <c r="AV9" s="10" t="n">
         <v>832.389</v>
-      </c>
-      <c r="AV9" s="10" t="n">
-        <v>1090.037</v>
       </c>
       <c r="AW9" s="10" t="n">
         <v>2718.998</v>
       </c>
       <c r="AX9" s="10" t="n">
+        <v>2371.297</v>
+      </c>
+      <c r="AY9" s="10" t="n">
         <v>1720.699</v>
       </c>
-      <c r="AY9" s="10" t="n">
+      <c r="AZ9" s="10" t="n">
         <v>1622.913</v>
-      </c>
-      <c r="AZ9" s="10" t="n">
-        <v>2371.297</v>
       </c>
       <c r="BA9" s="10" t="n">
         <v>1709.605</v>
       </c>
       <c r="BB9" s="10" t="n">
+        <v>1573.87</v>
+      </c>
+      <c r="BC9" s="10" t="n">
         <v>1545.515</v>
       </c>
-      <c r="BC9" s="10" t="n">
+      <c r="BD9" s="10" t="n">
         <v>1508.065</v>
-      </c>
-      <c r="BD9" s="10" t="n">
-        <v>1573.87</v>
       </c>
       <c r="BE9" s="10" t="n">
         <v>2239.309</v>
@@ -11360,37 +11360,37 @@
         <v>2500.464</v>
       </c>
       <c r="BI9" s="10" t="n">
+        <v>2146.535</v>
+      </c>
+      <c r="BJ9" s="10" t="n">
         <v>1785.205</v>
       </c>
-      <c r="BJ9" s="10" t="n">
+      <c r="BK9" s="10" t="n">
         <v>1349.205</v>
-      </c>
-      <c r="BK9" s="10" t="n">
-        <v>2146.535</v>
       </c>
       <c r="BL9" s="10" t="n">
         <v>1017.643</v>
       </c>
       <c r="BM9" s="10" t="n">
+        <v>964.673</v>
+      </c>
+      <c r="BN9" s="10" t="n">
         <v>911.856</v>
       </c>
-      <c r="BN9" s="10" t="n">
+      <c r="BO9" s="10" t="n">
         <v>870.75</v>
-      </c>
-      <c r="BO9" s="10" t="n">
-        <v>964.673</v>
       </c>
       <c r="BP9" s="10" t="n">
         <v>812.47</v>
       </c>
       <c r="BQ9" s="10" t="n">
+        <v>789.662</v>
+      </c>
+      <c r="BR9" s="10" t="n">
         <v>730.296</v>
       </c>
-      <c r="BR9" s="10" t="n">
+      <c r="BS9" s="10" t="n">
         <v>653.532</v>
-      </c>
-      <c r="BS9" s="10" t="n">
-        <v>789.662</v>
       </c>
       <c r="BT9" s="10" t="n">
         <v>615.819</v>
@@ -11406,49 +11406,49 @@
         <v>0.311</v>
       </c>
       <c r="AP10" s="10" t="n">
-        <v>0.346</v>
+        <v>0.311</v>
       </c>
       <c r="AQ10" s="10" t="n">
         <v>0.346</v>
       </c>
       <c r="AR10" s="10" t="n">
-        <v>0.311</v>
+        <v>0.346</v>
       </c>
       <c r="AS10" s="10" t="n">
         <v>0.354</v>
       </c>
       <c r="AT10" s="10" t="n">
-        <v>0.338</v>
+        <v>0.354</v>
       </c>
       <c r="AU10" s="10" t="n">
         <v>0.338</v>
       </c>
       <c r="AV10" s="10" t="n">
-        <v>0.354</v>
+        <v>0.338</v>
       </c>
       <c r="AW10" s="10" t="n">
         <v>0.31</v>
       </c>
       <c r="AX10" s="10" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="AY10" s="10" t="n">
         <v>0.309</v>
       </c>
       <c r="AZ10" s="10" t="n">
-        <v>0.31</v>
+        <v>0.309</v>
       </c>
       <c r="BA10" s="10" t="n">
         <v>0.309</v>
       </c>
       <c r="BB10" s="10" t="n">
-        <v>0.9</v>
+        <v>0.211</v>
       </c>
       <c r="BC10" s="10" t="n">
         <v>0.9</v>
       </c>
       <c r="BD10" s="10" t="n">
-        <v>0.211</v>
+        <v>0.9</v>
       </c>
       <c r="BE10" s="10" t="n">
         <v>6.457</v>
@@ -11463,37 +11463,37 @@
         <v>24.652</v>
       </c>
       <c r="BI10" s="10" t="n">
+        <v>82.837</v>
+      </c>
+      <c r="BJ10" s="10" t="n">
         <v>87.09099999999999</v>
       </c>
-      <c r="BJ10" s="10" t="n">
+      <c r="BK10" s="10" t="n">
         <v>90.652</v>
-      </c>
-      <c r="BK10" s="10" t="n">
-        <v>82.837</v>
       </c>
       <c r="BL10" s="10" t="n">
         <v>92.206</v>
       </c>
       <c r="BM10" s="10" t="n">
+        <v>104.641</v>
+      </c>
+      <c r="BN10" s="10" t="n">
         <v>107.801</v>
       </c>
-      <c r="BN10" s="10" t="n">
+      <c r="BO10" s="10" t="n">
         <v>107.025</v>
-      </c>
-      <c r="BO10" s="10" t="n">
-        <v>104.641</v>
       </c>
       <c r="BP10" s="10" t="n">
         <v>131.72</v>
       </c>
       <c r="BQ10" s="10" t="n">
+        <v>123.148</v>
+      </c>
+      <c r="BR10" s="10" t="n">
         <v>136.432</v>
       </c>
-      <c r="BR10" s="10" t="n">
+      <c r="BS10" s="10" t="n">
         <v>135.05</v>
-      </c>
-      <c r="BS10" s="10" t="n">
-        <v>123.148</v>
       </c>
       <c r="BT10" s="10" t="n">
         <v>148.395</v>
@@ -11590,52 +11590,52 @@
         <v>5.342</v>
       </c>
       <c r="AD11" s="10" t="n">
-        <v>2.672</v>
+        <v>5.342</v>
       </c>
       <c r="AE11" s="10" t="n">
         <v>2.672</v>
       </c>
       <c r="AF11" s="10" t="n">
-        <v>5.342</v>
-      </c>
-      <c r="AQ11" s="10" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="AR11" s="10" t="n">
         <v>2.869</v>
       </c>
       <c r="AS11" s="10" t="n">
         <v>4.551</v>
       </c>
       <c r="AT11" s="10" t="n">
+        <v>9.544</v>
+      </c>
+      <c r="AU11" s="10" t="n">
         <v>9.877000000000001</v>
       </c>
-      <c r="AU11" s="10" t="n">
+      <c r="AV11" s="10" t="n">
         <v>14.27</v>
-      </c>
-      <c r="AV11" s="10" t="n">
-        <v>9.544</v>
       </c>
       <c r="AW11" s="10" t="n">
         <v>14.487</v>
       </c>
       <c r="AX11" s="10" t="n">
+        <v>17.975</v>
+      </c>
+      <c r="AY11" s="10" t="n">
         <v>17.996</v>
       </c>
-      <c r="AY11" s="10" t="n">
+      <c r="AZ11" s="10" t="n">
         <v>22.364</v>
-      </c>
-      <c r="AZ11" s="10" t="n">
-        <v>17.975</v>
       </c>
       <c r="BA11" s="10" t="n">
         <v>22.626</v>
       </c>
       <c r="BB11" s="10" t="n">
+        <v>22.148</v>
+      </c>
+      <c r="BC11" s="10" t="n">
         <v>22.38</v>
       </c>
-      <c r="BC11" s="10" t="n">
+      <c r="BD11" s="10" t="n">
         <v>22.312</v>
-      </c>
-      <c r="BD11" s="10" t="n">
-        <v>22.148</v>
       </c>
       <c r="BE11" s="10" t="n">
         <v>24.003</v>
@@ -11650,37 +11650,37 @@
         <v>41.053</v>
       </c>
       <c r="BI11" s="10" t="n">
+        <v>47.301</v>
+      </c>
+      <c r="BJ11" s="10" t="n">
         <v>47.703</v>
       </c>
-      <c r="BJ11" s="10" t="n">
+      <c r="BK11" s="10" t="n">
         <v>49.29</v>
-      </c>
-      <c r="BK11" s="10" t="n">
-        <v>47.301</v>
       </c>
       <c r="BL11" s="10" t="n">
         <v>49.955</v>
       </c>
       <c r="BM11" s="10" t="n">
+        <v>50.136</v>
+      </c>
+      <c r="BN11" s="10" t="n">
         <v>52.124</v>
       </c>
-      <c r="BN11" s="10" t="n">
+      <c r="BO11" s="10" t="n">
         <v>54.746</v>
-      </c>
-      <c r="BO11" s="10" t="n">
-        <v>50.136</v>
       </c>
       <c r="BP11" s="10" t="n">
         <v>58.323</v>
       </c>
       <c r="BQ11" s="10" t="n">
+        <v>57.197</v>
+      </c>
+      <c r="BR11" s="10" t="n">
         <v>58.908</v>
       </c>
-      <c r="BR11" s="10" t="n">
+      <c r="BS11" s="10" t="n">
         <v>58.067</v>
-      </c>
-      <c r="BS11" s="10" t="n">
-        <v>57.197</v>
       </c>
       <c r="BT11" s="10" t="n">
         <v>58.591</v>
@@ -11777,85 +11777,85 @@
         <v>2388.417</v>
       </c>
       <c r="AD12" s="10" t="n">
+        <v>2378.848</v>
+      </c>
+      <c r="AE12" s="10" t="n">
         <v>2449.762</v>
       </c>
-      <c r="AE12" s="10" t="n">
+      <c r="AF12" s="10" t="n">
         <v>2458.025</v>
-      </c>
-      <c r="AF12" s="10" t="n">
-        <v>2378.848</v>
       </c>
       <c r="AG12" s="10" t="n">
         <v>2533.486</v>
       </c>
       <c r="AH12" s="10" t="n">
+        <v>2534.5</v>
+      </c>
+      <c r="AI12" s="10" t="n">
         <v>2541.45</v>
       </c>
-      <c r="AI12" s="10" t="n">
+      <c r="AJ12" s="10" t="n">
         <v>2499.723</v>
-      </c>
-      <c r="AJ12" s="10" t="n">
-        <v>2534.5</v>
       </c>
       <c r="AK12" s="10" t="n">
         <v>2507.675</v>
       </c>
       <c r="AL12" s="10" t="n">
+        <v>2419.165</v>
+      </c>
+      <c r="AM12" s="10" t="n">
         <v>2425.252</v>
       </c>
-      <c r="AM12" s="10" t="n">
+      <c r="AN12" s="10" t="n">
         <v>2411.904</v>
-      </c>
-      <c r="AN12" s="10" t="n">
-        <v>2419.165</v>
       </c>
       <c r="AO12" s="10" t="n">
         <v>2455.049</v>
       </c>
       <c r="AP12" s="10" t="n">
+        <v>2449.466</v>
+      </c>
+      <c r="AQ12" s="10" t="n">
         <v>2461.07</v>
       </c>
-      <c r="AQ12" s="10" t="n">
+      <c r="AR12" s="10" t="n">
         <v>2503.412</v>
-      </c>
-      <c r="AR12" s="10" t="n">
-        <v>2449.466</v>
       </c>
       <c r="AS12" s="10" t="n">
         <v>2519.063</v>
       </c>
       <c r="AT12" s="10" t="n">
+        <v>2546.585</v>
+      </c>
+      <c r="AU12" s="10" t="n">
         <v>2596.897</v>
       </c>
-      <c r="AU12" s="10" t="n">
+      <c r="AV12" s="10" t="n">
         <v>2543.693</v>
-      </c>
-      <c r="AV12" s="10" t="n">
-        <v>2546.585</v>
       </c>
       <c r="AW12" s="10" t="n">
         <v>2486.753</v>
       </c>
       <c r="AX12" s="10" t="n">
+        <v>2422.603</v>
+      </c>
+      <c r="AY12" s="10" t="n">
         <v>2406.224</v>
       </c>
-      <c r="AY12" s="10" t="n">
+      <c r="AZ12" s="10" t="n">
         <v>2276.961</v>
-      </c>
-      <c r="AZ12" s="10" t="n">
-        <v>2422.603</v>
       </c>
       <c r="BA12" s="10" t="n">
         <v>2256.816</v>
       </c>
       <c r="BB12" s="10" t="n">
+        <v>2223.883</v>
+      </c>
+      <c r="BC12" s="10" t="n">
         <v>2219.731</v>
       </c>
-      <c r="BC12" s="10" t="n">
+      <c r="BD12" s="10" t="n">
         <v>2222.355</v>
-      </c>
-      <c r="BD12" s="10" t="n">
-        <v>2223.883</v>
       </c>
       <c r="BE12" s="10" t="n">
         <v>2285.051</v>
@@ -11870,37 +11870,37 @@
         <v>3369.166</v>
       </c>
       <c r="BI12" s="10" t="n">
+        <v>3430.28</v>
+      </c>
+      <c r="BJ12" s="10" t="n">
         <v>3564.454</v>
       </c>
-      <c r="BJ12" s="10" t="n">
+      <c r="BK12" s="10" t="n">
         <v>3806.945</v>
-      </c>
-      <c r="BK12" s="10" t="n">
-        <v>3430.28</v>
       </c>
       <c r="BL12" s="10" t="n">
         <v>3890.438</v>
       </c>
       <c r="BM12" s="10" t="n">
+        <v>4008.972</v>
+      </c>
+      <c r="BN12" s="10" t="n">
         <v>4021.307</v>
       </c>
-      <c r="BN12" s="10" t="n">
+      <c r="BO12" s="10" t="n">
         <v>4246.817</v>
-      </c>
-      <c r="BO12" s="10" t="n">
-        <v>4008.972</v>
       </c>
       <c r="BP12" s="10" t="n">
         <v>4346.865</v>
       </c>
       <c r="BQ12" s="10" t="n">
+        <v>4275.09</v>
+      </c>
+      <c r="BR12" s="10" t="n">
         <v>4319.425</v>
       </c>
-      <c r="BR12" s="10" t="n">
+      <c r="BS12" s="10" t="n">
         <v>4467.732</v>
-      </c>
-      <c r="BS12" s="10" t="n">
-        <v>4275.09</v>
       </c>
       <c r="BT12" s="10" t="n">
         <v>4437.868</v>
@@ -11997,85 +11997,85 @@
         <v>393.01</v>
       </c>
       <c r="AD13" s="10" t="n">
+        <v>413.619</v>
+      </c>
+      <c r="AE13" s="10" t="n">
         <v>389.251</v>
       </c>
-      <c r="AE13" s="10" t="n">
+      <c r="AF13" s="10" t="n">
         <v>393.881</v>
-      </c>
-      <c r="AF13" s="10" t="n">
-        <v>413.619</v>
       </c>
       <c r="AG13" s="10" t="n">
         <v>396.422</v>
       </c>
       <c r="AH13" s="10" t="n">
+        <v>398.119</v>
+      </c>
+      <c r="AI13" s="10" t="n">
         <v>372.361</v>
       </c>
-      <c r="AI13" s="10" t="n">
+      <c r="AJ13" s="10" t="n">
         <v>375.985</v>
-      </c>
-      <c r="AJ13" s="10" t="n">
-        <v>398.119</v>
       </c>
       <c r="AK13" s="10" t="n">
         <v>347.206</v>
       </c>
       <c r="AL13" s="10" t="n">
+        <v>390.971</v>
+      </c>
+      <c r="AM13" s="10" t="n">
         <v>403.52</v>
       </c>
-      <c r="AM13" s="10" t="n">
+      <c r="AN13" s="10" t="n">
         <v>476.121</v>
-      </c>
-      <c r="AN13" s="10" t="n">
-        <v>390.971</v>
       </c>
       <c r="AO13" s="10" t="n">
         <v>562.251</v>
       </c>
       <c r="AP13" s="10" t="n">
+        <v>660.189</v>
+      </c>
+      <c r="AQ13" s="10" t="n">
         <v>684.2140000000001</v>
       </c>
-      <c r="AQ13" s="10" t="n">
+      <c r="AR13" s="10" t="n">
         <v>834.925</v>
-      </c>
-      <c r="AR13" s="10" t="n">
-        <v>660.189</v>
       </c>
       <c r="AS13" s="10" t="n">
         <v>932.4</v>
       </c>
       <c r="AT13" s="10" t="n">
+        <v>975.737</v>
+      </c>
+      <c r="AU13" s="10" t="n">
         <v>972.151</v>
       </c>
-      <c r="AU13" s="10" t="n">
+      <c r="AV13" s="10" t="n">
         <v>1028.042</v>
-      </c>
-      <c r="AV13" s="10" t="n">
-        <v>975.737</v>
       </c>
       <c r="AW13" s="10" t="n">
         <v>987.336</v>
       </c>
       <c r="AX13" s="10" t="n">
+        <v>1005.335</v>
+      </c>
+      <c r="AY13" s="10" t="n">
         <v>966.896</v>
       </c>
-      <c r="AY13" s="10" t="n">
+      <c r="AZ13" s="10" t="n">
         <v>957.261</v>
-      </c>
-      <c r="AZ13" s="10" t="n">
-        <v>1005.335</v>
       </c>
       <c r="BA13" s="10" t="n">
         <v>930.145</v>
       </c>
       <c r="BB13" s="10" t="n">
+        <v>910.802</v>
+      </c>
+      <c r="BC13" s="10" t="n">
         <v>880.783</v>
       </c>
-      <c r="BC13" s="10" t="n">
+      <c r="BD13" s="10" t="n">
         <v>865.679</v>
-      </c>
-      <c r="BD13" s="10" t="n">
-        <v>910.802</v>
       </c>
       <c r="BE13" s="10" t="n">
         <v>928.873</v>
@@ -12090,37 +12090,37 @@
         <v>1211.05</v>
       </c>
       <c r="BI13" s="10" t="n">
+        <v>1332.695</v>
+      </c>
+      <c r="BJ13" s="10" t="n">
         <v>1289.813</v>
       </c>
-      <c r="BJ13" s="10" t="n">
+      <c r="BK13" s="10" t="n">
         <v>1271.603</v>
-      </c>
-      <c r="BK13" s="10" t="n">
-        <v>1332.695</v>
       </c>
       <c r="BL13" s="10" t="n">
         <v>1338.442</v>
       </c>
       <c r="BM13" s="10" t="n">
+        <v>1315.455</v>
+      </c>
+      <c r="BN13" s="10" t="n">
         <v>1301.426</v>
       </c>
-      <c r="BN13" s="10" t="n">
+      <c r="BO13" s="10" t="n">
         <v>1279.989</v>
-      </c>
-      <c r="BO13" s="10" t="n">
-        <v>1315.455</v>
       </c>
       <c r="BP13" s="10" t="n">
         <v>1248.338</v>
       </c>
       <c r="BQ13" s="10" t="n">
+        <v>1228.133</v>
+      </c>
+      <c r="BR13" s="10" t="n">
         <v>1187.271</v>
       </c>
-      <c r="BR13" s="10" t="n">
+      <c r="BS13" s="10" t="n">
         <v>1169.869</v>
-      </c>
-      <c r="BS13" s="10" t="n">
-        <v>1228.133</v>
       </c>
       <c r="BT13" s="10" t="n">
         <v>1235.152</v>
@@ -12217,85 +12217,85 @@
         <v>1649.103</v>
       </c>
       <c r="AD14" s="10" t="n">
+        <v>1629.66</v>
+      </c>
+      <c r="AE14" s="10" t="n">
         <v>1598.492</v>
       </c>
-      <c r="AE14" s="10" t="n">
+      <c r="AF14" s="10" t="n">
         <v>1583.087</v>
-      </c>
-      <c r="AF14" s="10" t="n">
-        <v>1629.66</v>
       </c>
       <c r="AG14" s="10" t="n">
         <v>1563.333</v>
       </c>
       <c r="AH14" s="10" t="n">
+        <v>1571.751</v>
+      </c>
+      <c r="AI14" s="10" t="n">
         <v>1561.696</v>
       </c>
-      <c r="AI14" s="10" t="n">
+      <c r="AJ14" s="10" t="n">
         <v>1548.818</v>
-      </c>
-      <c r="AJ14" s="10" t="n">
-        <v>1571.751</v>
       </c>
       <c r="AK14" s="10" t="n">
         <v>1548.749</v>
       </c>
       <c r="AL14" s="10" t="n">
+        <v>1555.523</v>
+      </c>
+      <c r="AM14" s="10" t="n">
         <v>1539.892</v>
       </c>
-      <c r="AM14" s="10" t="n">
+      <c r="AN14" s="10" t="n">
         <v>1518.33</v>
-      </c>
-      <c r="AN14" s="10" t="n">
-        <v>1555.523</v>
       </c>
       <c r="AO14" s="10" t="n">
         <v>1496.516</v>
       </c>
       <c r="AP14" s="10" t="n">
+        <v>1477.385</v>
+      </c>
+      <c r="AQ14" s="10" t="n">
         <v>1443.895</v>
       </c>
-      <c r="AQ14" s="10" t="n">
+      <c r="AR14" s="10" t="n">
         <v>1404.065</v>
-      </c>
-      <c r="AR14" s="10" t="n">
-        <v>1477.385</v>
       </c>
       <c r="AS14" s="10" t="n">
         <v>1400.459</v>
       </c>
       <c r="AT14" s="10" t="n">
+        <v>1358.018</v>
+      </c>
+      <c r="AU14" s="10" t="n">
         <v>1339.865</v>
       </c>
-      <c r="AU14" s="10" t="n">
+      <c r="AV14" s="10" t="n">
         <v>1296.104</v>
-      </c>
-      <c r="AV14" s="10" t="n">
-        <v>1358.018</v>
       </c>
       <c r="AW14" s="10" t="n">
         <v>1252.168</v>
       </c>
       <c r="AX14" s="10" t="n">
+        <v>1126.912</v>
+      </c>
+      <c r="AY14" s="10" t="n">
         <v>1057.004</v>
       </c>
-      <c r="AY14" s="10" t="n">
+      <c r="AZ14" s="10" t="n">
         <v>954.506</v>
-      </c>
-      <c r="AZ14" s="10" t="n">
-        <v>1126.912</v>
       </c>
       <c r="BA14" s="10" t="n">
         <v>909.832</v>
       </c>
       <c r="BB14" s="10" t="n">
+        <v>856.087</v>
+      </c>
+      <c r="BC14" s="10" t="n">
         <v>832.607</v>
       </c>
-      <c r="BC14" s="10" t="n">
+      <c r="BD14" s="10" t="n">
         <v>790.222</v>
-      </c>
-      <c r="BD14" s="10" t="n">
-        <v>856.087</v>
       </c>
       <c r="BE14" s="10" t="n">
         <v>827.0359999999999</v>
@@ -12310,37 +12310,37 @@
         <v>1592.911</v>
       </c>
       <c r="BI14" s="10" t="n">
+        <v>1616.242</v>
+      </c>
+      <c r="BJ14" s="10" t="n">
         <v>1725.033</v>
       </c>
-      <c r="BJ14" s="10" t="n">
+      <c r="BK14" s="10" t="n">
         <v>1805.862</v>
-      </c>
-      <c r="BK14" s="10" t="n">
-        <v>1616.242</v>
       </c>
       <c r="BL14" s="10" t="n">
         <v>1880.529</v>
       </c>
       <c r="BM14" s="10" t="n">
+        <v>1931.196</v>
+      </c>
+      <c r="BN14" s="10" t="n">
         <v>1953.64</v>
       </c>
-      <c r="BN14" s="10" t="n">
+      <c r="BO14" s="10" t="n">
         <v>1981.338</v>
-      </c>
-      <c r="BO14" s="10" t="n">
-        <v>1931.196</v>
       </c>
       <c r="BP14" s="10" t="n">
         <v>2135.428</v>
       </c>
       <c r="BQ14" s="10" t="n">
+        <v>2027.82</v>
+      </c>
+      <c r="BR14" s="10" t="n">
         <v>2202.965</v>
       </c>
-      <c r="BR14" s="10" t="n">
+      <c r="BS14" s="10" t="n">
         <v>2243.103</v>
-      </c>
-      <c r="BS14" s="10" t="n">
-        <v>2027.82</v>
       </c>
       <c r="BT14" s="10" t="n">
         <v>2328.555</v>
@@ -12447,85 +12447,85 @@
         <v>34905.995</v>
       </c>
       <c r="AD16" s="10" t="n">
+        <v>35851.974</v>
+      </c>
+      <c r="AE16" s="10" t="n">
         <v>47175.955</v>
       </c>
-      <c r="AE16" s="10" t="n">
+      <c r="AF16" s="10" t="n">
         <v>51196.389</v>
-      </c>
-      <c r="AF16" s="10" t="n">
-        <v>35851.974</v>
       </c>
       <c r="AG16" s="10" t="n">
         <v>37753.504</v>
       </c>
       <c r="AH16" s="10" t="n">
+        <v>37811.954</v>
+      </c>
+      <c r="AI16" s="10" t="n">
         <v>39845.014</v>
       </c>
-      <c r="AI16" s="10" t="n">
+      <c r="AJ16" s="10" t="n">
         <v>40164.172</v>
-      </c>
-      <c r="AJ16" s="10" t="n">
-        <v>37811.954</v>
       </c>
       <c r="AK16" s="10" t="n">
         <v>44595.632</v>
       </c>
       <c r="AL16" s="10" t="n">
+        <v>51628.365</v>
+      </c>
+      <c r="AM16" s="10" t="n">
         <v>51213.888</v>
       </c>
-      <c r="AM16" s="10" t="n">
+      <c r="AN16" s="10" t="n">
         <v>53423.532</v>
-      </c>
-      <c r="AN16" s="10" t="n">
-        <v>51628.365</v>
       </c>
       <c r="AO16" s="10" t="n">
         <v>56408.676</v>
       </c>
       <c r="AP16" s="10" t="n">
+        <v>63373.974</v>
+      </c>
+      <c r="AQ16" s="10" t="n">
         <v>71862.876</v>
       </c>
-      <c r="AQ16" s="10" t="n">
+      <c r="AR16" s="10" t="n">
         <v>66107.50999999999</v>
-      </c>
-      <c r="AR16" s="10" t="n">
-        <v>63373.974</v>
       </c>
       <c r="AS16" s="10" t="n">
         <v>72410.78200000001</v>
       </c>
       <c r="AT16" s="10" t="n">
+        <v>77986.981</v>
+      </c>
+      <c r="AU16" s="10" t="n">
         <v>80420.71799999999</v>
       </c>
-      <c r="AU16" s="10" t="n">
+      <c r="AV16" s="10" t="n">
         <v>64165.773</v>
-      </c>
-      <c r="AV16" s="10" t="n">
-        <v>77986.981</v>
       </c>
       <c r="AW16" s="10" t="n">
         <v>63538.624</v>
       </c>
       <c r="AX16" s="10" t="n">
+        <v>67722.173</v>
+      </c>
+      <c r="AY16" s="10" t="n">
         <v>74263.848</v>
       </c>
-      <c r="AY16" s="10" t="n">
+      <c r="AZ16" s="10" t="n">
         <v>44214.977</v>
-      </c>
-      <c r="AZ16" s="10" t="n">
-        <v>67722.173</v>
       </c>
       <c r="BA16" s="10" t="n">
         <v>50786.317</v>
       </c>
       <c r="BB16" s="10" t="n">
+        <v>53129.104</v>
+      </c>
+      <c r="BC16" s="10" t="n">
         <v>52407.734</v>
       </c>
-      <c r="BC16" s="10" t="n">
+      <c r="BD16" s="10" t="n">
         <v>56632.955</v>
-      </c>
-      <c r="BD16" s="10" t="n">
-        <v>53129.104</v>
       </c>
       <c r="BE16" s="10" t="n">
         <v>60166.942</v>
@@ -12540,37 +12540,37 @@
         <v>90545.04300000001</v>
       </c>
       <c r="BI16" s="10" t="n">
+        <v>108432.728</v>
+      </c>
+      <c r="BJ16" s="10" t="n">
         <v>135448.318</v>
       </c>
-      <c r="BJ16" s="10" t="n">
+      <c r="BK16" s="10" t="n">
         <v>139723.91</v>
-      </c>
-      <c r="BK16" s="10" t="n">
-        <v>108432.728</v>
       </c>
       <c r="BL16" s="10" t="n">
         <v>123788.774</v>
       </c>
       <c r="BM16" s="10" t="n">
+        <v>102760.014</v>
+      </c>
+      <c r="BN16" s="10" t="n">
         <v>121555.319</v>
       </c>
-      <c r="BN16" s="10" t="n">
+      <c r="BO16" s="10" t="n">
         <v>114184.831</v>
-      </c>
-      <c r="BO16" s="10" t="n">
-        <v>102760.014</v>
       </c>
       <c r="BP16" s="10" t="n">
         <v>147228.082</v>
       </c>
       <c r="BQ16" s="10" t="n">
+        <v>151587.225</v>
+      </c>
+      <c r="BR16" s="10" t="n">
         <v>138329.843</v>
       </c>
-      <c r="BR16" s="10" t="n">
+      <c r="BS16" s="10" t="n">
         <v>131137.071</v>
-      </c>
-      <c r="BS16" s="10" t="n">
-        <v>151587.225</v>
       </c>
       <c r="BT16" s="10" t="n">
         <v>125730.772</v>
@@ -12667,85 +12667,85 @@
         <v>532.823</v>
       </c>
       <c r="AD17" s="10" t="n">
+        <v>552.25</v>
+      </c>
+      <c r="AE17" s="10" t="n">
         <v>577.326</v>
       </c>
-      <c r="AE17" s="10" t="n">
+      <c r="AF17" s="10" t="n">
         <v>604.033</v>
-      </c>
-      <c r="AF17" s="10" t="n">
-        <v>552.25</v>
       </c>
       <c r="AG17" s="10" t="n">
         <v>642.602</v>
       </c>
       <c r="AH17" s="10" t="n">
+        <v>662.178</v>
+      </c>
+      <c r="AI17" s="10" t="n">
         <v>694.236</v>
       </c>
-      <c r="AI17" s="10" t="n">
+      <c r="AJ17" s="10" t="n">
         <v>715.588</v>
-      </c>
-      <c r="AJ17" s="10" t="n">
-        <v>662.178</v>
       </c>
       <c r="AK17" s="10" t="n">
         <v>761.504</v>
       </c>
       <c r="AL17" s="10" t="n">
+        <v>782.641</v>
+      </c>
+      <c r="AM17" s="10" t="n">
         <v>802.02</v>
       </c>
-      <c r="AM17" s="10" t="n">
+      <c r="AN17" s="10" t="n">
         <v>831.033</v>
-      </c>
-      <c r="AN17" s="10" t="n">
-        <v>782.641</v>
       </c>
       <c r="AO17" s="10" t="n">
         <v>882.4160000000001</v>
       </c>
       <c r="AP17" s="10" t="n">
+        <v>932.376</v>
+      </c>
+      <c r="AQ17" s="10" t="n">
         <v>950.0309999999999</v>
       </c>
-      <c r="AQ17" s="10" t="n">
+      <c r="AR17" s="10" t="n">
         <v>1080.982</v>
-      </c>
-      <c r="AR17" s="10" t="n">
-        <v>932.376</v>
       </c>
       <c r="AS17" s="10" t="n">
         <v>1116.796</v>
       </c>
       <c r="AT17" s="10" t="n">
+        <v>1173.389</v>
+      </c>
+      <c r="AU17" s="10" t="n">
         <v>1193.187</v>
       </c>
-      <c r="AU17" s="10" t="n">
+      <c r="AV17" s="10" t="n">
         <v>1330.834</v>
-      </c>
-      <c r="AV17" s="10" t="n">
-        <v>1173.389</v>
       </c>
       <c r="AW17" s="10" t="n">
         <v>1311.229</v>
       </c>
       <c r="AX17" s="10" t="n">
+        <v>1335.888</v>
+      </c>
+      <c r="AY17" s="10" t="n">
         <v>1278.48</v>
       </c>
-      <c r="AY17" s="10" t="n">
+      <c r="AZ17" s="10" t="n">
         <v>1268.744</v>
-      </c>
-      <c r="AZ17" s="10" t="n">
-        <v>1335.888</v>
       </c>
       <c r="BA17" s="10" t="n">
         <v>1250.876</v>
       </c>
       <c r="BB17" s="10" t="n">
+        <v>1243.745</v>
+      </c>
+      <c r="BC17" s="10" t="n">
         <v>1218.707</v>
       </c>
-      <c r="BC17" s="10" t="n">
+      <c r="BD17" s="10" t="n">
         <v>1197.431</v>
-      </c>
-      <c r="BD17" s="10" t="n">
-        <v>1243.745</v>
       </c>
       <c r="BE17" s="10" t="n">
         <v>1210.822</v>
@@ -12760,37 +12760,37 @@
         <v>1520.572</v>
       </c>
       <c r="BI17" s="10" t="n">
+        <v>1566.554</v>
+      </c>
+      <c r="BJ17" s="10" t="n">
         <v>1612.318</v>
       </c>
-      <c r="BJ17" s="10" t="n">
+      <c r="BK17" s="10" t="n">
         <v>1661.602</v>
-      </c>
-      <c r="BK17" s="10" t="n">
-        <v>1566.554</v>
       </c>
       <c r="BL17" s="10" t="n">
         <v>2709.931</v>
       </c>
       <c r="BM17" s="10" t="n">
+        <v>1624.876</v>
+      </c>
+      <c r="BN17" s="10" t="n">
         <v>1647.86</v>
       </c>
-      <c r="BN17" s="10" t="n">
+      <c r="BO17" s="10" t="n">
         <v>1603.134</v>
-      </c>
-      <c r="BO17" s="10" t="n">
-        <v>1624.876</v>
       </c>
       <c r="BP17" s="10" t="n">
         <v>1622.169</v>
       </c>
       <c r="BQ17" s="10" t="n">
+        <v>1521.765</v>
+      </c>
+      <c r="BR17" s="10" t="n">
         <v>1509.161</v>
       </c>
-      <c r="BR17" s="10" t="n">
+      <c r="BS17" s="10" t="n">
         <v>1446.49</v>
-      </c>
-      <c r="BS17" s="10" t="n">
-        <v>1521.765</v>
       </c>
       <c r="BT17" s="10" t="n">
         <v>1474.355</v>
@@ -12809,85 +12809,85 @@
         <v>2968.788</v>
       </c>
       <c r="AD18" s="10" t="n">
+        <v>2805.204</v>
+      </c>
+      <c r="AE18" s="10" t="n">
         <v>4349.089</v>
       </c>
-      <c r="AE18" s="10" t="n">
+      <c r="AF18" s="10" t="n">
         <v>4364.484</v>
-      </c>
-      <c r="AF18" s="10" t="n">
-        <v>2805.204</v>
       </c>
       <c r="AG18" s="10" t="n">
         <v>4294.922</v>
       </c>
       <c r="AH18" s="10" t="n">
+        <v>3952.881</v>
+      </c>
+      <c r="AI18" s="10" t="n">
         <v>4500.308</v>
       </c>
-      <c r="AI18" s="10" t="n">
+      <c r="AJ18" s="10" t="n">
         <v>4548.246</v>
-      </c>
-      <c r="AJ18" s="10" t="n">
-        <v>3952.881</v>
       </c>
       <c r="AK18" s="10" t="n">
         <v>4253.937</v>
       </c>
       <c r="AL18" s="10" t="n">
+        <v>3323.505</v>
+      </c>
+      <c r="AM18" s="10" t="n">
         <v>5665.214</v>
       </c>
-      <c r="AM18" s="10" t="n">
+      <c r="AN18" s="10" t="n">
         <v>5753.368</v>
-      </c>
-      <c r="AN18" s="10" t="n">
-        <v>3323.505</v>
       </c>
       <c r="AO18" s="10" t="n">
         <v>5789.491</v>
       </c>
       <c r="AP18" s="10" t="n">
+        <v>5944.629</v>
+      </c>
+      <c r="AQ18" s="10" t="n">
         <v>3850.447</v>
       </c>
-      <c r="AQ18" s="10" t="n">
+      <c r="AR18" s="10" t="n">
         <v>3817.485</v>
-      </c>
-      <c r="AR18" s="10" t="n">
-        <v>5944.629</v>
       </c>
       <c r="AS18" s="10" t="n">
         <v>3815.392</v>
       </c>
       <c r="AT18" s="10" t="n">
+        <v>3971.336</v>
+      </c>
+      <c r="AU18" s="10" t="n">
         <v>2131.543</v>
       </c>
-      <c r="AU18" s="10" t="n">
+      <c r="AV18" s="10" t="n">
         <v>2088.264</v>
-      </c>
-      <c r="AV18" s="10" t="n">
-        <v>3971.336</v>
       </c>
       <c r="AW18" s="10" t="n">
         <v>2116.67</v>
       </c>
       <c r="AX18" s="10" t="n">
+        <v>2105.276</v>
+      </c>
+      <c r="AY18" s="10" t="n">
         <v>2314.27</v>
       </c>
-      <c r="AY18" s="10" t="n">
+      <c r="AZ18" s="10" t="n">
         <v>2410.435</v>
-      </c>
-      <c r="AZ18" s="10" t="n">
-        <v>2105.276</v>
       </c>
       <c r="BA18" s="10" t="n">
         <v>2476.048</v>
       </c>
       <c r="BB18" s="10" t="n">
+        <v>2381.958</v>
+      </c>
+      <c r="BC18" s="10" t="n">
         <v>2323.122</v>
       </c>
-      <c r="BC18" s="10" t="n">
+      <c r="BD18" s="10" t="n">
         <v>2071.109</v>
-      </c>
-      <c r="BD18" s="10" t="n">
-        <v>2381.958</v>
       </c>
       <c r="BE18" s="10" t="n">
         <v>2040.633</v>
@@ -12899,37 +12899,37 @@
         <v>812.932</v>
       </c>
       <c r="BI18" s="10" t="n">
+        <v>867.311</v>
+      </c>
+      <c r="BJ18" s="10" t="n">
         <v>857.1</v>
       </c>
-      <c r="BJ18" s="10" t="n">
+      <c r="BK18" s="10" t="n">
         <v>1061.882</v>
-      </c>
-      <c r="BK18" s="10" t="n">
-        <v>867.311</v>
       </c>
       <c r="BL18" s="10" t="n">
         <v>902.817</v>
       </c>
       <c r="BM18" s="10" t="n">
+        <v>826.351</v>
+      </c>
+      <c r="BN18" s="10" t="n">
         <v>814.397</v>
       </c>
-      <c r="BN18" s="10" t="n">
+      <c r="BO18" s="10" t="n">
         <v>798.643</v>
-      </c>
-      <c r="BO18" s="10" t="n">
-        <v>826.351</v>
       </c>
       <c r="BP18" s="10" t="n">
         <v>754.8440000000001</v>
       </c>
       <c r="BQ18" s="10" t="n">
+        <v>695.827</v>
+      </c>
+      <c r="BR18" s="10" t="n">
         <v>736.3630000000001</v>
       </c>
-      <c r="BR18" s="10" t="n">
+      <c r="BS18" s="10" t="n">
         <v>645.1609999999999</v>
-      </c>
-      <c r="BS18" s="10" t="n">
-        <v>695.827</v>
       </c>
       <c r="BT18" s="10" t="n">
         <v>639.396</v>
@@ -13196,85 +13196,85 @@
         <v>11.305</v>
       </c>
       <c r="AD21" s="10" t="n">
+        <v>11.553</v>
+      </c>
+      <c r="AE21" s="10" t="n">
         <v>11.885</v>
       </c>
-      <c r="AE21" s="10" t="n">
+      <c r="AF21" s="10" t="n">
         <v>11.904</v>
-      </c>
-      <c r="AF21" s="10" t="n">
-        <v>11.553</v>
       </c>
       <c r="AG21" s="10" t="n">
         <v>11.694</v>
       </c>
       <c r="AH21" s="10" t="n">
+        <v>12.061</v>
+      </c>
+      <c r="AI21" s="10" t="n">
         <v>11.868</v>
       </c>
-      <c r="AI21" s="10" t="n">
+      <c r="AJ21" s="10" t="n">
         <v>11.975</v>
-      </c>
-      <c r="AJ21" s="10" t="n">
-        <v>12.061</v>
       </c>
       <c r="AK21" s="10" t="n">
         <v>11.313</v>
       </c>
       <c r="AL21" s="10" t="n">
+        <v>11.675</v>
+      </c>
+      <c r="AM21" s="10" t="n">
         <v>12.275</v>
       </c>
-      <c r="AM21" s="10" t="n">
+      <c r="AN21" s="10" t="n">
         <v>12.61</v>
-      </c>
-      <c r="AN21" s="10" t="n">
-        <v>11.675</v>
       </c>
       <c r="AO21" s="10" t="n">
         <v>12.767</v>
       </c>
       <c r="AP21" s="10" t="n">
+        <v>13.216</v>
+      </c>
+      <c r="AQ21" s="10" t="n">
         <v>12.614</v>
       </c>
-      <c r="AQ21" s="10" t="n">
+      <c r="AR21" s="10" t="n">
         <v>12.804</v>
-      </c>
-      <c r="AR21" s="10" t="n">
-        <v>13.216</v>
       </c>
       <c r="AS21" s="10" t="n">
         <v>12.828</v>
       </c>
       <c r="AT21" s="10" t="n">
+        <v>12.746</v>
+      </c>
+      <c r="AU21" s="10" t="n">
         <v>12.871</v>
       </c>
-      <c r="AU21" s="10" t="n">
+      <c r="AV21" s="10" t="n">
         <v>12.452</v>
-      </c>
-      <c r="AV21" s="10" t="n">
-        <v>12.746</v>
       </c>
       <c r="AW21" s="10" t="n">
         <v>12.948</v>
       </c>
       <c r="AX21" s="10" t="n">
+        <v>12.753</v>
+      </c>
+      <c r="AY21" s="10" t="n">
         <v>12.799</v>
       </c>
-      <c r="AY21" s="10" t="n">
+      <c r="AZ21" s="10" t="n">
         <v>13.142</v>
-      </c>
-      <c r="AZ21" s="10" t="n">
-        <v>12.753</v>
       </c>
       <c r="BA21" s="10" t="n">
         <v>13.687</v>
       </c>
       <c r="BB21" s="10" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="BC21" s="10" t="n">
         <v>17.286</v>
       </c>
-      <c r="BC21" s="10" t="n">
+      <c r="BD21" s="10" t="n">
         <v>16.694</v>
-      </c>
-      <c r="BD21" s="10" t="n">
-        <v>13.35</v>
       </c>
       <c r="BE21" s="10" t="n">
         <v>15.801</v>
@@ -13289,37 +13289,37 @@
         <v>12.409</v>
       </c>
       <c r="BI21" s="10" t="n">
+        <v>13.688</v>
+      </c>
+      <c r="BJ21" s="10" t="n">
         <v>13.729</v>
       </c>
-      <c r="BJ21" s="10" t="n">
+      <c r="BK21" s="10" t="n">
         <v>15.097</v>
-      </c>
-      <c r="BK21" s="10" t="n">
-        <v>13.688</v>
       </c>
       <c r="BL21" s="10" t="n">
         <v>14.654</v>
       </c>
       <c r="BM21" s="10" t="n">
+        <v>14.373</v>
+      </c>
+      <c r="BN21" s="10" t="n">
         <v>14.185</v>
       </c>
-      <c r="BN21" s="10" t="n">
+      <c r="BO21" s="10" t="n">
         <v>14.594</v>
-      </c>
-      <c r="BO21" s="10" t="n">
-        <v>14.373</v>
       </c>
       <c r="BP21" s="10" t="n">
         <v>12.626</v>
       </c>
       <c r="BQ21" s="10" t="n">
+        <v>13.023</v>
+      </c>
+      <c r="BR21" s="10" t="n">
         <v>13.326</v>
       </c>
-      <c r="BR21" s="10" t="n">
+      <c r="BS21" s="10" t="n">
         <v>13.281</v>
-      </c>
-      <c r="BS21" s="10" t="n">
-        <v>13.023</v>
       </c>
       <c r="BT21" s="10" t="n">
         <v>13.046</v>
@@ -13331,47 +13331,47 @@
           <t>FMI</t>
         </is>
       </c>
-      <c r="AP22" s="10" t="n">
+      <c r="AQ22" s="10" t="n">
         <v>825.544</v>
       </c>
-      <c r="AQ22" s="10" t="n">
+      <c r="AR22" s="10" t="n">
         <v>891.0410000000001</v>
       </c>
       <c r="AS22" s="10" t="n">
         <v>1872.981</v>
       </c>
       <c r="AT22" s="10" t="n">
+        <v>1908.41</v>
+      </c>
+      <c r="AU22" s="10" t="n">
         <v>3134.044</v>
       </c>
-      <c r="AU22" s="10" t="n">
+      <c r="AV22" s="10" t="n">
         <v>5040.084</v>
-      </c>
-      <c r="AV22" s="10" t="n">
-        <v>1908.41</v>
       </c>
       <c r="AW22" s="10" t="n">
         <v>6897.342</v>
       </c>
       <c r="AX22" s="10" t="n">
+        <v>9616.444</v>
+      </c>
+      <c r="AY22" s="10" t="n">
         <v>13191.321</v>
       </c>
-      <c r="AY22" s="10" t="n">
+      <c r="AZ22" s="10" t="n">
         <v>18417.506</v>
-      </c>
-      <c r="AZ22" s="10" t="n">
-        <v>9616.444</v>
       </c>
       <c r="BA22" s="10" t="n">
         <v>24534.229</v>
       </c>
       <c r="BB22" s="10" t="n">
+        <v>29654.092</v>
+      </c>
+      <c r="BC22" s="10" t="n">
         <v>35363.508</v>
       </c>
-      <c r="BC22" s="10" t="n">
+      <c r="BD22" s="10" t="n">
         <v>36549.964</v>
-      </c>
-      <c r="BD22" s="10" t="n">
-        <v>29654.092</v>
       </c>
       <c r="BE22" s="10" t="n">
         <v>37826.16</v>
@@ -13386,37 +13386,37 @@
         <v>26213.968</v>
       </c>
       <c r="BI22" s="10" t="n">
+        <v>21752.236</v>
+      </c>
+      <c r="BJ22" s="10" t="n">
         <v>16266.774</v>
       </c>
-      <c r="BJ22" s="10" t="n">
+      <c r="BK22" s="10" t="n">
         <v>13563.823</v>
-      </c>
-      <c r="BK22" s="10" t="n">
-        <v>21752.236</v>
       </c>
       <c r="BL22" s="10" t="n">
         <v>10144.747</v>
       </c>
       <c r="BM22" s="10" t="n">
+        <v>8720.124</v>
+      </c>
+      <c r="BN22" s="10" t="n">
         <v>6726.601</v>
       </c>
-      <c r="BN22" s="10" t="n">
+      <c r="BO22" s="10" t="n">
         <v>6672.556</v>
-      </c>
-      <c r="BO22" s="10" t="n">
-        <v>8720.124</v>
       </c>
       <c r="BP22" s="10" t="n">
         <v>5686.654</v>
       </c>
       <c r="BQ22" s="10" t="n">
+        <v>6488.388</v>
+      </c>
+      <c r="BR22" s="10" t="n">
         <v>9329.125</v>
       </c>
-      <c r="BR22" s="10" t="n">
+      <c r="BS22" s="10" t="n">
         <v>10731.841</v>
-      </c>
-      <c r="BS22" s="10" t="n">
-        <v>6488.388</v>
       </c>
       <c r="BT22" s="10" t="n">
         <v>11622.991</v>
@@ -13513,85 +13513,85 @@
         <v>24.479</v>
       </c>
       <c r="AD23" s="10" t="n">
+        <v>22.556</v>
+      </c>
+      <c r="AE23" s="10" t="n">
         <v>23.514</v>
       </c>
-      <c r="AE23" s="10" t="n">
+      <c r="AF23" s="10" t="n">
         <v>24.363</v>
-      </c>
-      <c r="AF23" s="10" t="n">
-        <v>22.556</v>
       </c>
       <c r="AG23" s="10" t="n">
         <v>26.941</v>
       </c>
       <c r="AH23" s="10" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="AI23" s="10" t="n">
         <v>25.751</v>
       </c>
-      <c r="AI23" s="10" t="n">
+      <c r="AJ23" s="10" t="n">
         <v>26.359</v>
-      </c>
-      <c r="AJ23" s="10" t="n">
-        <v>25.03</v>
       </c>
       <c r="AK23" s="10" t="n">
         <v>28.156</v>
       </c>
       <c r="AL23" s="10" t="n">
+        <v>28.481</v>
+      </c>
+      <c r="AM23" s="10" t="n">
         <v>30.607</v>
       </c>
-      <c r="AM23" s="10" t="n">
+      <c r="AN23" s="10" t="n">
         <v>32.288</v>
-      </c>
-      <c r="AN23" s="10" t="n">
-        <v>28.481</v>
       </c>
       <c r="AO23" s="10" t="n">
         <v>36.519</v>
       </c>
       <c r="AP23" s="10" t="n">
+        <v>35.981</v>
+      </c>
+      <c r="AQ23" s="10" t="n">
         <v>37.255</v>
       </c>
-      <c r="AQ23" s="10" t="n">
+      <c r="AR23" s="10" t="n">
         <v>36.95</v>
-      </c>
-      <c r="AR23" s="10" t="n">
-        <v>35.981</v>
       </c>
       <c r="AS23" s="10" t="n">
         <v>45.402</v>
       </c>
       <c r="AT23" s="10" t="n">
+        <v>50.844</v>
+      </c>
+      <c r="AU23" s="10" t="n">
         <v>49.154</v>
       </c>
-      <c r="AU23" s="10" t="n">
+      <c r="AV23" s="10" t="n">
         <v>53.23</v>
-      </c>
-      <c r="AV23" s="10" t="n">
-        <v>50.844</v>
       </c>
       <c r="AW23" s="10" t="n">
         <v>58.719</v>
       </c>
       <c r="AX23" s="10" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="AY23" s="10" t="n">
         <v>70.658</v>
       </c>
-      <c r="AY23" s="10" t="n">
+      <c r="AZ23" s="10" t="n">
         <v>73.319</v>
-      </c>
-      <c r="AZ23" s="10" t="n">
-        <v>58.3</v>
       </c>
       <c r="BA23" s="10" t="n">
         <v>75.17400000000001</v>
       </c>
       <c r="BB23" s="10" t="n">
+        <v>77.904</v>
+      </c>
+      <c r="BC23" s="10" t="n">
         <v>80.407</v>
       </c>
-      <c r="BC23" s="10" t="n">
+      <c r="BD23" s="10" t="n">
         <v>85.718</v>
-      </c>
-      <c r="BD23" s="10" t="n">
-        <v>77.904</v>
       </c>
       <c r="BE23" s="10" t="n">
         <v>94.848</v>
@@ -13606,37 +13606,37 @@
         <v>173.946</v>
       </c>
       <c r="BI23" s="10" t="n">
+        <v>180.774</v>
+      </c>
+      <c r="BJ23" s="10" t="n">
         <v>188.288</v>
       </c>
-      <c r="BJ23" s="10" t="n">
+      <c r="BK23" s="10" t="n">
         <v>186.23</v>
-      </c>
-      <c r="BK23" s="10" t="n">
-        <v>180.774</v>
       </c>
       <c r="BL23" s="10" t="n">
         <v>186.077</v>
       </c>
       <c r="BM23" s="10" t="n">
+        <v>195.563</v>
+      </c>
+      <c r="BN23" s="10" t="n">
         <v>194.699</v>
       </c>
-      <c r="BN23" s="10" t="n">
+      <c r="BO23" s="10" t="n">
         <v>214.054</v>
-      </c>
-      <c r="BO23" s="10" t="n">
-        <v>195.563</v>
       </c>
       <c r="BP23" s="10" t="n">
         <v>218.05</v>
       </c>
       <c r="BQ23" s="10" t="n">
+        <v>207.226</v>
+      </c>
+      <c r="BR23" s="10" t="n">
         <v>203.109</v>
       </c>
-      <c r="BR23" s="10" t="n">
+      <c r="BS23" s="10" t="n">
         <v>199.548</v>
-      </c>
-      <c r="BS23" s="10" t="n">
-        <v>207.226</v>
       </c>
       <c r="BT23" s="10" t="n">
         <v>200.013</v>
@@ -13733,85 +13733,85 @@
         <v>9875.093000000001</v>
       </c>
       <c r="AD24" s="10" t="n">
+        <v>9473.919</v>
+      </c>
+      <c r="AE24" s="10" t="n">
         <v>9230.136</v>
       </c>
-      <c r="AE24" s="10" t="n">
+      <c r="AF24" s="10" t="n">
         <v>8023.498</v>
-      </c>
-      <c r="AF24" s="10" t="n">
-        <v>9473.919</v>
       </c>
       <c r="AG24" s="10" t="n">
         <v>8943.546</v>
       </c>
       <c r="AH24" s="10" t="n">
+        <v>7745.858</v>
+      </c>
+      <c r="AI24" s="10" t="n">
         <v>10243.582</v>
       </c>
-      <c r="AI24" s="10" t="n">
+      <c r="AJ24" s="10" t="n">
         <v>11411.557</v>
-      </c>
-      <c r="AJ24" s="10" t="n">
-        <v>7745.858</v>
       </c>
       <c r="AK24" s="10" t="n">
         <v>25935.592</v>
       </c>
       <c r="AL24" s="10" t="n">
+        <v>24521.385</v>
+      </c>
+      <c r="AM24" s="10" t="n">
         <v>27673.581</v>
       </c>
-      <c r="AM24" s="10" t="n">
+      <c r="AN24" s="10" t="n">
         <v>27762.326</v>
-      </c>
-      <c r="AN24" s="10" t="n">
-        <v>24521.385</v>
       </c>
       <c r="AO24" s="10" t="n">
         <v>31869.387</v>
       </c>
       <c r="AP24" s="10" t="n">
+        <v>29916.721</v>
+      </c>
+      <c r="AQ24" s="10" t="n">
         <v>24321.52</v>
       </c>
-      <c r="AQ24" s="10" t="n">
+      <c r="AR24" s="10" t="n">
         <v>23486.933</v>
-      </c>
-      <c r="AR24" s="10" t="n">
-        <v>29916.721</v>
       </c>
       <c r="AS24" s="10" t="n">
         <v>28037.188</v>
       </c>
       <c r="AT24" s="10" t="n">
+        <v>27902.815</v>
+      </c>
+      <c r="AU24" s="10" t="n">
         <v>29983.049</v>
       </c>
-      <c r="AU24" s="10" t="n">
+      <c r="AV24" s="10" t="n">
         <v>25937.165</v>
-      </c>
-      <c r="AV24" s="10" t="n">
-        <v>27902.815</v>
       </c>
       <c r="AW24" s="10" t="n">
         <v>24004.568</v>
       </c>
       <c r="AX24" s="10" t="n">
+        <v>18912.987</v>
+      </c>
+      <c r="AY24" s="10" t="n">
         <v>20589.159</v>
       </c>
-      <c r="AY24" s="10" t="n">
+      <c r="AZ24" s="10" t="n">
         <v>14326.279</v>
-      </c>
-      <c r="AZ24" s="10" t="n">
-        <v>18912.987</v>
       </c>
       <c r="BA24" s="10" t="n">
         <v>11555.574</v>
       </c>
       <c r="BB24" s="10" t="n">
+        <v>11951.528</v>
+      </c>
+      <c r="BC24" s="10" t="n">
         <v>16419.262</v>
       </c>
-      <c r="BC24" s="10" t="n">
+      <c r="BD24" s="10" t="n">
         <v>21817.648</v>
-      </c>
-      <c r="BD24" s="10" t="n">
-        <v>11951.528</v>
       </c>
       <c r="BE24" s="10" t="n">
         <v>23734.136</v>
@@ -13826,37 +13826,37 @@
         <v>32612.792</v>
       </c>
       <c r="BI24" s="10" t="n">
+        <v>15905.84</v>
+      </c>
+      <c r="BJ24" s="10" t="n">
         <v>11369.687</v>
       </c>
-      <c r="BJ24" s="10" t="n">
+      <c r="BK24" s="10" t="n">
         <v>12032.681</v>
-      </c>
-      <c r="BK24" s="10" t="n">
-        <v>15905.84</v>
       </c>
       <c r="BL24" s="10" t="n">
         <v>6486.231</v>
       </c>
       <c r="BM24" s="10" t="n">
+        <v>3636.31</v>
+      </c>
+      <c r="BN24" s="10" t="n">
         <v>21151.617</v>
       </c>
-      <c r="BN24" s="10" t="n">
+      <c r="BO24" s="10" t="n">
         <v>33644.848</v>
-      </c>
-      <c r="BO24" s="10" t="n">
-        <v>3636.31</v>
       </c>
       <c r="BP24" s="10" t="n">
         <v>29694.519</v>
       </c>
       <c r="BQ24" s="10" t="n">
+        <v>33744.452</v>
+      </c>
+      <c r="BR24" s="10" t="n">
         <v>31971.761</v>
       </c>
-      <c r="BR24" s="10" t="n">
+      <c r="BS24" s="10" t="n">
         <v>36809.35</v>
-      </c>
-      <c r="BS24" s="10" t="n">
-        <v>33744.452</v>
       </c>
       <c r="BT24" s="10" t="n">
         <v>55278.275</v>
@@ -13972,61 +13972,61 @@
         </is>
       </c>
       <c r="AL26" s="10" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="AM26" s="10" t="n">
         <v>0.87</v>
       </c>
-      <c r="AM26" s="10" t="n">
+      <c r="AN26" s="10" t="n">
         <v>1.818</v>
-      </c>
-      <c r="AN26" s="10" t="n">
-        <v>0.376</v>
       </c>
       <c r="AO26" s="10" t="n">
         <v>3.359</v>
       </c>
       <c r="AP26" s="10" t="n">
+        <v>5.386</v>
+      </c>
+      <c r="AQ26" s="10" t="n">
         <v>6.566</v>
       </c>
-      <c r="AQ26" s="10" t="n">
+      <c r="AR26" s="10" t="n">
         <v>8.888</v>
-      </c>
-      <c r="AR26" s="10" t="n">
-        <v>5.386</v>
       </c>
       <c r="AS26" s="10" t="n">
         <v>9.824</v>
       </c>
       <c r="AT26" s="10" t="n">
+        <v>11.187</v>
+      </c>
+      <c r="AU26" s="10" t="n">
         <v>12.324</v>
       </c>
-      <c r="AU26" s="10" t="n">
+      <c r="AV26" s="10" t="n">
         <v>13.028</v>
-      </c>
-      <c r="AV26" s="10" t="n">
-        <v>11.187</v>
       </c>
       <c r="AW26" s="10" t="n">
         <v>14.321</v>
       </c>
       <c r="AX26" s="10" t="n">
+        <v>16.329</v>
+      </c>
+      <c r="AY26" s="10" t="n">
         <v>16.982</v>
       </c>
-      <c r="AY26" s="10" t="n">
+      <c r="AZ26" s="10" t="n">
         <v>18.826</v>
-      </c>
-      <c r="AZ26" s="10" t="n">
-        <v>16.329</v>
       </c>
       <c r="BA26" s="10" t="n">
         <v>20.741</v>
       </c>
       <c r="BB26" s="10" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="BC26" s="10" t="n">
         <v>24.455</v>
       </c>
-      <c r="BC26" s="10" t="n">
+      <c r="BD26" s="10" t="n">
         <v>25.798</v>
-      </c>
-      <c r="BD26" s="10" t="n">
-        <v>22.65</v>
       </c>
       <c r="BE26" s="10" t="n">
         <v>31.318</v>
@@ -14041,37 +14041,37 @@
         <v>39.159</v>
       </c>
       <c r="BI26" s="10" t="n">
+        <v>41.048</v>
+      </c>
+      <c r="BJ26" s="10" t="n">
         <v>40.823</v>
       </c>
-      <c r="BJ26" s="10" t="n">
+      <c r="BK26" s="10" t="n">
         <v>43.785</v>
-      </c>
-      <c r="BK26" s="10" t="n">
-        <v>41.048</v>
       </c>
       <c r="BL26" s="10" t="n">
         <v>43.9</v>
       </c>
       <c r="BM26" s="10" t="n">
+        <v>43.621</v>
+      </c>
+      <c r="BN26" s="10" t="n">
         <v>43.234</v>
       </c>
-      <c r="BN26" s="10" t="n">
+      <c r="BO26" s="10" t="n">
         <v>42.985</v>
-      </c>
-      <c r="BO26" s="10" t="n">
-        <v>43.621</v>
       </c>
       <c r="BP26" s="10" t="n">
         <v>42.725</v>
       </c>
       <c r="BQ26" s="10" t="n">
+        <v>42.516</v>
+      </c>
+      <c r="BR26" s="10" t="n">
         <v>42.146</v>
       </c>
-      <c r="BR26" s="10" t="n">
+      <c r="BS26" s="10" t="n">
         <v>41.785</v>
-      </c>
-      <c r="BS26" s="10" t="n">
-        <v>42.516</v>
       </c>
       <c r="BT26" s="10" t="n">
         <v>40.356</v>
@@ -14145,54 +14145,54 @@
         <v>517.0650000000001</v>
       </c>
       <c r="AD28" s="10" t="n">
+        <v>516.9059999999999</v>
+      </c>
+      <c r="AE28" s="10" t="n">
         <v>472.938</v>
       </c>
-      <c r="AE28" s="10" t="n">
+      <c r="AF28" s="10" t="n">
         <v>473.242</v>
-      </c>
-      <c r="AF28" s="10" t="n">
-        <v>516.9059999999999</v>
       </c>
       <c r="AG28" s="10" t="n">
         <v>1281.836</v>
       </c>
       <c r="AH28" s="10" t="n">
+        <v>426.773</v>
+      </c>
+      <c r="AI28" s="10" t="n">
         <v>393.851</v>
       </c>
-      <c r="AI28" s="10" t="n">
+      <c r="AJ28" s="10" t="n">
         <v>398.528</v>
-      </c>
-      <c r="AJ28" s="10" t="n">
-        <v>426.773</v>
       </c>
       <c r="AK28" s="10" t="n">
         <v>1833.286</v>
       </c>
       <c r="AL28" s="10" t="n">
+        <v>811.285</v>
+      </c>
+      <c r="AM28" s="10" t="n">
         <v>794.8200000000001</v>
       </c>
-      <c r="AM28" s="10" t="n">
+      <c r="AN28" s="10" t="n">
         <v>784.105</v>
-      </c>
-      <c r="AN28" s="10" t="n">
-        <v>811.285</v>
       </c>
       <c r="AO28" s="10" t="n">
         <v>1597.773</v>
       </c>
       <c r="AP28" s="10" t="n">
+        <v>537.879</v>
+      </c>
+      <c r="AQ28" s="10" t="n">
         <v>530.955</v>
       </c>
-      <c r="AQ28" s="10" t="n">
+      <c r="AR28" s="10" t="n">
         <v>520.347</v>
-      </c>
-      <c r="AR28" s="10" t="n">
-        <v>537.879</v>
       </c>
       <c r="AS28" s="10" t="n">
         <v>1532.23</v>
       </c>
-      <c r="AV28" s="10" t="n">
+      <c r="AT28" s="10" t="n">
         <v>503.2</v>
       </c>
     </row>
@@ -14342,35 +14342,35 @@
       <c r="AB31" s="10" t="n">
         <v>148.958</v>
       </c>
-      <c r="AT31" s="10" t="n">
+      <c r="AU31" s="10" t="n">
         <v>45.312</v>
       </c>
-      <c r="AU31" s="10" t="n">
+      <c r="AV31" s="10" t="n">
         <v>28.026</v>
       </c>
       <c r="AW31" s="10" t="n">
         <v>1319.59</v>
       </c>
       <c r="AX31" s="10" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="AY31" s="10" t="n">
         <v>14.708</v>
       </c>
-      <c r="AY31" s="10" t="n">
+      <c r="AZ31" s="10" t="n">
         <v>13.257</v>
-      </c>
-      <c r="AZ31" s="10" t="n">
-        <v>14.98</v>
       </c>
       <c r="BA31" s="10" t="n">
         <v>855.76</v>
       </c>
       <c r="BB31" s="10" t="n">
+        <v>12.228</v>
+      </c>
+      <c r="BC31" s="10" t="n">
         <v>11.974</v>
       </c>
-      <c r="BC31" s="10" t="n">
+      <c r="BD31" s="10" t="n">
         <v>12.697</v>
-      </c>
-      <c r="BD31" s="10" t="n">
-        <v>12.228</v>
       </c>
       <c r="BE31" s="10" t="n">
         <v>840.653</v>
@@ -14385,37 +14385,37 @@
         <v>1031</v>
       </c>
       <c r="BI31" s="10" t="n">
+        <v>14.769</v>
+      </c>
+      <c r="BJ31" s="10" t="n">
         <v>15.034</v>
       </c>
-      <c r="BJ31" s="10" t="n">
+      <c r="BK31" s="10" t="n">
         <v>13.674</v>
-      </c>
-      <c r="BK31" s="10" t="n">
-        <v>14.769</v>
       </c>
       <c r="BL31" s="10" t="n">
         <v>8.151999999999999</v>
       </c>
       <c r="BM31" s="10" t="n">
+        <v>13.147</v>
+      </c>
+      <c r="BN31" s="10" t="n">
         <v>16.184</v>
       </c>
-      <c r="BN31" s="10" t="n">
+      <c r="BO31" s="10" t="n">
         <v>17.227</v>
-      </c>
-      <c r="BO31" s="10" t="n">
-        <v>13.147</v>
       </c>
       <c r="BP31" s="10" t="n">
         <v>986.316</v>
       </c>
       <c r="BQ31" s="10" t="n">
+        <v>18.387</v>
+      </c>
+      <c r="BR31" s="10" t="n">
         <v>17.965</v>
       </c>
-      <c r="BR31" s="10" t="n">
+      <c r="BS31" s="10" t="n">
         <v>16.528</v>
-      </c>
-      <c r="BS31" s="10" t="n">
-        <v>18.387</v>
       </c>
       <c r="BT31" s="10" t="n">
         <v>16.527</v>
@@ -14512,85 +14512,85 @@
         <v>897.367</v>
       </c>
       <c r="AD32" s="10" t="n">
+        <v>1321.336</v>
+      </c>
+      <c r="AE32" s="10" t="n">
         <v>1426.822</v>
       </c>
-      <c r="AE32" s="10" t="n">
+      <c r="AF32" s="10" t="n">
         <v>1409.661</v>
-      </c>
-      <c r="AF32" s="10" t="n">
-        <v>1321.336</v>
       </c>
       <c r="AG32" s="10" t="n">
         <v>1237.702</v>
       </c>
       <c r="AH32" s="10" t="n">
+        <v>1206.295</v>
+      </c>
+      <c r="AI32" s="10" t="n">
         <v>1277.221</v>
       </c>
-      <c r="AI32" s="10" t="n">
+      <c r="AJ32" s="10" t="n">
         <v>1325.546</v>
-      </c>
-      <c r="AJ32" s="10" t="n">
-        <v>1206.295</v>
       </c>
       <c r="AK32" s="10" t="n">
         <v>1062.342</v>
       </c>
       <c r="AL32" s="10" t="n">
+        <v>759.288</v>
+      </c>
+      <c r="AM32" s="10" t="n">
         <v>543.631</v>
       </c>
-      <c r="AM32" s="10" t="n">
+      <c r="AN32" s="10" t="n">
         <v>538.191</v>
-      </c>
-      <c r="AN32" s="10" t="n">
-        <v>759.288</v>
       </c>
       <c r="AO32" s="10" t="n">
         <v>321.521</v>
       </c>
       <c r="AP32" s="10" t="n">
+        <v>342.09</v>
+      </c>
+      <c r="AQ32" s="10" t="n">
         <v>108.333</v>
       </c>
-      <c r="AQ32" s="10" t="n">
+      <c r="AR32" s="10" t="n">
         <v>83.816</v>
-      </c>
-      <c r="AR32" s="10" t="n">
-        <v>342.09</v>
       </c>
       <c r="AS32" s="10" t="n">
         <v>98.88</v>
       </c>
       <c r="AT32" s="10" t="n">
+        <v>80.328</v>
+      </c>
+      <c r="AU32" s="10" t="n">
         <v>91.587</v>
       </c>
-      <c r="AU32" s="10" t="n">
+      <c r="AV32" s="10" t="n">
         <v>73.35599999999999</v>
-      </c>
-      <c r="AV32" s="10" t="n">
-        <v>80.328</v>
       </c>
       <c r="AW32" s="10" t="n">
         <v>80.009</v>
       </c>
       <c r="AX32" s="10" t="n">
+        <v>64.011</v>
+      </c>
+      <c r="AY32" s="10" t="n">
         <v>62.47</v>
       </c>
-      <c r="AY32" s="10" t="n">
+      <c r="AZ32" s="10" t="n">
         <v>61.435</v>
-      </c>
-      <c r="AZ32" s="10" t="n">
-        <v>64.011</v>
       </c>
       <c r="BA32" s="10" t="n">
         <v>61.127</v>
       </c>
       <c r="BB32" s="10" t="n">
+        <v>62.54</v>
+      </c>
+      <c r="BC32" s="10" t="n">
         <v>67.786</v>
       </c>
-      <c r="BC32" s="10" t="n">
+      <c r="BD32" s="10" t="n">
         <v>71.883</v>
-      </c>
-      <c r="BD32" s="10" t="n">
-        <v>62.54</v>
       </c>
       <c r="BE32" s="10" t="n">
         <v>75.874</v>
@@ -14605,37 +14605,37 @@
         <v>83.801</v>
       </c>
       <c r="BI32" s="10" t="n">
+        <v>83.696</v>
+      </c>
+      <c r="BJ32" s="10" t="n">
         <v>85.19799999999999</v>
       </c>
-      <c r="BJ32" s="10" t="n">
+      <c r="BK32" s="10" t="n">
         <v>77.49299999999999</v>
-      </c>
-      <c r="BK32" s="10" t="n">
-        <v>83.696</v>
       </c>
       <c r="BL32" s="10" t="n">
         <v>46.198</v>
       </c>
       <c r="BM32" s="10" t="n">
+        <v>74.428</v>
+      </c>
+      <c r="BN32" s="10" t="n">
         <v>91.62</v>
       </c>
-      <c r="BN32" s="10" t="n">
+      <c r="BO32" s="10" t="n">
         <v>97.526</v>
-      </c>
-      <c r="BO32" s="10" t="n">
-        <v>74.428</v>
       </c>
       <c r="BP32" s="10" t="n">
         <v>100.733</v>
       </c>
       <c r="BQ32" s="10" t="n">
+        <v>104.095</v>
+      </c>
+      <c r="BR32" s="10" t="n">
         <v>101.704</v>
       </c>
-      <c r="BR32" s="10" t="n">
+      <c r="BS32" s="10" t="n">
         <v>281.136</v>
-      </c>
-      <c r="BS32" s="10" t="n">
-        <v>104.095</v>
       </c>
       <c r="BT32" s="10" t="n">
         <v>278.778</v>
